--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9B650F-63E4-45D7-AE57-4B3C74CEC65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF88FABB-57E6-4C93-BEE7-F3F50ACD5713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="4" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3656,13 +3656,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3795,70 +3801,73 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4320,26 +4329,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>296.01</v>
+            <v>315.08</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>211656.83751926999</v>
+            <v>224842.48506471998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>1238</v>
+            <v>1876</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>38925</v>
+            <v>41403</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4909,7 +4918,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Financials"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -13698,22 +13707,22 @@
       </c>
       <c r="E5" s="19">
         <f>+[2]Main!$H$2</f>
-        <v>296.01</v>
+        <v>315.08</v>
       </c>
       <c r="F5" s="17">
         <f>+[2]Main!$H$4</f>
-        <v>211656.83751926999</v>
+        <v>224842.48506471998</v>
       </c>
       <c r="G5" s="17">
         <f>+[2]Main!$H$6-[2]Main!$H$5</f>
-        <v>37687</v>
+        <v>39527</v>
       </c>
       <c r="H5" s="17">
         <f>+F5+G5</f>
-        <v>249343.83751926999</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>491</v>
+        <v>264369.48506471998</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>1168</v>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF88FABB-57E6-4C93-BEE7-F3F50ACD5713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333584A8-A3D2-4477-BB21-3F8BF2BBB744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3651,10 +3651,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -3677,12 +3678,10 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3801,14 +3800,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3817,11 +3816,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3831,17 +3830,17 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3857,20 +3856,23 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4348,7 +4350,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4692,28 +4694,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="K3">
-            <v>170.9</v>
+            <v>165.35</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>265725.09906889999</v>
+            <v>257382.04687294998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>4216</v>
+            <v>4138</v>
           </cell>
         </row>
         <row r="7">
           <cell r="K7">
-            <v>45695</v>
+            <v>44971</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4734,27 +4736,27 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="M3">
-            <v>58.4</v>
+            <v>66.430000000000007</v>
           </cell>
         </row>
         <row r="5">
           <cell r="M5">
-            <v>98371.986171199998</v>
+            <v>111595.15600779002</v>
           </cell>
         </row>
         <row r="6">
           <cell r="M6">
-            <v>4726</v>
+            <v>1287</v>
           </cell>
         </row>
         <row r="7">
           <cell r="M7">
-            <v>26059</v>
+            <v>24720</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4904,7 +4906,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -33466,15 +33468,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>653721.65659828857</v>
+        <v>658601.77423892857</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>100086.510878</v>
+        <v>104228.510878</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>744116.28747628862</v>
+        <v>753138.40511692874</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33560,25 +33562,25 @@
       </c>
       <c r="E5" s="31">
         <f>+[28]Main!$K$3</f>
-        <v>170.9</v>
+        <v>165.35</v>
       </c>
       <c r="F5" s="17">
         <f>+[28]Main!$K$5</f>
-        <v>265725.09906889999</v>
+        <v>257382.04687294998</v>
       </c>
       <c r="G5" s="17">
         <f>+[28]Main!$K$7-[28]Main!$K$6</f>
-        <v>41479</v>
+        <v>40833</v>
       </c>
       <c r="H5" s="17">
         <f>+F5+G5</f>
-        <v>307204.09906889999</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>491</v>
+        <v>298215.04687294998</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>1168</v>
       </c>
       <c r="J5" s="22">
-        <v>45860</v>
+        <v>45951</v>
       </c>
       <c r="K5" s="31">
         <v>35174</v>
@@ -33673,25 +33675,25 @@
       </c>
       <c r="E6" s="31">
         <f>+[29]Main!$M$3</f>
-        <v>58.4</v>
+        <v>66.430000000000007</v>
       </c>
       <c r="F6" s="17">
         <f>+[29]Main!$M$5</f>
-        <v>98371.986171199998</v>
+        <v>111595.15600779002</v>
       </c>
       <c r="G6" s="17">
         <f>+[29]Main!$M$7-[29]Main!$M$6</f>
-        <v>21333</v>
+        <v>23433</v>
       </c>
       <c r="H6" s="17">
         <f>+F6+G6</f>
-        <v>119704.9861712</v>
-      </c>
-      <c r="I6" s="30" t="s">
-        <v>491</v>
+        <v>135028.15600779001</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>1168</v>
       </c>
       <c r="J6" s="22">
-        <v>45776</v>
+        <v>45960</v>
       </c>
       <c r="K6" s="31">
         <v>24483</v>
@@ -33794,11 +33796,11 @@
       </c>
       <c r="G7" s="17">
         <f>+([29]Main!$M$7-[29]Main!$M$6)*FX!C3</f>
-        <v>27306.240000000002</v>
+        <v>29994.240000000002</v>
       </c>
       <c r="H7" s="17">
         <f>F7+G7</f>
-        <v>141604.864</v>
+        <v>144292.864</v>
       </c>
       <c r="I7" s="30" t="s">
         <v>1168</v>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333584A8-A3D2-4477-BB21-3F8BF2BBB744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F658F58-0CB9-45D8-8829-67E449E9D061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="1168">
   <si>
     <t>Consumer Goods</t>
   </si>
@@ -2352,9 +2352,6 @@
   </si>
   <si>
     <t>IMB.L</t>
-  </si>
-  <si>
-    <t>H224</t>
   </si>
   <si>
     <t>KT&amp;G</t>
@@ -3657,13 +3654,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3800,71 +3803,74 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4713,9 +4719,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4755,8 +4761,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4881,32 +4887,32 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Financials"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>4080</v>
+            <v>4744</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>7244589.7719575036</v>
+            <v>8423611.2446486279</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>1098839</v>
+            <v>865185</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1227407</v>
+            <v>1626433</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4926,22 +4932,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>25.6</v>
+            <v>32.01</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>22246.400000000001</v>
+            <v>26894.802</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1078</v>
+            <v>142</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>8797</v>
+            <v>10501</v>
           </cell>
         </row>
       </sheetData>
@@ -5839,10 +5845,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>781</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>782</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -5890,10 +5896,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>783</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>784</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -5941,7 +5947,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>30</v>
@@ -5992,10 +5998,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>786</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>787</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -6094,10 +6100,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>788</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>789</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -6145,10 +6151,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>790</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>791</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -6196,10 +6202,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>792</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>793</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -6247,10 +6253,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>794</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>795</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -6298,10 +6304,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>796</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>797</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -6349,10 +6355,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>798</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>799</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -6400,10 +6406,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>800</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>801</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -6451,10 +6457,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>802</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>803</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -6502,10 +6508,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>804</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>805</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -6553,10 +6559,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>806</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>807</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -6604,10 +6610,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>808</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>809</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -6655,10 +6661,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>810</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>811</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -6706,10 +6712,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>812</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>813</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -6757,10 +6763,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>814</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>815</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -6808,10 +6814,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>816</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>817</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -6859,10 +6865,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>818</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>819</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -6910,10 +6916,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>820</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>821</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -6961,10 +6967,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>870</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>871</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -7012,10 +7018,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>822</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>823</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -7063,10 +7069,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>824</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>825</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -7114,10 +7120,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>826</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>827</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -7165,10 +7171,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>828</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>829</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -7216,10 +7222,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>830</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>831</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -7267,10 +7273,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>872</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>873</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -7369,10 +7375,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>832</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>833</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -7420,10 +7426,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>834</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>835</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -7471,10 +7477,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>836</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>837</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -7522,10 +7528,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>838</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>839</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -7573,10 +7579,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>840</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>841</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -7624,10 +7630,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>842</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>843</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -7675,10 +7681,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>844</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>845</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -7726,10 +7732,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>846</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>847</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -7777,10 +7783,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>848</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>849</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -7828,10 +7834,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>850</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>851</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -7879,10 +7885,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>852</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>853</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -7930,10 +7936,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>854</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>855</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -7981,10 +7987,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>856</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>857</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -8032,10 +8038,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>858</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>859</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -8083,10 +8089,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>860</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>861</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -8134,10 +8140,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>862</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>863</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -8185,10 +8191,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>864</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>865</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -8236,10 +8242,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>866</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>867</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -8287,10 +8293,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>868</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>869</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -13724,7 +13730,7 @@
         <v>264369.48506471998</v>
       </c>
       <c r="I5" s="33" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
@@ -14080,7 +14086,7 @@
         <v>42081.899404299998</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="Q15" s="17"/>
     </row>
@@ -14710,7 +14716,7 @@
         <v>20819.655533370002</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="Q40" s="17"/>
     </row>
@@ -15222,7 +15228,7 @@
         <v>171</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>172</v>
@@ -17985,7 +17991,7 @@
         <v>609.68633527199995</v>
       </c>
       <c r="I206" s="18" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="J206" s="22">
         <v>46066</v>
@@ -18017,13 +18023,13 @@
         <v>204</v>
       </c>
       <c r="B207" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="C207" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="C207" s="4" t="s">
+      <c r="D207" s="4" t="s">
         <v>875</v>
-      </c>
-      <c r="D207" s="4" t="s">
-        <v>876</v>
       </c>
       <c r="F207" s="17"/>
       <c r="G207" s="17"/>
@@ -18036,13 +18042,13 @@
         <v>205</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>460</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F208" s="17"/>
       <c r="G208" s="17"/>
@@ -18055,13 +18061,13 @@
         <v>206</v>
       </c>
       <c r="B209" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C209" s="4" t="s">
         <v>1160</v>
       </c>
-      <c r="C209" s="4" t="s">
-        <v>1161</v>
-      </c>
       <c r="D209" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F209" s="17"/>
       <c r="G209" s="17"/>
@@ -18074,13 +18080,13 @@
         <v>207</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>439</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F210" s="17"/>
       <c r="G210" s="17"/>
@@ -18093,13 +18099,13 @@
         <v>208</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>441</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F211" s="17"/>
       <c r="G211" s="17"/>
@@ -18112,13 +18118,13 @@
         <v>209</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>437</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F212" s="17"/>
       <c r="G212" s="17"/>
@@ -18131,13 +18137,13 @@
         <v>210</v>
       </c>
       <c r="B213" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="C213" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="C213" s="4" t="s">
+      <c r="D213" s="4" t="s">
         <v>884</v>
-      </c>
-      <c r="D213" s="4" t="s">
-        <v>885</v>
       </c>
       <c r="F213" s="17"/>
       <c r="G213" s="17"/>
@@ -18150,13 +18156,13 @@
         <v>211</v>
       </c>
       <c r="B214" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="C214" s="4" t="s">
         <v>886</v>
       </c>
-      <c r="C214" s="4" t="s">
-        <v>887</v>
-      </c>
       <c r="D214" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F214" s="17"/>
       <c r="G214" s="17"/>
@@ -18169,13 +18175,13 @@
         <v>212</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>464</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F215" s="17"/>
       <c r="G215" s="17"/>
@@ -18188,13 +18194,13 @@
         <v>213</v>
       </c>
       <c r="B216" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="C216" s="4" t="s">
         <v>890</v>
       </c>
-      <c r="C216" s="4" t="s">
+      <c r="D216" s="4" t="s">
         <v>891</v>
-      </c>
-      <c r="D216" s="4" t="s">
-        <v>892</v>
       </c>
       <c r="F216" s="17"/>
       <c r="G216" s="17"/>
@@ -18206,13 +18212,13 @@
         <v>214</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>456</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F217" s="17"/>
       <c r="G217" s="17"/>
@@ -18230,7 +18236,7 @@
         <v>393</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F218" s="17"/>
       <c r="G218" s="17"/>
@@ -18248,7 +18254,7 @@
         <v>448</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F219" s="17"/>
       <c r="G219" s="17"/>
@@ -18260,13 +18266,13 @@
         <v>217</v>
       </c>
       <c r="B220" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="C220" s="4" t="s">
         <v>894</v>
       </c>
-      <c r="C220" s="4" t="s">
+      <c r="D220" s="4" t="s">
         <v>895</v>
-      </c>
-      <c r="D220" s="4" t="s">
-        <v>896</v>
       </c>
       <c r="F220" s="17"/>
       <c r="G220" s="17"/>
@@ -18278,13 +18284,13 @@
         <v>218</v>
       </c>
       <c r="B221" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="C221" s="4" t="s">
         <v>897</v>
       </c>
-      <c r="C221" s="4" t="s">
-        <v>898</v>
-      </c>
       <c r="D221" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F221" s="17"/>
       <c r="G221" s="17"/>
@@ -18296,13 +18302,13 @@
         <v>219</v>
       </c>
       <c r="B222" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="C222" s="4" t="s">
         <v>899</v>
       </c>
-      <c r="C222" s="4" t="s">
+      <c r="D222" s="4" t="s">
         <v>900</v>
-      </c>
-      <c r="D222" s="4" t="s">
-        <v>901</v>
       </c>
       <c r="F222" s="17"/>
       <c r="G222" s="17"/>
@@ -18314,13 +18320,13 @@
         <v>220</v>
       </c>
       <c r="B223" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="C223" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="C223" s="4" t="s">
-        <v>903</v>
-      </c>
       <c r="D223" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F223" s="17"/>
       <c r="G223" s="17"/>
@@ -18332,13 +18338,13 @@
         <v>221</v>
       </c>
       <c r="B224" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="C224" s="4" t="s">
         <v>904</v>
       </c>
-      <c r="C224" s="4" t="s">
-        <v>905</v>
-      </c>
       <c r="D224" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F224" s="17"/>
       <c r="G224" s="17"/>
@@ -18350,13 +18356,13 @@
         <v>222</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C225" s="4" t="s">
         <v>470</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F225" s="17"/>
       <c r="G225" s="17"/>
@@ -18374,7 +18380,7 @@
         <v>462</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F226" s="17"/>
       <c r="G226" s="17"/>
@@ -18386,13 +18392,13 @@
         <v>224</v>
       </c>
       <c r="B227" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="C227" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="C227" s="4" t="s">
+      <c r="D227" s="4" t="s">
         <v>910</v>
-      </c>
-      <c r="D227" s="4" t="s">
-        <v>911</v>
       </c>
       <c r="F227" s="17"/>
       <c r="G227" s="17"/>
@@ -18404,13 +18410,13 @@
         <v>225</v>
       </c>
       <c r="B228" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="C228" s="4" t="s">
         <v>912</v>
       </c>
-      <c r="C228" s="4" t="s">
-        <v>913</v>
-      </c>
       <c r="D228" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F228" s="17"/>
       <c r="G228" s="17"/>
@@ -18422,13 +18428,13 @@
         <v>226</v>
       </c>
       <c r="B229" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="C229" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="C229" s="4" t="s">
+      <c r="D229" s="4" t="s">
         <v>915</v>
-      </c>
-      <c r="D229" s="4" t="s">
-        <v>916</v>
       </c>
       <c r="F229" s="17"/>
       <c r="G229" s="17"/>
@@ -18440,13 +18446,13 @@
         <v>227</v>
       </c>
       <c r="B230" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="C230" s="4" t="s">
         <v>917</v>
       </c>
-      <c r="C230" s="4" t="s">
-        <v>918</v>
-      </c>
       <c r="D230" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F230" s="17"/>
       <c r="G230" s="17"/>
@@ -18458,13 +18464,13 @@
         <v>228</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>435</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F231" s="17"/>
       <c r="G231" s="17"/>
@@ -18476,13 +18482,13 @@
         <v>229</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>446</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F232" s="17"/>
       <c r="G232" s="17"/>
@@ -18494,13 +18500,13 @@
         <v>230</v>
       </c>
       <c r="B233" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C233" s="4" t="s">
         <v>921</v>
       </c>
-      <c r="C233" s="4" t="s">
-        <v>922</v>
-      </c>
       <c r="D233" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F233" s="17"/>
       <c r="G233" s="17"/>
@@ -18512,13 +18518,13 @@
         <v>231</v>
       </c>
       <c r="B234" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C234" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="C234" s="4" t="s">
-        <v>924</v>
-      </c>
       <c r="D234" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F234" s="17"/>
       <c r="G234" s="17"/>
@@ -18530,13 +18536,13 @@
         <v>232</v>
       </c>
       <c r="B235" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C235" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="C235" s="4" t="s">
+      <c r="D235" s="4" t="s">
         <v>927</v>
-      </c>
-      <c r="D235" s="4" t="s">
-        <v>928</v>
       </c>
       <c r="F235" s="17"/>
       <c r="G235" s="17"/>
@@ -18548,13 +18554,13 @@
         <v>233</v>
       </c>
       <c r="B236" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="C236" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="C236" s="4" t="s">
+      <c r="D236" s="4" t="s">
         <v>930</v>
-      </c>
-      <c r="D236" s="4" t="s">
-        <v>931</v>
       </c>
       <c r="F236" s="17"/>
       <c r="G236" s="17"/>
@@ -18566,13 +18572,13 @@
         <v>234</v>
       </c>
       <c r="B237" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="C237" s="4" t="s">
         <v>932</v>
       </c>
-      <c r="C237" s="4" t="s">
-        <v>933</v>
-      </c>
       <c r="D237" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F237" s="17"/>
       <c r="G237" s="17"/>
@@ -18584,13 +18590,13 @@
         <v>235</v>
       </c>
       <c r="B238" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="C238" s="4" t="s">
         <v>934</v>
       </c>
-      <c r="C238" s="4" t="s">
-        <v>935</v>
-      </c>
       <c r="D238" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F238" s="17"/>
       <c r="G238" s="17"/>
@@ -18602,13 +18608,13 @@
         <v>236</v>
       </c>
       <c r="B239" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="C239" s="4" t="s">
         <v>936</v>
       </c>
-      <c r="C239" s="4" t="s">
+      <c r="D239" s="4" t="s">
         <v>937</v>
-      </c>
-      <c r="D239" s="4" t="s">
-        <v>938</v>
       </c>
       <c r="F239" s="17"/>
       <c r="G239" s="17"/>
@@ -18620,13 +18626,13 @@
         <v>237</v>
       </c>
       <c r="B240" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="C240" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="C240" s="4" t="s">
-        <v>857</v>
-      </c>
       <c r="D240" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F240" s="17"/>
       <c r="G240" s="17"/>
@@ -18638,13 +18644,13 @@
         <v>238</v>
       </c>
       <c r="B241" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="C241" s="4" t="s">
         <v>940</v>
       </c>
-      <c r="C241" s="4" t="s">
-        <v>941</v>
-      </c>
       <c r="D241" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F241" s="17"/>
       <c r="G241" s="17"/>
@@ -18656,13 +18662,13 @@
         <v>239</v>
       </c>
       <c r="B242" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="C242" s="4" t="s">
         <v>942</v>
       </c>
-      <c r="C242" s="4" t="s">
-        <v>943</v>
-      </c>
       <c r="D242" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F242" s="17"/>
       <c r="G242" s="17"/>
@@ -18674,13 +18680,13 @@
         <v>240</v>
       </c>
       <c r="B243" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="C243" s="4" t="s">
         <v>944</v>
       </c>
-      <c r="C243" s="4" t="s">
-        <v>945</v>
-      </c>
       <c r="D243" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F243" s="17"/>
       <c r="G243" s="17"/>
@@ -18692,7 +18698,7 @@
         <v>241</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F244" s="17"/>
       <c r="G244" s="17"/>
@@ -18704,13 +18710,13 @@
         <v>242</v>
       </c>
       <c r="B245" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="C245" s="4" t="s">
         <v>947</v>
       </c>
-      <c r="C245" s="4" t="s">
+      <c r="D245" s="4" t="s">
         <v>948</v>
-      </c>
-      <c r="D245" s="4" t="s">
-        <v>949</v>
       </c>
       <c r="F245" s="17"/>
       <c r="G245" s="17"/>
@@ -18722,13 +18728,13 @@
         <v>243</v>
       </c>
       <c r="B246" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="C246" s="4" t="s">
         <v>950</v>
       </c>
-      <c r="C246" s="4" t="s">
-        <v>951</v>
-      </c>
       <c r="D246" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F246" s="17"/>
       <c r="G246" s="17"/>
@@ -18740,13 +18746,13 @@
         <v>244</v>
       </c>
       <c r="B247" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="C247" s="4" t="s">
         <v>952</v>
       </c>
-      <c r="C247" s="4" t="s">
-        <v>953</v>
-      </c>
       <c r="D247" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F247" s="17"/>
       <c r="G247" s="17"/>
@@ -18758,13 +18764,13 @@
         <v>245</v>
       </c>
       <c r="B248" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="C248" s="4" t="s">
         <v>954</v>
       </c>
-      <c r="C248" s="4" t="s">
+      <c r="D248" s="4" t="s">
         <v>955</v>
-      </c>
-      <c r="D248" s="4" t="s">
-        <v>956</v>
       </c>
       <c r="F248" s="17"/>
       <c r="G248" s="17"/>
@@ -18776,13 +18782,13 @@
         <v>246</v>
       </c>
       <c r="B249" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="C249" s="4" t="s">
         <v>957</v>
       </c>
-      <c r="C249" s="4" t="s">
-        <v>958</v>
-      </c>
       <c r="D249" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F249" s="17"/>
       <c r="G249" s="17"/>
@@ -18800,7 +18806,7 @@
         <v>466</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F250" s="17"/>
       <c r="G250" s="17"/>
@@ -18818,7 +18824,7 @@
         <v>450</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F251" s="17"/>
       <c r="G251" s="17"/>
@@ -18830,13 +18836,13 @@
         <v>249</v>
       </c>
       <c r="B252" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="C252" s="4" t="s">
         <v>959</v>
       </c>
-      <c r="C252" s="4" t="s">
-        <v>960</v>
-      </c>
       <c r="D252" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F252" s="17"/>
       <c r="G252" s="17"/>
@@ -18848,13 +18854,13 @@
         <v>250</v>
       </c>
       <c r="B253" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="C253" s="4" t="s">
         <v>961</v>
       </c>
-      <c r="C253" s="4" t="s">
-        <v>962</v>
-      </c>
       <c r="D253" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F253" s="17"/>
       <c r="G253" s="17"/>
@@ -18866,13 +18872,13 @@
         <v>251</v>
       </c>
       <c r="B254" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="C254" s="4" t="s">
         <v>963</v>
       </c>
-      <c r="C254" s="4" t="s">
+      <c r="D254" s="4" t="s">
         <v>964</v>
-      </c>
-      <c r="D254" s="4" t="s">
-        <v>965</v>
       </c>
       <c r="F254" s="17"/>
       <c r="G254" s="17"/>
@@ -18884,13 +18890,13 @@
         <v>252</v>
       </c>
       <c r="B255" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="C255" s="4" t="s">
         <v>966</v>
       </c>
-      <c r="C255" s="4" t="s">
-        <v>967</v>
-      </c>
       <c r="D255" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F255" s="17"/>
       <c r="G255" s="17"/>
@@ -18902,13 +18908,13 @@
         <v>253</v>
       </c>
       <c r="B256" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="C256" s="4" t="s">
         <v>968</v>
       </c>
-      <c r="C256" s="4" t="s">
+      <c r="D256" s="4" t="s">
         <v>969</v>
-      </c>
-      <c r="D256" s="4" t="s">
-        <v>970</v>
       </c>
       <c r="F256" s="17"/>
       <c r="G256" s="17"/>
@@ -18920,13 +18926,13 @@
         <v>254</v>
       </c>
       <c r="B257" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="C257" s="4" t="s">
         <v>971</v>
       </c>
-      <c r="C257" s="4" t="s">
-        <v>972</v>
-      </c>
       <c r="D257" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F257" s="17"/>
       <c r="G257" s="17"/>
@@ -18938,13 +18944,13 @@
         <v>255</v>
       </c>
       <c r="B258" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="C258" s="4" t="s">
         <v>973</v>
       </c>
-      <c r="C258" s="4" t="s">
-        <v>974</v>
-      </c>
       <c r="D258" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F258" s="17"/>
       <c r="G258" s="17"/>
@@ -18956,13 +18962,13 @@
         <v>256</v>
       </c>
       <c r="B259" s="11" t="s">
+        <v>974</v>
+      </c>
+      <c r="C259" s="4" t="s">
         <v>975</v>
       </c>
-      <c r="C259" s="4" t="s">
-        <v>976</v>
-      </c>
       <c r="D259" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E259" s="4">
         <f>+[24]Main!$J$2</f>
@@ -18990,13 +18996,13 @@
         <v>257</v>
       </c>
       <c r="B260" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="C260" s="4" t="s">
         <v>977</v>
       </c>
-      <c r="C260" s="4" t="s">
-        <v>978</v>
-      </c>
       <c r="D260" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F260" s="17"/>
       <c r="G260" s="17"/>
@@ -19008,13 +19014,13 @@
         <v>258</v>
       </c>
       <c r="B261" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="C261" s="4" t="s">
         <v>979</v>
       </c>
-      <c r="C261" s="4" t="s">
+      <c r="D261" s="4" t="s">
         <v>980</v>
-      </c>
-      <c r="D261" s="4" t="s">
-        <v>981</v>
       </c>
       <c r="F261" s="17"/>
       <c r="G261" s="17"/>
@@ -19026,13 +19032,13 @@
         <v>259</v>
       </c>
       <c r="B262" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="C262" s="4" t="s">
         <v>982</v>
       </c>
-      <c r="C262" s="4" t="s">
-        <v>983</v>
-      </c>
       <c r="D262" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F262" s="17"/>
       <c r="G262" s="17"/>
@@ -19044,13 +19050,13 @@
         <v>260</v>
       </c>
       <c r="B263" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C263" s="4" t="s">
         <v>984</v>
       </c>
-      <c r="C263" s="4" t="s">
-        <v>985</v>
-      </c>
       <c r="D263" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F263" s="17"/>
       <c r="G263" s="17"/>
@@ -19062,13 +19068,13 @@
         <v>261</v>
       </c>
       <c r="B264" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="C264" s="4" t="s">
         <v>986</v>
       </c>
-      <c r="C264" s="4" t="s">
-        <v>987</v>
-      </c>
       <c r="D264" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F264" s="17"/>
       <c r="G264" s="17"/>
@@ -19080,13 +19086,13 @@
         <v>262</v>
       </c>
       <c r="B265" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="C265" s="4" t="s">
         <v>988</v>
       </c>
-      <c r="C265" s="4" t="s">
-        <v>989</v>
-      </c>
       <c r="D265" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F265" s="17"/>
       <c r="G265" s="17"/>
@@ -19098,13 +19104,13 @@
         <v>263</v>
       </c>
       <c r="B266" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="C266" s="4" t="s">
         <v>990</v>
       </c>
-      <c r="C266" s="4" t="s">
+      <c r="D266" s="4" t="s">
         <v>991</v>
-      </c>
-      <c r="D266" s="4" t="s">
-        <v>992</v>
       </c>
       <c r="F266" s="17"/>
       <c r="G266" s="17"/>
@@ -19116,13 +19122,13 @@
         <v>264</v>
       </c>
       <c r="B267" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="C267" s="4" t="s">
         <v>993</v>
       </c>
-      <c r="C267" s="4" t="s">
-        <v>994</v>
-      </c>
       <c r="D267" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F267" s="17"/>
       <c r="G267" s="17"/>
@@ -19134,13 +19140,13 @@
         <v>265</v>
       </c>
       <c r="B268" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="C268" s="4" t="s">
         <v>995</v>
       </c>
-      <c r="C268" s="4" t="s">
-        <v>996</v>
-      </c>
       <c r="D268" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F268" s="17"/>
       <c r="G268" s="17"/>
@@ -19152,13 +19158,13 @@
         <v>266</v>
       </c>
       <c r="B269" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="C269" s="4" t="s">
         <v>997</v>
       </c>
-      <c r="C269" s="4" t="s">
-        <v>998</v>
-      </c>
       <c r="D269" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F269" s="17"/>
       <c r="G269" s="17"/>
@@ -19170,13 +19176,13 @@
         <v>267</v>
       </c>
       <c r="B270" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="C270" s="4" t="s">
         <v>999</v>
       </c>
-      <c r="C270" s="4" t="s">
-        <v>1000</v>
-      </c>
       <c r="D270" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F270" s="17"/>
       <c r="G270" s="17"/>
@@ -19188,13 +19194,13 @@
         <v>268</v>
       </c>
       <c r="B271" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C271" s="4" t="s">
         <v>1001</v>
       </c>
-      <c r="C271" s="4" t="s">
+      <c r="D271" s="4" t="s">
         <v>1002</v>
-      </c>
-      <c r="D271" s="4" t="s">
-        <v>1003</v>
       </c>
       <c r="F271" s="17"/>
       <c r="G271" s="17"/>
@@ -19206,13 +19212,13 @@
         <v>269</v>
       </c>
       <c r="B272" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C272" s="4" t="s">
         <v>1004</v>
       </c>
-      <c r="C272" s="4" t="s">
-        <v>1005</v>
-      </c>
       <c r="D272" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F272" s="17"/>
       <c r="G272" s="17"/>
@@ -19224,13 +19230,13 @@
         <v>270</v>
       </c>
       <c r="B273" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C273" s="4" t="s">
         <v>1006</v>
       </c>
-      <c r="C273" s="4" t="s">
-        <v>1007</v>
-      </c>
       <c r="D273" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F273" s="17"/>
       <c r="G273" s="17"/>
@@ -19242,13 +19248,13 @@
         <v>271</v>
       </c>
       <c r="B274" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C274" s="4" t="s">
         <v>1008</v>
       </c>
-      <c r="C274" s="4" t="s">
-        <v>1009</v>
-      </c>
       <c r="D274" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F274" s="17"/>
       <c r="G274" s="17"/>
@@ -19260,13 +19266,13 @@
         <v>272</v>
       </c>
       <c r="B275" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C275" s="4" t="s">
         <v>1010</v>
       </c>
-      <c r="C275" s="4" t="s">
-        <v>1011</v>
-      </c>
       <c r="D275" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F275" s="17"/>
       <c r="G275" s="17"/>
@@ -19278,13 +19284,13 @@
         <v>273</v>
       </c>
       <c r="B276" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C276" s="4" t="s">
         <v>1012</v>
       </c>
-      <c r="C276" s="4" t="s">
-        <v>1013</v>
-      </c>
       <c r="D276" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F276" s="17"/>
       <c r="G276" s="17"/>
@@ -19296,13 +19302,13 @@
         <v>274</v>
       </c>
       <c r="B277" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C277" s="4" t="s">
         <v>1014</v>
       </c>
-      <c r="C277" s="4" t="s">
-        <v>1015</v>
-      </c>
       <c r="D277" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F277" s="17"/>
       <c r="G277" s="17"/>
@@ -19314,13 +19320,13 @@
         <v>275</v>
       </c>
       <c r="B278" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C278" s="4" t="s">
         <v>1016</v>
       </c>
-      <c r="C278" s="4" t="s">
-        <v>1017</v>
-      </c>
       <c r="D278" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F278" s="17"/>
       <c r="G278" s="17"/>
@@ -19332,13 +19338,13 @@
         <v>276</v>
       </c>
       <c r="B279" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C279" s="4" t="s">
         <v>1018</v>
       </c>
-      <c r="C279" s="4" t="s">
-        <v>1019</v>
-      </c>
       <c r="D279" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F279" s="17"/>
       <c r="G279" s="17"/>
@@ -19350,13 +19356,13 @@
         <v>277</v>
       </c>
       <c r="B280" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C280" s="4" t="s">
         <v>1020</v>
       </c>
-      <c r="C280" s="4" t="s">
+      <c r="D280" s="4" t="s">
         <v>1021</v>
-      </c>
-      <c r="D280" s="4" t="s">
-        <v>1022</v>
       </c>
       <c r="F280" s="17"/>
       <c r="G280" s="17"/>
@@ -19368,7 +19374,7 @@
         <v>278</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F281" s="17"/>
       <c r="G281" s="17"/>
@@ -19380,13 +19386,13 @@
         <v>279</v>
       </c>
       <c r="B282" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C282" s="4" t="s">
         <v>1024</v>
       </c>
-      <c r="C282" s="4" t="s">
-        <v>1025</v>
-      </c>
       <c r="D282" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F282" s="17"/>
       <c r="G282" s="17"/>
@@ -19398,13 +19404,13 @@
         <v>280</v>
       </c>
       <c r="B283" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C283" s="4" t="s">
         <v>1026</v>
       </c>
-      <c r="C283" s="4" t="s">
+      <c r="D283" s="4" t="s">
         <v>1027</v>
-      </c>
-      <c r="D283" s="4" t="s">
-        <v>1028</v>
       </c>
       <c r="F283" s="17"/>
       <c r="G283" s="17"/>
@@ -19416,13 +19422,13 @@
         <v>281</v>
       </c>
       <c r="B284" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C284" s="4" t="s">
         <v>1029</v>
       </c>
-      <c r="C284" s="4" t="s">
-        <v>1030</v>
-      </c>
       <c r="D284" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F284" s="17"/>
       <c r="G284" s="17"/>
@@ -19434,13 +19440,13 @@
         <v>282</v>
       </c>
       <c r="B285" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C285" s="4" t="s">
         <v>1031</v>
       </c>
-      <c r="C285" s="4" t="s">
+      <c r="D285" s="4" t="s">
         <v>1032</v>
-      </c>
-      <c r="D285" s="4" t="s">
-        <v>1033</v>
       </c>
       <c r="F285" s="17"/>
       <c r="G285" s="17"/>
@@ -19452,13 +19458,13 @@
         <v>283</v>
       </c>
       <c r="B286" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C286" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="C286" s="4" t="s">
-        <v>1035</v>
-      </c>
       <c r="D286" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F286" s="17"/>
       <c r="G286" s="17"/>
@@ -19476,7 +19482,7 @@
         <v>472</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F287" s="17"/>
       <c r="G287" s="17"/>
@@ -19488,13 +19494,13 @@
         <v>285</v>
       </c>
       <c r="B288" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C288" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="C288" s="4" t="s">
-        <v>1037</v>
-      </c>
       <c r="D288" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F288" s="17"/>
       <c r="G288" s="17"/>
@@ -19506,13 +19512,13 @@
         <v>286</v>
       </c>
       <c r="B289" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C289" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="C289" s="4" t="s">
-        <v>1039</v>
-      </c>
       <c r="D289" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F289" s="17"/>
       <c r="G289" s="17"/>
@@ -19524,13 +19530,13 @@
         <v>287</v>
       </c>
       <c r="B290" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C290" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="C290" s="4" t="s">
-        <v>1041</v>
-      </c>
       <c r="D290" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F290" s="17"/>
       <c r="G290" s="17"/>
@@ -19542,13 +19548,13 @@
         <v>288</v>
       </c>
       <c r="B291" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C291" s="4" t="s">
         <v>1042</v>
       </c>
-      <c r="C291" s="4" t="s">
-        <v>1043</v>
-      </c>
       <c r="D291" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F291" s="17"/>
       <c r="G291" s="17"/>
@@ -19560,13 +19566,13 @@
         <v>289</v>
       </c>
       <c r="B292" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C292" s="4" t="s">
         <v>1044</v>
       </c>
-      <c r="C292" s="4" t="s">
-        <v>1045</v>
-      </c>
       <c r="D292" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F292" s="17"/>
       <c r="G292" s="17"/>
@@ -19578,13 +19584,13 @@
         <v>290</v>
       </c>
       <c r="B293" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C293" s="4" t="s">
         <v>1046</v>
       </c>
-      <c r="C293" s="4" t="s">
+      <c r="D293" s="4" t="s">
         <v>1047</v>
-      </c>
-      <c r="D293" s="4" t="s">
-        <v>1048</v>
       </c>
       <c r="F293" s="17"/>
       <c r="G293" s="17"/>
@@ -19596,13 +19602,13 @@
         <v>291</v>
       </c>
       <c r="B294" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C294" s="4" t="s">
         <v>1049</v>
       </c>
-      <c r="C294" s="4" t="s">
-        <v>1050</v>
-      </c>
       <c r="D294" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F294" s="17"/>
       <c r="G294" s="17"/>
@@ -19614,13 +19620,13 @@
         <v>292</v>
       </c>
       <c r="B295" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C295" s="4" t="s">
         <v>1051</v>
       </c>
-      <c r="C295" s="4" t="s">
-        <v>1052</v>
-      </c>
       <c r="D295" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F295" s="17"/>
       <c r="G295" s="17"/>
@@ -19632,13 +19638,13 @@
         <v>293</v>
       </c>
       <c r="B296" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C296" s="4" t="s">
         <v>1053</v>
       </c>
-      <c r="C296" s="4" t="s">
-        <v>1054</v>
-      </c>
       <c r="D296" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F296" s="17"/>
       <c r="G296" s="17"/>
@@ -19650,13 +19656,13 @@
         <v>294</v>
       </c>
       <c r="B297" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C297" s="4" t="s">
         <v>1055</v>
       </c>
-      <c r="C297" s="4" t="s">
-        <v>1056</v>
-      </c>
       <c r="D297" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F297" s="17"/>
       <c r="G297" s="17"/>
@@ -19668,13 +19674,13 @@
         <v>295</v>
       </c>
       <c r="B298" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C298" s="4" t="s">
         <v>1057</v>
       </c>
-      <c r="C298" s="4" t="s">
+      <c r="D298" s="4" t="s">
         <v>1058</v>
-      </c>
-      <c r="D298" s="4" t="s">
-        <v>1059</v>
       </c>
       <c r="F298" s="17"/>
       <c r="G298" s="17"/>
@@ -19686,13 +19692,13 @@
         <v>296</v>
       </c>
       <c r="B299" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C299" s="4" t="s">
         <v>1060</v>
       </c>
-      <c r="C299" s="4" t="s">
-        <v>1061</v>
-      </c>
       <c r="D299" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F299" s="17"/>
       <c r="G299" s="17"/>
@@ -19704,13 +19710,13 @@
         <v>297</v>
       </c>
       <c r="B300" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C300" s="4" t="s">
         <v>1062</v>
       </c>
-      <c r="C300" s="4" t="s">
-        <v>1063</v>
-      </c>
       <c r="D300" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F300" s="17"/>
       <c r="G300" s="17"/>
@@ -19722,13 +19728,13 @@
         <v>298</v>
       </c>
       <c r="B301" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C301" s="4" t="s">
         <v>1064</v>
       </c>
-      <c r="C301" s="4" t="s">
-        <v>1065</v>
-      </c>
       <c r="D301" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F301" s="17"/>
       <c r="G301" s="17"/>
@@ -19740,13 +19746,13 @@
         <v>299</v>
       </c>
       <c r="B302" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C302" s="4" t="s">
         <v>1066</v>
       </c>
-      <c r="C302" s="4" t="s">
+      <c r="D302" s="4" t="s">
         <v>1067</v>
-      </c>
-      <c r="D302" s="4" t="s">
-        <v>1068</v>
       </c>
       <c r="F302" s="17"/>
       <c r="G302" s="17"/>
@@ -19758,13 +19764,13 @@
         <v>300</v>
       </c>
       <c r="B303" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C303" s="4" t="s">
         <v>1069</v>
       </c>
-      <c r="C303" s="4" t="s">
-        <v>1070</v>
-      </c>
       <c r="D303" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F303" s="17"/>
       <c r="G303" s="17"/>
@@ -19776,13 +19782,13 @@
         <v>301</v>
       </c>
       <c r="B304" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C304" s="4" t="s">
         <v>1071</v>
       </c>
-      <c r="C304" s="4" t="s">
-        <v>1072</v>
-      </c>
       <c r="D304" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F304" s="17"/>
       <c r="G304" s="17"/>
@@ -19794,13 +19800,13 @@
         <v>302</v>
       </c>
       <c r="B305" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C305" s="4" t="s">
         <v>1073</v>
       </c>
-      <c r="C305" s="4" t="s">
-        <v>1074</v>
-      </c>
       <c r="D305" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F305" s="17"/>
       <c r="G305" s="17"/>
@@ -19812,13 +19818,13 @@
         <v>303</v>
       </c>
       <c r="B306" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C306" s="4" t="s">
         <v>1075</v>
       </c>
-      <c r="C306" s="4" t="s">
+      <c r="D306" s="4" t="s">
         <v>1076</v>
-      </c>
-      <c r="D306" s="4" t="s">
-        <v>1077</v>
       </c>
       <c r="F306" s="17"/>
       <c r="G306" s="17"/>
@@ -19830,13 +19836,13 @@
         <v>304</v>
       </c>
       <c r="B307" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C307" s="4" t="s">
         <v>1078</v>
       </c>
-      <c r="C307" s="4" t="s">
+      <c r="D307" s="4" t="s">
         <v>1079</v>
-      </c>
-      <c r="D307" s="4" t="s">
-        <v>1080</v>
       </c>
       <c r="F307" s="17"/>
       <c r="G307" s="17"/>
@@ -19848,13 +19854,13 @@
         <v>305</v>
       </c>
       <c r="B308" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C308" s="4" t="s">
         <v>1081</v>
       </c>
-      <c r="C308" s="4" t="s">
-        <v>1082</v>
-      </c>
       <c r="D308" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F308" s="17"/>
       <c r="G308" s="17"/>
@@ -19866,13 +19872,13 @@
         <v>306</v>
       </c>
       <c r="B309" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C309" s="4" t="s">
         <v>1083</v>
       </c>
-      <c r="C309" s="4" t="s">
-        <v>1084</v>
-      </c>
       <c r="D309" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F309" s="17"/>
       <c r="G309" s="17"/>
@@ -19884,13 +19890,13 @@
         <v>307</v>
       </c>
       <c r="B310" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C310" s="4" t="s">
         <v>1085</v>
       </c>
-      <c r="C310" s="4" t="s">
-        <v>1086</v>
-      </c>
       <c r="D310" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F310" s="17"/>
       <c r="G310" s="17"/>
@@ -19902,13 +19908,13 @@
         <v>308</v>
       </c>
       <c r="B311" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C311" s="4" t="s">
         <v>1087</v>
       </c>
-      <c r="C311" s="4" t="s">
-        <v>1088</v>
-      </c>
       <c r="D311" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F311" s="17"/>
       <c r="G311" s="17"/>
@@ -19920,13 +19926,13 @@
         <v>309</v>
       </c>
       <c r="B312" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C312" s="4" t="s">
         <v>1089</v>
       </c>
-      <c r="C312" s="4" t="s">
-        <v>1090</v>
-      </c>
       <c r="D312" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F312" s="17"/>
       <c r="G312" s="17"/>
@@ -19938,13 +19944,13 @@
         <v>310</v>
       </c>
       <c r="B313" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C313" s="4" t="s">
         <v>1091</v>
       </c>
-      <c r="C313" s="4" t="s">
-        <v>1092</v>
-      </c>
       <c r="D313" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F313" s="17"/>
       <c r="G313" s="17"/>
@@ -19956,13 +19962,13 @@
         <v>311</v>
       </c>
       <c r="B314" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C314" s="4" t="s">
         <v>1093</v>
       </c>
-      <c r="C314" s="4" t="s">
-        <v>1094</v>
-      </c>
       <c r="D314" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F314" s="17"/>
       <c r="G314" s="17"/>
@@ -19974,7 +19980,7 @@
         <v>312</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F315" s="17"/>
       <c r="G315" s="17"/>
@@ -19986,13 +19992,13 @@
         <v>313</v>
       </c>
       <c r="B316" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C316" s="4" t="s">
         <v>1096</v>
       </c>
-      <c r="C316" s="4" t="s">
-        <v>1097</v>
-      </c>
       <c r="D316" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F316" s="17"/>
       <c r="G316" s="17"/>
@@ -20004,13 +20010,13 @@
         <v>314</v>
       </c>
       <c r="B317" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C317" s="4" t="s">
         <v>1098</v>
       </c>
-      <c r="C317" s="4" t="s">
-        <v>1099</v>
-      </c>
       <c r="D317" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F317" s="17"/>
       <c r="G317" s="17"/>
@@ -20022,13 +20028,13 @@
         <v>315</v>
       </c>
       <c r="B318" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C318" s="4" t="s">
         <v>1100</v>
       </c>
-      <c r="C318" s="4" t="s">
-        <v>1101</v>
-      </c>
       <c r="D318" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F318" s="17"/>
       <c r="G318" s="17"/>
@@ -20040,13 +20046,13 @@
         <v>316</v>
       </c>
       <c r="B319" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C319" s="4" t="s">
         <v>1102</v>
       </c>
-      <c r="C319" s="4" t="s">
-        <v>1103</v>
-      </c>
       <c r="D319" s="4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F319" s="17"/>
       <c r="G319" s="17"/>
@@ -20058,13 +20064,13 @@
         <v>317</v>
       </c>
       <c r="B320" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C320" s="4" t="s">
         <v>1104</v>
       </c>
-      <c r="C320" s="4" t="s">
-        <v>1105</v>
-      </c>
       <c r="D320" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F320" s="17"/>
       <c r="G320" s="17"/>
@@ -20076,13 +20082,13 @@
         <v>318</v>
       </c>
       <c r="B321" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C321" s="4" t="s">
         <v>1106</v>
       </c>
-      <c r="C321" s="4" t="s">
-        <v>1107</v>
-      </c>
       <c r="D321" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F321" s="17"/>
       <c r="G321" s="17"/>
@@ -20094,13 +20100,13 @@
         <v>319</v>
       </c>
       <c r="B322" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C322" s="4" t="s">
         <v>1108</v>
       </c>
-      <c r="C322" s="4" t="s">
-        <v>1109</v>
-      </c>
       <c r="D322" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F322" s="17"/>
       <c r="G322" s="17"/>
@@ -20112,13 +20118,13 @@
         <v>320</v>
       </c>
       <c r="B323" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C323" s="4" t="s">
         <v>1110</v>
       </c>
-      <c r="C323" s="4" t="s">
-        <v>1111</v>
-      </c>
       <c r="D323" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F323" s="17"/>
       <c r="G323" s="17"/>
@@ -20130,13 +20136,13 @@
         <v>321</v>
       </c>
       <c r="B324" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C324" s="4" t="s">
         <v>1112</v>
       </c>
-      <c r="C324" s="4" t="s">
-        <v>1113</v>
-      </c>
       <c r="D324" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F324" s="17"/>
       <c r="G324" s="17"/>
@@ -20148,13 +20154,13 @@
         <v>322</v>
       </c>
       <c r="B325" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C325" s="4" t="s">
         <v>1114</v>
       </c>
-      <c r="C325" s="4" t="s">
-        <v>1115</v>
-      </c>
       <c r="D325" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F325" s="17"/>
       <c r="G325" s="17"/>
@@ -20166,7 +20172,7 @@
         <v>323</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F326" s="17"/>
       <c r="G326" s="17"/>
@@ -20178,13 +20184,13 @@
         <v>324</v>
       </c>
       <c r="B327" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C327" s="4" t="s">
         <v>1117</v>
       </c>
-      <c r="C327" s="4" t="s">
-        <v>1118</v>
-      </c>
       <c r="D327" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F327" s="17"/>
       <c r="G327" s="17"/>
@@ -20196,13 +20202,13 @@
         <v>325</v>
       </c>
       <c r="B328" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C328" s="4" t="s">
         <v>1119</v>
       </c>
-      <c r="C328" s="4" t="s">
-        <v>1120</v>
-      </c>
       <c r="D328" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F328" s="17"/>
       <c r="G328" s="17"/>
@@ -20214,13 +20220,13 @@
         <v>326</v>
       </c>
       <c r="B329" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C329" s="4" t="s">
         <v>1121</v>
       </c>
-      <c r="C329" s="4" t="s">
-        <v>1122</v>
-      </c>
       <c r="D329" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F329" s="17"/>
       <c r="G329" s="17"/>
@@ -20232,13 +20238,13 @@
         <v>327</v>
       </c>
       <c r="B330" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C330" s="4" t="s">
         <v>1123</v>
       </c>
-      <c r="C330" s="4" t="s">
-        <v>1124</v>
-      </c>
       <c r="D330" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F330" s="17"/>
       <c r="G330" s="17"/>
@@ -20250,13 +20256,13 @@
         <v>328</v>
       </c>
       <c r="B331" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C331" s="4" t="s">
         <v>1125</v>
       </c>
-      <c r="C331" s="4" t="s">
-        <v>1126</v>
-      </c>
       <c r="D331" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F331" s="17"/>
       <c r="G331" s="17"/>
@@ -20268,13 +20274,13 @@
         <v>329</v>
       </c>
       <c r="B332" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C332" s="4" t="s">
         <v>1127</v>
       </c>
-      <c r="C332" s="4" t="s">
+      <c r="D332" s="4" t="s">
         <v>1128</v>
-      </c>
-      <c r="D332" s="4" t="s">
-        <v>1129</v>
       </c>
       <c r="F332" s="17"/>
       <c r="G332" s="17"/>
@@ -20286,13 +20292,13 @@
         <v>330</v>
       </c>
       <c r="B333" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C333" s="4" t="s">
         <v>1130</v>
       </c>
-      <c r="C333" s="4" t="s">
-        <v>1131</v>
-      </c>
       <c r="D333" s="4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F333" s="17"/>
       <c r="G333" s="17"/>
@@ -20304,13 +20310,13 @@
         <v>331</v>
       </c>
       <c r="B334" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C334" s="4" t="s">
         <v>1132</v>
       </c>
-      <c r="C334" s="4" t="s">
-        <v>1133</v>
-      </c>
       <c r="D334" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F334" s="17"/>
       <c r="G334" s="17"/>
@@ -20322,13 +20328,13 @@
         <v>332</v>
       </c>
       <c r="B335" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C335" s="4" t="s">
         <v>1134</v>
       </c>
-      <c r="C335" s="4" t="s">
-        <v>1135</v>
-      </c>
       <c r="D335" s="4" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F335" s="17"/>
       <c r="G335" s="17"/>
@@ -20340,13 +20346,13 @@
         <v>333</v>
       </c>
       <c r="B336" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C336" s="4" t="s">
         <v>1136</v>
       </c>
-      <c r="C336" s="4" t="s">
-        <v>1137</v>
-      </c>
       <c r="D336" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F336" s="17"/>
       <c r="G336" s="17"/>
@@ -20358,13 +20364,13 @@
         <v>334</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F337" s="17"/>
       <c r="G337" s="17"/>
@@ -20376,13 +20382,13 @@
         <v>335</v>
       </c>
       <c r="B338" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C338" s="4" t="s">
         <v>1139</v>
       </c>
-      <c r="C338" s="4" t="s">
-        <v>1140</v>
-      </c>
       <c r="D338" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F338" s="17"/>
       <c r="G338" s="17"/>
@@ -20394,13 +20400,13 @@
         <v>336</v>
       </c>
       <c r="B339" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C339" s="4" t="s">
         <v>1141</v>
       </c>
-      <c r="C339" s="4" t="s">
+      <c r="D339" s="4" t="s">
         <v>1142</v>
-      </c>
-      <c r="D339" s="4" t="s">
-        <v>1143</v>
       </c>
       <c r="F339" s="17"/>
       <c r="G339" s="17"/>
@@ -20412,13 +20418,13 @@
         <v>337</v>
       </c>
       <c r="B340" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C340" s="4" t="s">
         <v>1144</v>
       </c>
-      <c r="C340" s="4" t="s">
-        <v>1145</v>
-      </c>
       <c r="D340" s="4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F340" s="17"/>
       <c r="G340" s="17"/>
@@ -20430,13 +20436,13 @@
         <v>338</v>
       </c>
       <c r="B341" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C341" s="4" t="s">
         <v>1146</v>
       </c>
-      <c r="C341" s="4" t="s">
-        <v>1147</v>
-      </c>
       <c r="D341" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F341" s="17"/>
       <c r="G341" s="17"/>
@@ -20448,13 +20454,13 @@
         <v>339</v>
       </c>
       <c r="B342" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C342" s="4" t="s">
         <v>1148</v>
       </c>
-      <c r="C342" s="4" t="s">
-        <v>1149</v>
-      </c>
       <c r="D342" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F342" s="17"/>
       <c r="G342" s="17"/>
@@ -20466,13 +20472,13 @@
         <v>340</v>
       </c>
       <c r="B343" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C343" s="4" t="s">
         <v>1150</v>
       </c>
-      <c r="C343" s="4" t="s">
-        <v>1151</v>
-      </c>
       <c r="D343" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F343" s="17"/>
       <c r="G343" s="17"/>
@@ -20484,13 +20490,13 @@
         <v>341</v>
       </c>
       <c r="B344" s="4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C344" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="C344" s="4" t="s">
-        <v>1153</v>
-      </c>
       <c r="D344" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F344" s="17"/>
       <c r="G344" s="17"/>
@@ -20502,13 +20508,13 @@
         <v>342</v>
       </c>
       <c r="B345" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C345" s="4" t="s">
         <v>1154</v>
       </c>
-      <c r="C345" s="4" t="s">
-        <v>1155</v>
-      </c>
       <c r="D345" s="4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F345" s="17"/>
       <c r="G345" s="17"/>
@@ -20520,13 +20526,13 @@
         <v>343</v>
       </c>
       <c r="B346" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C346" s="4" t="s">
         <v>1156</v>
       </c>
-      <c r="C346" s="4" t="s">
-        <v>1157</v>
-      </c>
       <c r="D346" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F346" s="17"/>
       <c r="G346" s="17"/>
@@ -20538,13 +20544,13 @@
         <v>344</v>
       </c>
       <c r="B347" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C347" s="4" t="s">
         <v>1158</v>
       </c>
-      <c r="C347" s="4" t="s">
-        <v>1159</v>
-      </c>
       <c r="D347" s="4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F347" s="17"/>
       <c r="G347" s="17"/>
@@ -20556,13 +20562,13 @@
         <v>345</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E348" s="4">
         <f>+[25]Main!$I$2</f>
@@ -33468,15 +33474,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>658601.77423892857</v>
+        <v>672569.0748132281</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>104228.510878</v>
+        <v>111909.934878</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>753138.40511692874</v>
+        <v>774787.12969122827</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33577,7 +33583,7 @@
         <v>298215.04687294998</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="J5" s="22">
         <v>45951</v>
@@ -33690,7 +33696,7 @@
         <v>135028.15600779001</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="J6" s="22">
         <v>45960</v>
@@ -33803,7 +33809,7 @@
         <v>144292.864</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="J7" s="22">
         <v>46065</v>
@@ -33999,25 +34005,25 @@
       </c>
       <c r="E9" s="17">
         <f>+[32]Main!$J$2</f>
-        <v>4080</v>
+        <v>4744</v>
       </c>
       <c r="F9" s="17">
         <f>+[32]Main!$J$4*FX!C5</f>
-        <v>49263.210449311024</v>
+        <v>57280.556463610665</v>
       </c>
       <c r="G9" s="17">
         <f>+([32]Main!$J$6-[32]Main!$J$5)*FX!C5</f>
-        <v>874.26239999999996</v>
+        <v>5176.4863999999998</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
-        <v>50137.472849311023</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>24</v>
+        <v>62457.042863610666</v>
+      </c>
+      <c r="I9" s="35" t="s">
+        <v>1167</v>
       </c>
       <c r="J9" s="22">
-        <v>45784</v>
+        <v>45960</v>
       </c>
       <c r="K9" s="31">
         <f>2841077*C33</f>
@@ -34105,25 +34111,25 @@
       </c>
       <c r="E10" s="31">
         <f>+[33]Main!$I$2</f>
-        <v>25.6</v>
+        <v>32.01</v>
       </c>
       <c r="F10" s="17">
         <f>+([33]Main!$I$4)*FX!C3</f>
-        <v>28475.392000000003</v>
+        <v>34425.346559999998</v>
       </c>
       <c r="G10" s="17">
         <f>+([33]Main!$I$6-[33]Main!$I$5)*FX!C3</f>
-        <v>9880.32</v>
+        <v>13259.52</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>38355.712</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>738</v>
+        <v>47684.866559999995</v>
+      </c>
+      <c r="I10" s="35" t="s">
+        <v>1167</v>
       </c>
       <c r="J10" s="22">
-        <v>45615</v>
+        <v>45979</v>
       </c>
       <c r="K10" s="31">
         <v>32475</v>
@@ -34196,10 +34202,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
+        <v>738</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>739</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>740</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>617</v>
@@ -34295,10 +34301,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>740</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>741</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>742</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>240</v>
@@ -34390,10 +34396,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>743</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>744</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>58</v>
@@ -34473,10 +34479,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>745</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>746</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>240</v>
@@ -34556,13 +34562,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>748</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>749</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="17">
@@ -34639,10 +34645,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>750</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>751</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>27</v>
@@ -34722,10 +34728,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>752</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>753</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>527</v>
@@ -34805,13 +34811,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>755</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>756</v>
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="17">
@@ -34888,10 +34894,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="11" t="s">
+        <v>756</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>757</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>758</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>27</v>
@@ -34987,10 +34993,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>758</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>759</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>760</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>27</v>
@@ -35086,10 +35092,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>761</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>762</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>27</v>
@@ -35169,10 +35175,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>763</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>764</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>27</v>
@@ -35252,10 +35258,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>765</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>766</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>27</v>
@@ -35335,16 +35341,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>766</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>767</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>768</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
@@ -35361,7 +35367,7 @@
         <v>1988</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
@@ -35491,7 +35497,7 @@
     <row r="26" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="16" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -35565,7 +35571,7 @@
     <row r="27" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -35583,7 +35589,7 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
       <c r="R27" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
@@ -36547,7 +36553,7 @@
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C3" s="32">
         <v>1.28</v>
@@ -36556,7 +36562,7 @@
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C4" s="32">
         <v>1.2E-2</v>
@@ -36565,7 +36571,7 @@
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C5" s="32">
         <v>6.7999999999999996E-3</v>
@@ -36574,7 +36580,7 @@
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C6" s="32">
         <v>7.5000000000000002E-4</v>
@@ -36583,7 +36589,7 @@
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C7" s="32">
         <v>6.2000000000000003E-5</v>
@@ -36592,7 +36598,7 @@
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C8" s="32">
         <v>1.1399999999999999</v>
@@ -36601,7 +36607,7 @@
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C9" s="32">
         <v>1.23</v>
@@ -36610,7 +36616,7 @@
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C10" s="32">
         <v>9.8000000000000004E-2</v>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F658F58-0CB9-45D8-8829-67E449E9D061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0563EE87-0DB2-4DB5-8074-222A5635D8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -57,6 +57,7 @@
     <externalReference r:id="rId40"/>
     <externalReference r:id="rId41"/>
     <externalReference r:id="rId42"/>
+    <externalReference r:id="rId43"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -138,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="1168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="1169">
   <si>
     <t>Consumer Goods</t>
   </si>
@@ -3642,6 +3643,9 @@
   </si>
   <si>
     <t>Q225</t>
+  </si>
+  <si>
+    <t>DKK/USD</t>
   </si>
 </sst>
 </file>
@@ -3654,13 +3658,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3803,79 +3813,81 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
@@ -5113,6 +5125,45 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>86.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>6820.9575000000004</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>67.900000000000006</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>5226.3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -5205,22 +5256,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="G3">
-            <v>172.39</v>
+            <v>267.60000000000002</v>
           </cell>
         </row>
         <row r="5">
           <cell r="G5">
-            <v>71610.157641209997</v>
+            <v>114317.33704320001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="G6">
-            <v>4078</v>
+            <v>4999</v>
           </cell>
         </row>
         <row r="7">
           <cell r="G7">
-            <v>0</v>
+            <v>2721</v>
           </cell>
         </row>
       </sheetData>
@@ -13899,19 +13950,19 @@
       </c>
       <c r="E10" s="19">
         <f>+[6]Main!$G$3</f>
-        <v>172.39</v>
+        <v>267.60000000000002</v>
       </c>
       <c r="F10" s="17">
         <f>+[6]Main!$G$5</f>
-        <v>71610.157641209997</v>
+        <v>114317.33704320001</v>
       </c>
       <c r="G10" s="17">
         <f>+[6]Main!$G$7-[6]Main!$G$6</f>
-        <v>-4078</v>
+        <v>-2278</v>
       </c>
       <c r="H10" s="17">
         <f>+F10+G10</f>
-        <v>67532.157641209997</v>
+        <v>112039.33704320001</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>24</v>
@@ -33474,15 +33525,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>672569.0748132281</v>
+        <v>672460.42801322811</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>111909.934878</v>
+        <v>112735.278878</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>774787.12969122827</v>
+        <v>776703.82689122832</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -34727,7 +34778,7 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="11" t="s">
         <v>751</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -34736,13 +34787,25 @@
       <c r="D17" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="E17" s="31"/>
+      <c r="E17" s="31">
+        <f>+[38]Main!$J$2</f>
+        <v>86.5</v>
+      </c>
       <c r="F17" s="17">
-        <v>1200</v>
-      </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="31"/>
+        <f>+[38]Main!$J$4*FX!C11</f>
+        <v>1091.3532</v>
+      </c>
+      <c r="G17" s="17">
+        <f>+([38]Main!$J$6-[38]Main!$J$5)*FX!C11</f>
+        <v>825.34400000000005</v>
+      </c>
+      <c r="H17" s="17">
+        <f t="shared" ref="H17" si="3">F17+G17</f>
+        <v>1916.6972000000001</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>1167</v>
+      </c>
       <c r="J17" s="22"/>
       <c r="K17" s="31"/>
       <c r="L17" s="4"/>
@@ -34915,7 +34978,7 @@
         <v>214.72500000000002</v>
       </c>
       <c r="H19" s="17">
-        <f t="shared" ref="H19:H20" si="3">F19+G19</f>
+        <f t="shared" ref="H19:H20" si="4">F19+G19</f>
         <v>1446.9675974100001</v>
       </c>
       <c r="I19" s="31" t="s">
@@ -35014,7 +35077,7 @@
         <v>-34.395385999999995</v>
       </c>
       <c r="H20" s="17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>214.52125192000003</v>
       </c>
       <c r="I20" s="31" t="s">
@@ -36522,9 +36585,10 @@
     <hyperlink ref="B24" r:id="rId10" xr:uid="{33C04853-6261-40F8-97CC-F386D2548E01}"/>
     <hyperlink ref="B12" r:id="rId11" xr:uid="{DFD8F2CF-86EC-4B31-8542-B1852B8E4B47}"/>
     <hyperlink ref="A1" location="Main!A1" display="Main " xr:uid="{AAE11089-88D1-477A-AA94-904A456506EA}"/>
+    <hyperlink ref="B17" r:id="rId12" xr:uid="{600A6A38-ECE4-4309-913F-BF689E8755B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId12"/>
+  <legacyDrawing r:id="rId13"/>
 </worksheet>
 </file>
 
@@ -36624,8 +36688,12 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="B11" s="36" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.16</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0563EE87-0DB2-4DB5-8074-222A5635D8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF926BEA-BE47-4E36-A726-F9D392F05DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="1171">
   <si>
     <t>Consumer Goods</t>
   </si>
@@ -3646,6 +3646,12 @@
   </si>
   <si>
     <t>DKK/USD</t>
+  </si>
+  <si>
+    <t>Magnum Ice Cream Company</t>
+  </si>
+  <si>
+    <t>MICC</t>
   </si>
 </sst>
 </file>
@@ -3658,13 +3664,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3813,81 +3825,82 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
@@ -5056,6 +5069,49 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="KPI"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>86.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>6822.6875</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>97.5</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>5104.8999999999996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -5086,7 +5142,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5116,45 +5172,6 @@
         <row r="6">
           <cell r="I6">
             <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>86.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>6820.9575000000004</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>67.900000000000006</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>5226.3</v>
           </cell>
         </row>
       </sheetData>
@@ -20646,6 +20663,15 @@
         <f t="shared" si="5"/>
         <v>346</v>
       </c>
+      <c r="B349" s="11" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C349" s="38" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D349" s="38" t="s">
+        <v>63</v>
+      </c>
       <c r="F349" s="17"/>
       <c r="G349" s="17"/>
       <c r="H349" s="17"/>
@@ -20803,6 +20829,7 @@
     <hyperlink ref="B15" r:id="rId23" xr:uid="{018A53B6-FF7F-40C5-8DBC-8AF6CEADEA65}"/>
     <hyperlink ref="B16" r:id="rId24" xr:uid="{4D5587CE-95E4-41FD-91DC-7D5D63A25FEB}"/>
     <hyperlink ref="B39" r:id="rId25" xr:uid="{10AE8582-E9CB-402A-BE65-0D0ABE3F637D}"/>
+    <hyperlink ref="B349" r:id="rId26" xr:uid="{1E799C65-5F5F-48A9-9C2F-C264768CD49D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33525,15 +33552,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>672460.42801322811</v>
+        <v>672460.70481322811</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>112735.278878</v>
+        <v>112711.11887799999</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>776703.82689122832</v>
+        <v>776679.94369122828</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -34788,20 +34815,20 @@
         <v>527</v>
       </c>
       <c r="E17" s="31">
-        <f>+[38]Main!$J$2</f>
+        <f>+[36]Main!$J$2</f>
         <v>86.5</v>
       </c>
       <c r="F17" s="17">
-        <f>+[38]Main!$J$4*FX!C11</f>
-        <v>1091.3532</v>
+        <f>+[36]Main!$J$4*FX!C11</f>
+        <v>1091.6300000000001</v>
       </c>
       <c r="G17" s="17">
-        <f>+([38]Main!$J$6-[38]Main!$J$5)*FX!C11</f>
-        <v>825.34400000000005</v>
+        <f>+([36]Main!$J$6-[36]Main!$J$5)*FX!C11</f>
+        <v>801.18399999999997</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ref="H17" si="3">F17+G17</f>
-        <v>1916.6972000000001</v>
+        <v>1892.8140000000001</v>
       </c>
       <c r="I17" s="37" t="s">
         <v>1167</v>
@@ -34966,15 +34993,15 @@
         <v>27</v>
       </c>
       <c r="E19" s="31">
-        <f>+[36]Main!$I$3</f>
+        <f>+[37]Main!$I$3</f>
         <v>69.63</v>
       </c>
       <c r="F19" s="17">
-        <f>+[36]Main!$I$5</f>
+        <f>+[37]Main!$I$5</f>
         <v>1232.2425974099999</v>
       </c>
       <c r="G19" s="17">
-        <f>+[36]Main!$I$7-[36]Main!$I$6</f>
+        <f>+[37]Main!$I$7-[37]Main!$I$6</f>
         <v>214.72500000000002</v>
       </c>
       <c r="H19" s="17">
@@ -35065,15 +35092,15 @@
         <v>27</v>
       </c>
       <c r="E20" s="31">
-        <f>+[37]Main!$I$2</f>
+        <f>+[38]Main!$I$2</f>
         <v>4.3600000000000003</v>
       </c>
       <c r="F20" s="17">
-        <f>+[37]Main!$I$4</f>
+        <f>+[38]Main!$I$4</f>
         <v>248.91663792000003</v>
       </c>
       <c r="G20" s="17">
-        <f>+[37]Main!$I$6-[37]Main!$I$5</f>
+        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
         <v>-34.395385999999995</v>
       </c>
       <c r="H20" s="17">

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF926BEA-BE47-4E36-A726-F9D392F05DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DF377F-E28C-4CDE-BC4E-DBF330846FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4362,26 +4362,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>315.08</v>
+            <v>316.05</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>224842.48506471998</v>
+            <v>225076.38231750001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>1876</v>
+            <v>2413</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>41403</v>
+            <v>41283</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -13783,19 +13783,19 @@
       </c>
       <c r="E5" s="19">
         <f>+[2]Main!$H$2</f>
-        <v>315.08</v>
+        <v>316.05</v>
       </c>
       <c r="F5" s="17">
         <f>+[2]Main!$H$4</f>
-        <v>224842.48506471998</v>
+        <v>225076.38231750001</v>
       </c>
       <c r="G5" s="17">
         <f>+[2]Main!$H$6-[2]Main!$H$5</f>
-        <v>39527</v>
+        <v>38870</v>
       </c>
       <c r="H5" s="17">
         <f>+F5+G5</f>
-        <v>264369.48506471998</v>
+        <v>263946.38231750001</v>
       </c>
       <c r="I5" s="33" t="s">
         <v>1167</v>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DF377F-E28C-4CDE-BC4E-DBF330846FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60198C46-0224-49AA-A1C9-A3844830795D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -58,6 +58,7 @@
     <externalReference r:id="rId41"/>
     <externalReference r:id="rId42"/>
     <externalReference r:id="rId43"/>
+    <externalReference r:id="rId44"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -139,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="1174">
   <si>
     <t>Consumer Goods</t>
   </si>
@@ -3652,6 +3653,15 @@
   </si>
   <si>
     <t>MICC</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Alcohol</t>
+  </si>
+  <si>
+    <t>FQ226</t>
   </si>
 </sst>
 </file>
@@ -3664,13 +3674,25 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3825,81 +3847,88 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -4381,7 +4410,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4645,26 +4674,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>71.89</v>
+            <v>70.05</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>309198.91839655</v>
+            <v>301327.69959224999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>14571</v>
+            <v>13874</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>43023</v>
+            <v>47398</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4684,26 +4713,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>97.02</v>
+            <v>87.85</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>110205.01800000001</v>
+            <v>99859.095000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>3957.2000000000003</v>
+            <v>4505.9000000000005</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>15561.400000000001</v>
+            <v>17319.099999999999</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4725,22 +4754,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="K3">
-            <v>165.35</v>
+            <v>157.97999999999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>257382.04687294998</v>
+            <v>245917.78956701997</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>4138</v>
+            <v>4037</v>
           </cell>
         </row>
         <row r="7">
           <cell r="K7">
-            <v>44971</v>
+            <v>50082</v>
           </cell>
         </row>
       </sheetData>
@@ -5172,6 +5201,45 @@
         <row r="6">
           <cell r="I6">
             <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>141.83000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>28675.237054880003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>10544.9</v>
           </cell>
         </row>
       </sheetData>
@@ -21167,22 +21235,22 @@
       </c>
       <c r="E4" s="4">
         <f>+[26]Main!$I$2</f>
-        <v>71.89</v>
+        <v>70.05</v>
       </c>
       <c r="F4" s="17">
         <f>+[26]Main!$I$4</f>
-        <v>309198.91839655</v>
+        <v>301327.69959224999</v>
       </c>
       <c r="G4" s="17">
         <f>+[26]Main!$I$6-[26]Main!$I$5</f>
-        <v>28452</v>
+        <v>33524</v>
       </c>
       <c r="H4" s="17">
         <f>+F4+G4</f>
-        <v>337650.91839655</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>491</v>
+        <v>334851.69959224999</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>1171</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -21700,22 +21768,22 @@
       </c>
       <c r="E9" s="4">
         <f>+[27]Main!$J$2</f>
-        <v>97.02</v>
+        <v>87.85</v>
       </c>
       <c r="F9" s="17">
         <f>+[27]Main!$J$4</f>
-        <v>110205.01800000001</v>
+        <v>99859.095000000001</v>
       </c>
       <c r="G9" s="17">
         <f>+[27]Main!$J$6-[27]Main!$J$5</f>
-        <v>11604.2</v>
+        <v>12813.199999999997</v>
       </c>
       <c r="H9" s="17">
         <f>+F9+G9</f>
-        <v>121809.21800000001</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>491</v>
+        <v>112672.295</v>
+      </c>
+      <c r="I9" s="40" t="s">
+        <v>1171</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -22426,7 +22494,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="11" t="s">
         <v>505</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -22435,16 +22503,32 @@
       <c r="D16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="18"/>
+      <c r="E16" s="4">
+        <f>+[39]Main!$I$2</f>
+        <v>141.83000000000001</v>
+      </c>
+      <c r="F16" s="17">
+        <f>+[39]Main!$I$4</f>
+        <v>28675.237054880003</v>
+      </c>
+      <c r="G16" s="17">
+        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
+        <v>10472.9</v>
+      </c>
+      <c r="H16" s="17">
+        <f>+F16+G16</f>
+        <v>39148.137054880004</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>1173</v>
+      </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
+      <c r="N16" s="41" t="s">
+        <v>1172</v>
+      </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
@@ -33266,6 +33350,7 @@
     <hyperlink ref="B9" r:id="rId1" xr:uid="{F3412E22-551D-42F2-8BCF-4C748D66618A}"/>
     <hyperlink ref="A1" location="Main!A1" display="Main " xr:uid="{A03E94C0-27E1-48E4-83EF-BCF8CC3558D8}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{86CFCFAB-6D19-414A-B52D-B20F8A30E2A7}"/>
+    <hyperlink ref="B16" r:id="rId3" xr:uid="{D92C236F-E190-4A24-819B-177CFDB7C15D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33552,15 +33637,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>672460.70481322811</v>
+        <v>660996.44750729809</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>112711.11887799999</v>
+        <v>117923.11887799999</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>776679.94369122828</v>
+        <v>770427.68638529826</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33646,22 +33731,22 @@
       </c>
       <c r="E5" s="31">
         <f>+[28]Main!$K$3</f>
-        <v>165.35</v>
+        <v>157.97999999999999</v>
       </c>
       <c r="F5" s="17">
         <f>+[28]Main!$K$5</f>
-        <v>257382.04687294998</v>
+        <v>245917.78956701997</v>
       </c>
       <c r="G5" s="17">
         <f>+[28]Main!$K$7-[28]Main!$K$6</f>
-        <v>40833</v>
+        <v>46045</v>
       </c>
       <c r="H5" s="17">
         <f>+F5+G5</f>
-        <v>298215.04687294998</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>1167</v>
+        <v>291962.78956701997</v>
+      </c>
+      <c r="I5" s="39" t="s">
+        <v>1171</v>
       </c>
       <c r="J5" s="22">
         <v>45951</v>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60198C46-0224-49AA-A1C9-A3844830795D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A12CF4-1A8D-4263-9CE2-864C19E98B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="1175">
   <si>
     <t>Consumer Goods</t>
   </si>
@@ -3662,6 +3662,9 @@
   </si>
   <si>
     <t>FQ226</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -3923,13 +3926,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
@@ -4693,7 +4696,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4732,13 +4735,52 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>141.83000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>28675.237054880003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>10544.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4754,69 +4796,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="K3">
-            <v>157.97999999999999</v>
+            <v>182.31</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>245917.78956701997</v>
+            <v>283798.25404749002</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>4037</v>
+            <v>4872</v>
           </cell>
         </row>
         <row r="7">
           <cell r="K7">
-            <v>50082</v>
+            <v>48835</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="M3">
-            <v>66.430000000000007</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="M5">
-            <v>111595.15600779002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="M6">
-            <v>1287</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="M7">
-            <v>24720</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4867,6 +4868,47 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="M3">
+            <v>66.430000000000007</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="M5">
+            <v>111595.15600779002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="M6">
+            <v>1287</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="M7">
+            <v>24720</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
       <sheetName val="Products"/>
       <sheetName val="Model"/>
       <sheetName val="Ratios"/>
@@ -4894,7 +4936,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4933,7 +4975,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4972,7 +5014,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5011,7 +5053,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5050,7 +5092,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5089,7 +5131,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5132,7 +5174,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5171,7 +5213,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5201,45 +5243,6 @@
         <row r="6">
           <cell r="I6">
             <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>141.83000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>28675.237054880003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>72</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>10544.9</v>
           </cell>
         </row>
       </sheetData>
@@ -21249,7 +21252,7 @@
         <f>+F4+G4</f>
         <v>334851.69959224999</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="39" t="s">
         <v>1171</v>
       </c>
       <c r="J4" s="4"/>
@@ -21782,7 +21785,7 @@
         <f>+F9+G9</f>
         <v>112672.295</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="39" t="s">
         <v>1171</v>
       </c>
       <c r="J9" s="4"/>
@@ -22504,29 +22507,29 @@
         <v>27</v>
       </c>
       <c r="E16" s="4">
-        <f>+[39]Main!$I$2</f>
+        <f>+[28]Main!$I$2</f>
         <v>141.83000000000001</v>
       </c>
       <c r="F16" s="17">
-        <f>+[39]Main!$I$4</f>
+        <f>+[28]Main!$I$4</f>
         <v>28675.237054880003</v>
       </c>
       <c r="G16" s="17">
-        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
+        <f>+[28]Main!$I$6-[28]Main!$I$5</f>
         <v>10472.9</v>
       </c>
       <c r="H16" s="17">
         <f>+F16+G16</f>
         <v>39148.137054880004</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="39" t="s">
         <v>1173</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="41" t="s">
+      <c r="N16" s="40" t="s">
         <v>1172</v>
       </c>
       <c r="O16" s="4"/>
@@ -33637,15 +33640,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>660996.44750729809</v>
+        <v>698876.91198776814</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>117923.11887799999</v>
+        <v>115841.11887799999</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>770427.68638529826</v>
+        <v>806226.15086576832</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33730,26 +33733,26 @@
         <v>27</v>
       </c>
       <c r="E5" s="31">
-        <f>+[28]Main!$K$3</f>
-        <v>157.97999999999999</v>
+        <f>+[29]Main!$K$3</f>
+        <v>182.31</v>
       </c>
       <c r="F5" s="17">
-        <f>+[28]Main!$K$5</f>
-        <v>245917.78956701997</v>
+        <f>+[29]Main!$K$5</f>
+        <v>283798.25404749002</v>
       </c>
       <c r="G5" s="17">
-        <f>+[28]Main!$K$7-[28]Main!$K$6</f>
-        <v>46045</v>
+        <f>+[29]Main!$K$7-[29]Main!$K$6</f>
+        <v>43963</v>
       </c>
       <c r="H5" s="17">
         <f>+F5+G5</f>
-        <v>291962.78956701997</v>
-      </c>
-      <c r="I5" s="39" t="s">
-        <v>1171</v>
+        <v>327761.25404749002</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>1174</v>
       </c>
       <c r="J5" s="22">
-        <v>45951</v>
+        <v>46134</v>
       </c>
       <c r="K5" s="31">
         <v>35174</v>
@@ -33843,15 +33846,15 @@
         <v>27</v>
       </c>
       <c r="E6" s="31">
-        <f>+[29]Main!$M$3</f>
+        <f>+[30]Main!$M$3</f>
         <v>66.430000000000007</v>
       </c>
       <c r="F6" s="17">
-        <f>+[29]Main!$M$5</f>
+        <f>+[30]Main!$M$5</f>
         <v>111595.15600779002</v>
       </c>
       <c r="G6" s="17">
-        <f>+[29]Main!$M$7-[29]Main!$M$6</f>
+        <f>+[30]Main!$M$7-[30]Main!$M$6</f>
         <v>23433</v>
       </c>
       <c r="H6" s="17">
@@ -33956,15 +33959,15 @@
         <v>31</v>
       </c>
       <c r="E7" s="31">
-        <f>+[30]Main!$H$2</f>
+        <f>+[31]Main!$H$2</f>
         <v>38.49</v>
       </c>
       <c r="F7" s="17">
-        <f>+[30]Main!$H$5*FX!C3</f>
+        <f>+[31]Main!$H$5*FX!C3</f>
         <v>114298.62400000001</v>
       </c>
       <c r="G7" s="17">
-        <f>+([29]Main!$M$7-[29]Main!$M$6)*FX!C3</f>
+        <f>+([30]Main!$M$7-[30]Main!$M$6)*FX!C3</f>
         <v>29994.240000000002</v>
       </c>
       <c r="H7" s="17">
@@ -34066,15 +34069,15 @@
         <v>40</v>
       </c>
       <c r="E8" s="31">
-        <f>+[31]Main!$H$2</f>
+        <f>+[32]Main!$H$2</f>
         <v>485.4</v>
       </c>
       <c r="F8" s="17">
-        <f>+[31]Main!$H$4*FX!C4</f>
+        <f>+[32]Main!$H$4*FX!C4</f>
         <v>72888.393927045603</v>
       </c>
       <c r="G8" s="17">
-        <f>+([31]Main!$H$6-[31]Main!$H$5)*FX!C4</f>
+        <f>+([32]Main!$H$6-[32]Main!$H$5)*FX!C4</f>
         <v>-228.87708000000006</v>
       </c>
       <c r="H8" s="17">
@@ -34167,15 +34170,15 @@
         <v>95</v>
       </c>
       <c r="E9" s="17">
-        <f>+[32]Main!$J$2</f>
+        <f>+[33]Main!$J$2</f>
         <v>4744</v>
       </c>
       <c r="F9" s="17">
-        <f>+[32]Main!$J$4*FX!C5</f>
+        <f>+[33]Main!$J$4*FX!C5</f>
         <v>57280.556463610665</v>
       </c>
       <c r="G9" s="17">
-        <f>+([32]Main!$J$6-[32]Main!$J$5)*FX!C5</f>
+        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C5</f>
         <v>5176.4863999999998</v>
       </c>
       <c r="H9" s="17">
@@ -34273,15 +34276,15 @@
         <v>31</v>
       </c>
       <c r="E10" s="31">
-        <f>+[33]Main!$I$2</f>
+        <f>+[34]Main!$I$2</f>
         <v>32.01</v>
       </c>
       <c r="F10" s="17">
-        <f>+([33]Main!$I$4)*FX!C3</f>
+        <f>+([34]Main!$I$4)*FX!C3</f>
         <v>34425.346559999998</v>
       </c>
       <c r="G10" s="17">
-        <f>+([33]Main!$I$6-[33]Main!$I$5)*FX!C3</f>
+        <f>+([34]Main!$I$6-[34]Main!$I$5)*FX!C3</f>
         <v>13259.52</v>
       </c>
       <c r="H10" s="17">
@@ -34374,15 +34377,15 @@
         <v>617</v>
       </c>
       <c r="E11" s="17">
-        <f>+[34]Main!$I$2</f>
+        <f>+[35]Main!$I$2</f>
         <v>107400</v>
       </c>
       <c r="F11" s="17">
-        <f>+[34]Main!$I$4*FX!C6</f>
+        <f>+[35]Main!$I$4*FX!C6</f>
         <v>9270.9964935000007</v>
       </c>
       <c r="G11" s="17">
-        <f>+([34]Main!$I$6-[34]Main!$I$5)*FX!C6</f>
+        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C6</f>
         <v>-575.42399999999998</v>
       </c>
       <c r="H11" s="17">
@@ -34473,15 +34476,15 @@
         <v>240</v>
       </c>
       <c r="E12" s="17">
-        <f>+[35]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>590</v>
       </c>
       <c r="F12" s="17">
-        <f>+[35]Main!$I$4*FX!C7</f>
+        <f>+[36]Main!$I$4*FX!C7</f>
         <v>4254.915253002001</v>
       </c>
       <c r="G12" s="17">
-        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C7</f>
+        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C7</f>
         <v>-162.340056</v>
       </c>
       <c r="H12" s="17">
@@ -34900,15 +34903,15 @@
         <v>527</v>
       </c>
       <c r="E17" s="31">
-        <f>+[36]Main!$J$2</f>
+        <f>+[37]Main!$J$2</f>
         <v>86.5</v>
       </c>
       <c r="F17" s="17">
-        <f>+[36]Main!$J$4*FX!C11</f>
+        <f>+[37]Main!$J$4*FX!C11</f>
         <v>1091.6300000000001</v>
       </c>
       <c r="G17" s="17">
-        <f>+([36]Main!$J$6-[36]Main!$J$5)*FX!C11</f>
+        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C11</f>
         <v>801.18399999999997</v>
       </c>
       <c r="H17" s="17">
@@ -35078,15 +35081,15 @@
         <v>27</v>
       </c>
       <c r="E19" s="31">
-        <f>+[37]Main!$I$3</f>
+        <f>+[38]Main!$I$3</f>
         <v>69.63</v>
       </c>
       <c r="F19" s="17">
-        <f>+[37]Main!$I$5</f>
+        <f>+[38]Main!$I$5</f>
         <v>1232.2425974099999</v>
       </c>
       <c r="G19" s="17">
-        <f>+[37]Main!$I$7-[37]Main!$I$6</f>
+        <f>+[38]Main!$I$7-[38]Main!$I$6</f>
         <v>214.72500000000002</v>
       </c>
       <c r="H19" s="17">
@@ -35177,15 +35180,15 @@
         <v>27</v>
       </c>
       <c r="E20" s="31">
-        <f>+[38]Main!$I$2</f>
+        <f>+[39]Main!$I$2</f>
         <v>4.3600000000000003</v>
       </c>
       <c r="F20" s="17">
-        <f>+[38]Main!$I$4</f>
+        <f>+[39]Main!$I$4</f>
         <v>248.91663792000003</v>
       </c>
       <c r="G20" s="17">
-        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
+        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
         <v>-34.395385999999995</v>
       </c>
       <c r="H20" s="17">

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A12CF4-1A8D-4263-9CE2-864C19E98B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CBF81F-8A8C-4AC7-8A23-382AE05EE174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
@@ -3677,13 +3677,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3850,86 +3856,89 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4815,9 +4824,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4918,19 +4927,19 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>38.49</v>
+            <v>60.8</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>89295.8</v>
+            <v>95703.12</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -33640,7 +33649,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>698876.91198776814</v>
+        <v>707078.28158776811</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
@@ -33648,7 +33657,7 @@
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>806226.15086576832</v>
+        <v>814427.52046576829</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33960,11 +33969,11 @@
       </c>
       <c r="E7" s="31">
         <f>+[31]Main!$H$2</f>
-        <v>38.49</v>
+        <v>60.8</v>
       </c>
       <c r="F7" s="17">
         <f>+[31]Main!$H$5*FX!C3</f>
-        <v>114298.62400000001</v>
+        <v>122499.9936</v>
       </c>
       <c r="G7" s="17">
         <f>+([30]Main!$M$7-[30]Main!$M$6)*FX!C3</f>
@@ -33972,13 +33981,13 @@
       </c>
       <c r="H7" s="17">
         <f>F7+G7</f>
-        <v>144292.864</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>1167</v>
+        <v>152494.23360000001</v>
+      </c>
+      <c r="I7" s="42" t="s">
+        <v>1174</v>
       </c>
       <c r="J7" s="22">
-        <v>46065</v>
+        <v>46203</v>
       </c>
       <c r="K7" s="31">
         <f>25592.8810095771*C31</f>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CBF81F-8A8C-4AC7-8A23-382AE05EE174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2387926-6F80-4DFD-9000-C90A3EE3DF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3677,13 +3677,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3856,90 +3862,93 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -4564,31 +4573,31 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>92.6</v>
+            <v>95.4</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>630.84657479999998</v>
+            <v>649.92184920000011</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>110.125</v>
+            <v>116.907</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>14.090999999999999</v>
+            <v>12.127000000000001</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4936,10 +4945,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -18124,25 +18133,25 @@
       </c>
       <c r="E206" s="4">
         <f>+[23]Main!$H$2</f>
-        <v>92.6</v>
+        <v>95.4</v>
       </c>
       <c r="F206" s="17">
         <f>+[23]Main!$H$4*FX!C8</f>
-        <v>719.16509527199992</v>
+        <v>740.91090808800004</v>
       </c>
       <c r="G206" s="17">
         <f>+([23]Main!$H$6-[23]Main!$H$5)*FX!C8</f>
-        <v>-109.47875999999999</v>
+        <v>-119.44919999999999</v>
       </c>
       <c r="H206" s="17">
         <f>+F206+G206</f>
-        <v>609.68633527199995</v>
-      </c>
-      <c r="I206" s="18" t="s">
-        <v>1167</v>
+        <v>621.46170808800002</v>
+      </c>
+      <c r="I206" s="43" t="s">
+        <v>1174</v>
       </c>
       <c r="J206" s="22">
-        <v>46066</v>
+        <v>46186</v>
       </c>
       <c r="K206" s="18"/>
       <c r="L206" s="23">

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2387926-6F80-4DFD-9000-C90A3EE3DF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A6D418-67F8-420B-B9A9-799CE76CF99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3677,13 +3677,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3862,93 +3868,95 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -4592,12 +4600,12 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4893,12 +4901,12 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="M3">
-            <v>66.430000000000007</v>
+            <v>68.67</v>
           </cell>
         </row>
         <row r="5">
           <cell r="M5">
-            <v>111595.15600779002</v>
+            <v>116097.73488747</v>
           </cell>
         </row>
         <row r="6">
@@ -4912,8 +4920,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5046,26 +5054,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>32.01</v>
+            <v>32.61</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>26894.802</v>
+            <v>26896.727999999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>142</v>
+            <v>1439</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>10501</v>
+            <v>9594</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5184,9 +5192,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -18147,7 +18155,7 @@
         <f>+F206+G206</f>
         <v>621.46170808800002</v>
       </c>
-      <c r="I206" s="43" t="s">
+      <c r="I206" s="42" t="s">
         <v>1174</v>
       </c>
       <c r="J206" s="22">
@@ -20755,10 +20763,10 @@
       <c r="B349" s="11" t="s">
         <v>1169</v>
       </c>
-      <c r="C349" s="38" t="s">
+      <c r="C349" s="37" t="s">
         <v>1170</v>
       </c>
-      <c r="D349" s="38" t="s">
+      <c r="D349" s="37" t="s">
         <v>63</v>
       </c>
       <c r="F349" s="17"/>
@@ -21270,7 +21278,7 @@
         <f>+F4+G4</f>
         <v>334851.69959224999</v>
       </c>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="38" t="s">
         <v>1171</v>
       </c>
       <c r="J4" s="4"/>
@@ -21803,7 +21811,7 @@
         <f>+F9+G9</f>
         <v>112672.295</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="38" t="s">
         <v>1171</v>
       </c>
       <c r="J9" s="4"/>
@@ -22540,14 +22548,14 @@
         <f>+F16+G16</f>
         <v>39148.137054880004</v>
       </c>
-      <c r="I16" s="39" t="s">
+      <c r="I16" s="38" t="s">
         <v>1173</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="40" t="s">
+      <c r="N16" s="39" t="s">
         <v>1172</v>
       </c>
       <c r="O16" s="4"/>
@@ -33650,7 +33658,7 @@
       <c r="A4" s="9" t="s">
         <v>721</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>722</v>
       </c>
       <c r="C4" s="4"/>
@@ -33658,15 +33666,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>707078.28158776811</v>
+        <v>711583.32574744802</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>115841.11887799999</v>
+        <v>113019.99887799998</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>814427.52046576829</v>
+        <v>816111.44462544832</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33766,7 +33774,7 @@
         <f>+F5+G5</f>
         <v>327761.25404749002</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="40" t="s">
         <v>1174</v>
       </c>
       <c r="J5" s="22">
@@ -33865,11 +33873,11 @@
       </c>
       <c r="E6" s="31">
         <f>+[30]Main!$M$3</f>
-        <v>66.430000000000007</v>
+        <v>68.67</v>
       </c>
       <c r="F6" s="17">
         <f>+[30]Main!$M$5</f>
-        <v>111595.15600779002</v>
+        <v>116097.73488747</v>
       </c>
       <c r="G6" s="17">
         <f>+[30]Main!$M$7-[30]Main!$M$6</f>
@@ -33877,7 +33885,7 @@
       </c>
       <c r="H6" s="17">
         <f>+F6+G6</f>
-        <v>135028.15600779001</v>
+        <v>139530.73488747</v>
       </c>
       <c r="I6" s="34" t="s">
         <v>1167</v>
@@ -33992,7 +34000,7 @@
         <f>F7+G7</f>
         <v>152494.23360000001</v>
       </c>
-      <c r="I7" s="42" t="s">
+      <c r="I7" s="41" t="s">
         <v>1174</v>
       </c>
       <c r="J7" s="22">
@@ -34295,25 +34303,25 @@
       </c>
       <c r="E10" s="31">
         <f>+[34]Main!$I$2</f>
-        <v>32.01</v>
+        <v>32.61</v>
       </c>
       <c r="F10" s="17">
         <f>+([34]Main!$I$4)*FX!C3</f>
-        <v>34425.346559999998</v>
+        <v>34427.811840000002</v>
       </c>
       <c r="G10" s="17">
         <f>+([34]Main!$I$6-[34]Main!$I$5)*FX!C3</f>
-        <v>13259.52</v>
+        <v>10438.4</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>47684.866559999995</v>
-      </c>
-      <c r="I10" s="35" t="s">
-        <v>1167</v>
+        <v>44866.211840000004</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>1174</v>
       </c>
       <c r="J10" s="22">
-        <v>45979</v>
+        <v>46156</v>
       </c>
       <c r="K10" s="31">
         <v>32475</v>
@@ -34936,10 +34944,12 @@
         <f t="shared" ref="H17" si="3">F17+G17</f>
         <v>1892.8140000000001</v>
       </c>
-      <c r="I17" s="37" t="s">
-        <v>1167</v>
-      </c>
-      <c r="J17" s="22"/>
+      <c r="I17" s="43" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J17" s="22">
+        <v>46085</v>
+      </c>
       <c r="K17" s="31"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -35021,7 +35031,7 @@
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17"/>
-      <c r="I18" s="31"/>
+      <c r="I18" s="30"/>
       <c r="J18" s="22"/>
       <c r="K18" s="31"/>
       <c r="L18" s="4"/>
@@ -35114,7 +35124,7 @@
         <f t="shared" ref="H19:H20" si="4">F19+G19</f>
         <v>1446.9675974100001</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="30" t="s">
         <v>24</v>
       </c>
       <c r="J19" s="22">
@@ -35213,7 +35223,7 @@
         <f t="shared" si="4"/>
         <v>214.52125192000003</v>
       </c>
-      <c r="I20" s="31" t="s">
+      <c r="I20" s="30" t="s">
         <v>32</v>
       </c>
       <c r="J20" s="22">

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A6D418-67F8-420B-B9A9-799CE76CF99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F78F06-7CC9-4DE7-88A7-629A57885A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3677,13 +3677,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3868,92 +3874,95 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3982,6 +3991,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4021,6 +4031,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4060,6 +4071,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4099,6 +4111,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4138,6 +4151,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4177,6 +4191,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4216,6 +4231,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4255,6 +4271,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4294,6 +4311,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4333,6 +4351,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4372,6 +4391,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4411,6 +4431,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4450,6 +4471,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4489,6 +4511,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4528,6 +4551,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4567,6 +4591,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4616,6 +4641,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4655,6 +4681,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4694,6 +4721,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4733,6 +4761,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4772,6 +4801,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4811,6 +4841,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4854,6 +4885,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4891,6 +4923,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4920,8 +4953,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4932,6 +4965,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4967,6 +5001,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5006,6 +5041,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5045,6 +5081,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5073,7 +5110,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5084,6 +5121,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5123,6 +5161,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5162,6 +5201,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5173,22 +5213,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>86.5</v>
+            <v>100.6</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>6822.6875</v>
+            <v>7921.3445999999994</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>97.5</v>
+            <v>197.7</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>5104.8999999999996</v>
+            <v>5080.6000000000004</v>
           </cell>
         </row>
       </sheetData>
@@ -5205,6 +5245,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5244,6 +5285,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5283,6 +5325,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5322,6 +5365,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5361,6 +5405,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5400,6 +5445,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5433,6 +5479,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5472,6 +5519,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -33666,15 +33714,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>711583.32574744802</v>
+        <v>711759.11088344804</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>113019.99887799998</v>
+        <v>113000.07887799999</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>816111.44462544832</v>
+        <v>816267.3097614483</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -34930,25 +34978,25 @@
       </c>
       <c r="E17" s="31">
         <f>+[37]Main!$J$2</f>
-        <v>86.5</v>
+        <v>100.6</v>
       </c>
       <c r="F17" s="17">
         <f>+[37]Main!$J$4*FX!C11</f>
-        <v>1091.6300000000001</v>
+        <v>1267.4151359999998</v>
       </c>
       <c r="G17" s="17">
         <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C11</f>
-        <v>801.18399999999997</v>
+        <v>781.26400000000012</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ref="H17" si="3">F17+G17</f>
-        <v>1892.8140000000001</v>
-      </c>
-      <c r="I17" s="43" t="s">
-        <v>1171</v>
+        <v>2048.6791359999997</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>1174</v>
       </c>
       <c r="J17" s="22">
-        <v>46085</v>
+        <v>46162</v>
       </c>
       <c r="K17" s="31"/>
       <c r="L17" s="4"/>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F78F06-7CC9-4DE7-88A7-629A57885A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4129169B-0A58-4024-A1A1-89F2B3A94C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
@@ -3677,19 +3677,13 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3874,92 +3868,89 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4934,27 +4925,27 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="M3">
-            <v>68.67</v>
+            <v>66.25</v>
           </cell>
         </row>
         <row r="5">
           <cell r="M5">
-            <v>116097.73488747</v>
+            <v>111498.75</v>
           </cell>
         </row>
         <row r="6">
           <cell r="M6">
-            <v>1287</v>
+            <v>4474</v>
           </cell>
         </row>
         <row r="7">
           <cell r="M7">
-            <v>24720</v>
+            <v>25709</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5030,7 +5021,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5051,26 +5042,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>4744</v>
+            <v>5714</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>8423611.2446486279</v>
+            <v>10144658.456</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>865185</v>
+            <v>273923</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1626433</v>
+            <v>679542</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5213,12 +5204,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>100.6</v>
+            <v>66.2</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>7921.3445999999994</v>
+            <v>5212.6541999999999</v>
           </cell>
         </row>
         <row r="5">
@@ -18203,7 +18194,7 @@
         <f>+F206+G206</f>
         <v>621.46170808800002</v>
       </c>
-      <c r="I206" s="42" t="s">
+      <c r="I206" s="40" t="s">
         <v>1174</v>
       </c>
       <c r="J206" s="22">
@@ -20811,10 +20802,10 @@
       <c r="B349" s="11" t="s">
         <v>1169</v>
       </c>
-      <c r="C349" s="37" t="s">
+      <c r="C349" s="35" t="s">
         <v>1170</v>
       </c>
-      <c r="D349" s="37" t="s">
+      <c r="D349" s="35" t="s">
         <v>63</v>
       </c>
       <c r="F349" s="17"/>
@@ -21326,7 +21317,7 @@
         <f>+F4+G4</f>
         <v>334851.69959224999</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="36" t="s">
         <v>1171</v>
       </c>
       <c r="J4" s="4"/>
@@ -21859,7 +21850,7 @@
         <f>+F9+G9</f>
         <v>112672.295</v>
       </c>
-      <c r="I9" s="38" t="s">
+      <c r="I9" s="36" t="s">
         <v>1171</v>
       </c>
       <c r="J9" s="4"/>
@@ -22596,14 +22587,14 @@
         <f>+F16+G16</f>
         <v>39148.137054880004</v>
       </c>
-      <c r="I16" s="38" t="s">
+      <c r="I16" s="36" t="s">
         <v>1173</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="39" t="s">
+      <c r="N16" s="37" t="s">
         <v>1172</v>
       </c>
       <c r="O16" s="4"/>
@@ -33714,15 +33705,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>711759.11088344804</v>
+        <v>718429.85656916746</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>113000.07887799999</v>
+        <v>105570.36167799999</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>816267.3097614483</v>
+        <v>815508.33824716776</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33822,7 +33813,7 @@
         <f>+F5+G5</f>
         <v>327761.25404749002</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="38" t="s">
         <v>1174</v>
       </c>
       <c r="J5" s="22">
@@ -33921,25 +33912,25 @@
       </c>
       <c r="E6" s="31">
         <f>+[30]Main!$M$3</f>
-        <v>68.67</v>
+        <v>66.25</v>
       </c>
       <c r="F6" s="17">
         <f>+[30]Main!$M$5</f>
-        <v>116097.73488747</v>
+        <v>111498.75</v>
       </c>
       <c r="G6" s="17">
         <f>+[30]Main!$M$7-[30]Main!$M$6</f>
-        <v>23433</v>
+        <v>21235</v>
       </c>
       <c r="H6" s="17">
         <f>+F6+G6</f>
-        <v>139530.73488747</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>1167</v>
+        <v>132733.75</v>
+      </c>
+      <c r="I6" s="43" t="s">
+        <v>1174</v>
       </c>
       <c r="J6" s="22">
-        <v>45960</v>
+        <v>46142</v>
       </c>
       <c r="K6" s="31">
         <v>24483</v>
@@ -34042,13 +34033,13 @@
       </c>
       <c r="G7" s="17">
         <f>+([30]Main!$M$7-[30]Main!$M$6)*FX!C3</f>
-        <v>29994.240000000002</v>
+        <v>27180.799999999999</v>
       </c>
       <c r="H7" s="17">
         <f>F7+G7</f>
-        <v>152494.23360000001</v>
-      </c>
-      <c r="I7" s="41" t="s">
+        <v>149680.7936</v>
+      </c>
+      <c r="I7" s="39" t="s">
         <v>1174</v>
       </c>
       <c r="J7" s="22">
@@ -34245,25 +34236,25 @@
       </c>
       <c r="E9" s="17">
         <f>+[33]Main!$J$2</f>
-        <v>4744</v>
+        <v>5714</v>
       </c>
       <c r="F9" s="17">
         <f>+[33]Main!$J$4*FX!C5</f>
-        <v>57280.556463610665</v>
+        <v>68983.677500799997</v>
       </c>
       <c r="G9" s="17">
         <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C5</f>
-        <v>5176.4863999999998</v>
+        <v>2758.2091999999998</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
-        <v>62457.042863610666</v>
-      </c>
-      <c r="I9" s="35" t="s">
-        <v>1167</v>
+        <v>71741.886700799994</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>1174</v>
       </c>
       <c r="J9" s="22">
-        <v>45960</v>
+        <v>46150</v>
       </c>
       <c r="K9" s="31">
         <f>2841077*C33</f>
@@ -34365,7 +34356,7 @@
         <f t="shared" si="1"/>
         <v>44866.211840000004</v>
       </c>
-      <c r="I10" s="43" t="s">
+      <c r="I10" s="41" t="s">
         <v>1174</v>
       </c>
       <c r="J10" s="22">
@@ -34978,11 +34969,11 @@
       </c>
       <c r="E17" s="31">
         <f>+[37]Main!$J$2</f>
-        <v>100.6</v>
+        <v>66.2</v>
       </c>
       <c r="F17" s="17">
         <f>+[37]Main!$J$4*FX!C11</f>
-        <v>1267.4151359999998</v>
+        <v>834.02467200000001</v>
       </c>
       <c r="G17" s="17">
         <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C11</f>
@@ -34990,9 +34981,9 @@
       </c>
       <c r="H17" s="17">
         <f t="shared" ref="H17" si="3">F17+G17</f>
-        <v>2048.6791359999997</v>
-      </c>
-      <c r="I17" s="44" t="s">
+        <v>1615.2886720000001</v>
+      </c>
+      <c r="I17" s="42" t="s">
         <v>1174</v>
       </c>
       <c r="J17" s="22">
@@ -36879,7 +36870,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="34" t="s">
         <v>1168</v>
       </c>
       <c r="C11" s="4">

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4129169B-0A58-4024-A1A1-89F2B3A94C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A5DF34-0258-45FC-830B-1BF1641F8B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4451,7 +4451,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4944,8 +4944,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5021,7 +5021,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5061,7 +5061,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5223,9 +5223,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A5DF34-0258-45FC-830B-1BF1641F8B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8304AA5F-FB46-4BF0-BD72-7823357364CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="4" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4451,7 +4451,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8304AA5F-FB46-4BF0-BD72-7823357364CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8FF1B6-3FAC-4716-95EE-3D4601A243A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="4" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="2" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -59,6 +59,7 @@
     <externalReference r:id="rId42"/>
     <externalReference r:id="rId43"/>
     <externalReference r:id="rId44"/>
+    <externalReference r:id="rId45"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -140,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="1175">
   <si>
     <t>Consumer Goods</t>
   </si>
@@ -3677,13 +3678,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="00000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3868,86 +3875,89 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3956,7 +3966,7 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -5351,6 +5361,46 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>153.69</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>210040.29295557001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>9530</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>49182</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -21514,7 +21564,7 @@
         <f>+A5+1</f>
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="11" t="s">
         <v>483</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -21523,11 +21573,25 @@
       <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18"/>
+      <c r="E6" s="4">
+        <f>+[40]Main!$I$2</f>
+        <v>153.69</v>
+      </c>
+      <c r="F6" s="17">
+        <f>+[40]Main!$I$4</f>
+        <v>210040.29295557001</v>
+      </c>
+      <c r="G6" s="17">
+        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
+        <v>39652</v>
+      </c>
+      <c r="H6" s="17">
+        <f>+F6+G6</f>
+        <v>249692.29295557001</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>1174</v>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -33419,6 +33483,7 @@
     <hyperlink ref="A1" location="Main!A1" display="Main " xr:uid="{A03E94C0-27E1-48E4-83EF-BCF8CC3558D8}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{86CFCFAB-6D19-414A-B52D-B20F8A30E2A7}"/>
     <hyperlink ref="B16" r:id="rId3" xr:uid="{D92C236F-E190-4A24-819B-177CFDB7C15D}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{B3B2B78B-9DED-4B0F-8795-872EEA424CF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8FF1B6-3FAC-4716-95EE-3D4601A243A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E6ABB9-95EA-41F1-AF1C-BC475EE9C731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="2" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4001,23 +4001,23 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="H2">
-            <v>77.62</v>
+          <cell r="I2">
+            <v>70.05</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="H4">
-            <v>203364.40000000002</v>
+          <cell r="I4">
+            <v>301327.69959224999</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="H5">
-            <v>6394</v>
+          <cell r="I5">
+            <v>13874</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="H6">
-            <v>65867</v>
+          <cell r="I6">
+            <v>47398</v>
           </cell>
         </row>
       </sheetData>
@@ -4028,6 +4028,160 @@
 </file>
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="G3">
+            <v>267.60000000000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>114317.33704320001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>4999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="G7">
+            <v>2721</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>72.48</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>46401.463049279999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5"/>
+        </row>
+        <row r="6">
+          <cell r="H6"/>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>26.72</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>31624.244938719999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2113</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>21603</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>75.650000000000006</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>37161.254464999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>733</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>12356</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4067,7 +4221,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4107,7 +4261,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4147,7 +4301,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4187,7 +4341,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4227,7 +4381,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4267,7 +4421,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>153.69</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>210040.29295557001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>9530</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>49182</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4307,7 +4501,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4347,7 +4541,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4387,7 +4581,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4427,47 +4621,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>316.05</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>225076.38231750001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2413</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>41283</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4507,7 +4661,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4547,7 +4701,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4587,7 +4741,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4637,7 +4791,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4677,7 +4831,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4717,47 +4871,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>70.05</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>301327.69959224999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>13874</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>47398</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4797,47 +4911,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>141.83000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>28675.237054880003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>72</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>10544.9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4873,53 +4947,15 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>47.255000000000003</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>118657.30500000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>6415</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>31654</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4961,7 +4997,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4997,7 +5033,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5037,7 +5073,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5077,7 +5113,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5117,7 +5153,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5157,7 +5193,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5197,7 +5233,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5241,7 +5277,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5281,7 +5317,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>141.83000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>28675.237054880003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>10544.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5321,7 +5397,125 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>77.62</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>203364.40000000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>6394</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>65867</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>316.05</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>225076.38231750001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2413</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>41283</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>47.255000000000003</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>118657.30500000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>6415</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>31654</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5361,47 +5555,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>153.69</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>210040.29295557001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>9530</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>49182</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5432,160 +5586,6 @@
         <row r="6">
           <cell r="H6">
             <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="G3">
-            <v>267.60000000000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>114317.33704320001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>4999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="G7">
-            <v>2721</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>72.48</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>46401.463049279999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5"/>
-        </row>
-        <row r="6">
-          <cell r="H6"/>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>26.72</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>31624.244938719999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2113</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>21603</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>75.650000000000006</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>37161.254464999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>733</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>12356</v>
           </cell>
         </row>
       </sheetData>
@@ -13929,15 +13929,15 @@
         <v>23</v>
       </c>
       <c r="E4" s="4">
-        <f>+[1]Main!$H$2</f>
+        <f>+[5]Main!$H$2</f>
         <v>77.62</v>
       </c>
       <c r="F4" s="17">
-        <f>+[1]Main!$H$4*FX!C9</f>
+        <f>+[5]Main!$H$4*FX!C9</f>
         <v>250138.21200000003</v>
       </c>
       <c r="G4" s="17">
-        <f>+([1]Main!$H$6-[1]Main!$H$5)*FX!C9</f>
+        <f>+([5]Main!$H$6-[5]Main!$H$5)*FX!C9</f>
         <v>73151.789999999994</v>
       </c>
       <c r="H4" s="17">
@@ -13968,15 +13968,15 @@
         <v>27</v>
       </c>
       <c r="E5" s="19">
-        <f>+[2]Main!$H$2</f>
+        <f>+[6]Main!$H$2</f>
         <v>316.05</v>
       </c>
       <c r="F5" s="17">
-        <f>+[2]Main!$H$4</f>
+        <f>+[6]Main!$H$4</f>
         <v>225076.38231750001</v>
       </c>
       <c r="G5" s="17">
-        <f>+[2]Main!$H$6-[2]Main!$H$5</f>
+        <f>+[6]Main!$H$6-[6]Main!$H$5</f>
         <v>38870</v>
       </c>
       <c r="H5" s="17">
@@ -14013,15 +14013,15 @@
         <v>31</v>
       </c>
       <c r="E6" s="19">
-        <f>+[3]Main!$I$2</f>
+        <f>+[7]Main!$I$2</f>
         <v>47.255000000000003</v>
       </c>
       <c r="F6" s="17">
-        <f>+[3]Main!$I$4*FX!C3</f>
+        <f>+[7]Main!$I$4*FX!C3</f>
         <v>151881.35040000002</v>
       </c>
       <c r="G6" s="17">
-        <f>+([3]Main!$I$6-[3]Main!$I$5)*FX!C3</f>
+        <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C3</f>
         <v>32305.920000000002</v>
       </c>
       <c r="H6" s="17">
@@ -14048,15 +14048,15 @@
         <v>27</v>
       </c>
       <c r="E7" s="19">
-        <f>+[4]Main!$H$2</f>
+        <f>+[8]Main!$H$2</f>
         <v>68.88</v>
       </c>
       <c r="F7" s="17">
-        <f>+[4]Main!$H$4</f>
+        <f>+[8]Main!$H$4</f>
         <v>89186.882892239984</v>
       </c>
       <c r="G7" s="17">
-        <f>+[4]Main!$H$6-[4]Main!$H$5</f>
+        <f>+[8]Main!$H$6-[8]Main!$H$5</f>
         <v>16063</v>
       </c>
       <c r="H7" s="17">
@@ -14093,15 +14093,15 @@
         <v>27</v>
       </c>
       <c r="E8" s="19">
-        <f>+[5]Main!$H$2</f>
+        <f>+[9]Main!$H$2</f>
         <v>56.28</v>
       </c>
       <c r="F8" s="17">
-        <f>+[5]Main!$H$4</f>
+        <f>+[9]Main!$H$4</f>
         <v>76686.73404000001</v>
       </c>
       <c r="G8" s="17">
-        <f>+[5]Main!$H$6-[5]Main!$H$5</f>
+        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
         <v>-698.54700000000003</v>
       </c>
       <c r="H8" s="17">
@@ -14152,15 +14152,15 @@
         <v>27</v>
       </c>
       <c r="E10" s="19">
-        <f>+[6]Main!$G$3</f>
+        <f>+[10]Main!$G$3</f>
         <v>267.60000000000002</v>
       </c>
       <c r="F10" s="17">
-        <f>+[6]Main!$G$5</f>
+        <f>+[10]Main!$G$5</f>
         <v>114317.33704320001</v>
       </c>
       <c r="G10" s="17">
-        <f>+[6]Main!$G$7-[6]Main!$G$6</f>
+        <f>+[10]Main!$G$7-[10]Main!$G$6</f>
         <v>-2278</v>
       </c>
       <c r="H10" s="17">
@@ -14211,15 +14211,15 @@
         <v>47</v>
       </c>
       <c r="E12" s="19">
-        <f>+[7]Main!$H$2</f>
+        <f>+[11]Main!$H$2</f>
         <v>72.48</v>
       </c>
       <c r="F12" s="17">
-        <f>+[7]Main!$H$4*FX!C8</f>
+        <f>+[11]Main!$H$4*FX!C8</f>
         <v>52897.667876179192</v>
       </c>
       <c r="G12" s="17">
-        <f>+([7]Main!$H$6-[7]Main!$H$5)*FX!C8</f>
+        <f>+([11]Main!$H$6-[11]Main!$H$5)*FX!C8</f>
         <v>0</v>
       </c>
       <c r="H12" s="17">
@@ -14246,15 +14246,15 @@
         <v>27</v>
       </c>
       <c r="E13" s="19">
-        <f>+[8]Main!$H$2</f>
+        <f>+[12]Main!$H$2</f>
         <v>26.72</v>
       </c>
       <c r="F13" s="17">
-        <f>+[8]Main!$H$4</f>
+        <f>+[12]Main!$H$4</f>
         <v>31624.244938719999</v>
       </c>
       <c r="G13" s="17">
-        <f>+[8]Main!$H$6-[8]Main!$H$5</f>
+        <f>+[12]Main!$H$6-[12]Main!$H$5</f>
         <v>19490</v>
       </c>
       <c r="H13" s="17">
@@ -14285,15 +14285,15 @@
         <v>27</v>
       </c>
       <c r="E14" s="19">
-        <f>+[9]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>75.650000000000006</v>
       </c>
       <c r="F14" s="17">
-        <f>+[9]Main!$H$4</f>
+        <f>+[13]Main!$H$4</f>
         <v>37161.254464999998</v>
       </c>
       <c r="G14" s="17">
-        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
+        <f>+[13]Main!$H$6-[13]Main!$H$5</f>
         <v>11623</v>
       </c>
       <c r="H14" s="17">
@@ -14324,15 +14324,15 @@
         <v>27</v>
       </c>
       <c r="E15" s="19">
-        <f>+[10]Main!$J$2</f>
+        <f>+[14]Main!$J$2</f>
         <v>52.07</v>
       </c>
       <c r="F15" s="17">
-        <f>+[10]Main!$J$4</f>
+        <f>+[14]Main!$J$4</f>
         <v>28244.199404300001</v>
       </c>
       <c r="G15" s="17">
-        <f>+[10]Main!$J$6-[10]Main!$J$5</f>
+        <f>+[14]Main!$J$6-[14]Main!$J$5</f>
         <v>13837.7</v>
       </c>
       <c r="H15" s="17">
@@ -14359,15 +14359,15 @@
         <v>27</v>
       </c>
       <c r="E16" s="19">
-        <f>+[11]Main!$J$2</f>
+        <f>+[15]Main!$J$2</f>
         <v>164.97</v>
       </c>
       <c r="F16" s="17">
-        <f>+[11]Main!$J$4</f>
+        <f>+[15]Main!$J$4</f>
         <v>33423.547236300001</v>
       </c>
       <c r="G16" s="17">
-        <f>+[11]Main!$J$6-[11]Main!$J$5</f>
+        <f>+[15]Main!$J$6-[15]Main!$J$5</f>
         <v>4410.2420000000002</v>
       </c>
       <c r="H16" s="17">
@@ -14494,15 +14494,15 @@
         <v>27</v>
       </c>
       <c r="E22" s="19">
-        <f>+[12]Main!$I$2</f>
+        <f>+[16]Main!$I$2</f>
         <v>81.52</v>
       </c>
       <c r="F22" s="17">
-        <f>+[12]Main!$I$4</f>
+        <f>+[16]Main!$I$4</f>
         <v>28099.772318880001</v>
       </c>
       <c r="G22" s="17">
-        <f>+[12]Main!$I$6-[12]Main!$I$5</f>
+        <f>+[16]Main!$I$6-[16]Main!$I$5</f>
         <v>5160</v>
       </c>
       <c r="H22" s="17">
@@ -14599,15 +14599,15 @@
         <v>27</v>
       </c>
       <c r="E26" s="19">
-        <f>+[13]Main!$I$2</f>
+        <f>+[17]Main!$I$2</f>
         <v>51.28</v>
       </c>
       <c r="F26" s="17">
-        <f>+[13]Main!$I$4</f>
+        <f>+[17]Main!$I$4</f>
         <v>24539.198905600002</v>
       </c>
       <c r="G26" s="17">
-        <f>+[13]Main!$I$6-[13]Main!$I$5</f>
+        <f>+[17]Main!$I$6-[17]Main!$I$5</f>
         <v>1450</v>
       </c>
       <c r="H26" s="17">
@@ -14701,15 +14701,15 @@
         <v>27</v>
       </c>
       <c r="E30" s="19">
-        <f>+[14]Main!$J$2</f>
+        <f>+[18]Main!$J$2</f>
         <v>76.930000000000007</v>
       </c>
       <c r="F30" s="17">
-        <f>+[14]Main!$J$4</f>
+        <f>+[18]Main!$J$4</f>
         <v>20629.107760310002</v>
       </c>
       <c r="G30" s="17">
-        <f>+[14]Main!$J$6-[14]Main!$J$5</f>
+        <f>+[18]Main!$J$6-[18]Main!$J$5</f>
         <v>4155.7999999999993</v>
       </c>
       <c r="H30" s="17">
@@ -14740,15 +14740,15 @@
         <v>27</v>
       </c>
       <c r="E31" s="19">
-        <f>+[15]Main!$I$2</f>
+        <f>+[19]Main!$I$2</f>
         <v>192.3</v>
       </c>
       <c r="F31" s="17">
-        <f>+[15]Main!$I$4</f>
+        <f>+[19]Main!$I$4</f>
         <v>22527.326947800004</v>
       </c>
       <c r="G31" s="17">
-        <f>+[15]Main!$I$6-[15]Main!$I$5</f>
+        <f>+[19]Main!$I$6-[19]Main!$I$5</f>
         <v>2179.5999999999995</v>
       </c>
       <c r="H31" s="17">
@@ -14919,15 +14919,15 @@
         <v>27</v>
       </c>
       <c r="E39" s="19">
-        <f>+[16]Main!$I$2</f>
+        <f>+[20]Main!$I$2</f>
         <v>90.6</v>
       </c>
       <c r="F39" s="17">
-        <f>+[16]Main!$I$4</f>
+        <f>+[20]Main!$I$4</f>
         <v>10478.7931914</v>
       </c>
       <c r="G39" s="17">
-        <f>+[16]Main!$I$6-[16]Main!$I$5</f>
+        <f>+[20]Main!$I$6-[20]Main!$I$5</f>
         <v>-289.35000000000002</v>
       </c>
       <c r="H39" s="17">
@@ -14954,15 +14954,15 @@
         <v>27</v>
       </c>
       <c r="E40" s="19">
-        <f>+[17]Main!$J$2</f>
+        <f>+[21]Main!$J$2</f>
         <v>480.97</v>
       </c>
       <c r="F40" s="17">
-        <f>+[17]Main!$J$4</f>
+        <f>+[21]Main!$J$4</f>
         <v>16328.412533369999</v>
       </c>
       <c r="G40" s="17">
-        <f>+[17]Main!$J$6-[17]Main!$J$5</f>
+        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
         <v>4491.2430000000004</v>
       </c>
       <c r="H40" s="17">
@@ -15049,15 +15049,15 @@
         <v>27</v>
       </c>
       <c r="E44" s="19">
-        <f>+[18]Main!$I$2</f>
+        <f>+[22]Main!$I$2</f>
         <v>164.28</v>
       </c>
       <c r="F44" s="17">
-        <f>+[18]Main!$I$4</f>
+        <f>+[22]Main!$I$4</f>
         <v>16076.2140936</v>
       </c>
       <c r="G44" s="17">
-        <f>+[18]Main!$I$6-[18]Main!$I$5</f>
+        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
         <v>-277.411</v>
       </c>
       <c r="H44" s="17">
@@ -15488,15 +15488,15 @@
         <v>172</v>
       </c>
       <c r="E66" s="4">
-        <f>+[19]Main!$J$2</f>
+        <f>+[23]Main!$J$2</f>
         <v>190.5</v>
       </c>
       <c r="F66" s="17">
-        <f>+[19]Main!$J$4*FX!C10</f>
+        <f>+[23]Main!$J$4*FX!C10</f>
         <v>9653.9469578789995</v>
       </c>
       <c r="G66" s="17">
-        <f>+([19]Main!$J$6-[19]Main!$J$5)*FX!C10</f>
+        <f>+([23]Main!$J$6-[23]Main!$J$5)*FX!C10</f>
         <v>185.67080000000001</v>
       </c>
       <c r="H66" s="17">
@@ -15618,15 +15618,15 @@
         <v>27</v>
       </c>
       <c r="E72" s="4">
-        <f>+[20]Main!$J$2</f>
+        <f>+[24]Main!$J$2</f>
         <v>137.83000000000001</v>
       </c>
       <c r="F72" s="17">
-        <f>+[20]Main!$J$4</f>
+        <f>+[24]Main!$J$4</f>
         <v>5880.7446451600008</v>
       </c>
       <c r="G72" s="17">
-        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
+        <f>+[24]Main!$J$6-[24]Main!$J$5</f>
         <v>-65.975999999999999</v>
       </c>
       <c r="H72" s="17">
@@ -16698,15 +16698,15 @@
         <v>31</v>
       </c>
       <c r="E128" s="4">
-        <f>+[21]Main!$I$2</f>
+        <f>+[25]Main!$I$2</f>
         <v>15.7</v>
       </c>
       <c r="F128" s="17">
-        <f>+[21]Main!$I$4*FX!C3</f>
+        <f>+[25]Main!$I$4*FX!C3</f>
         <v>3243.4944</v>
       </c>
       <c r="G128" s="17">
-        <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C3</f>
+        <f>+([25]Main!$I$6-[25]Main!$I$5)*FX!C3</f>
         <v>2300.16</v>
       </c>
       <c r="H128" s="17">
@@ -18156,15 +18156,15 @@
         <v>172</v>
       </c>
       <c r="E203" s="4">
-        <f>+[22]Main!$J$2</f>
+        <f>+[26]Main!$J$2</f>
         <v>70.25</v>
       </c>
       <c r="F203" s="17">
-        <f>+[22]Main!$J$4*FX!C10</f>
+        <f>+[26]Main!$J$4*FX!C10</f>
         <v>772.74349442850007</v>
       </c>
       <c r="G203" s="17">
-        <f>+([22]Main!$J$6-[22]Main!$J$5)*FX!C10</f>
+        <f>+([26]Main!$J$6-[26]Main!$J$5)*FX!C10</f>
         <v>466.023124</v>
       </c>
       <c r="H203" s="17">
@@ -18229,15 +18229,15 @@
         <v>146</v>
       </c>
       <c r="E206" s="4">
-        <f>+[23]Main!$H$2</f>
+        <f>+[27]Main!$H$2</f>
         <v>95.4</v>
       </c>
       <c r="F206" s="17">
-        <f>+[23]Main!$H$4*FX!C8</f>
+        <f>+[27]Main!$H$4*FX!C8</f>
         <v>740.91090808800004</v>
       </c>
       <c r="G206" s="17">
-        <f>+([23]Main!$H$6-[23]Main!$H$5)*FX!C8</f>
+        <f>+([27]Main!$H$6-[27]Main!$H$5)*FX!C8</f>
         <v>-119.44919999999999</v>
       </c>
       <c r="H206" s="17">
@@ -19225,15 +19225,15 @@
         <v>924</v>
       </c>
       <c r="E259" s="4">
-        <f>+[24]Main!$J$2</f>
+        <f>+[28]Main!$J$2</f>
         <v>58.4</v>
       </c>
       <c r="F259" s="17">
-        <f>+[24]Main!$J$4*FX!C10</f>
+        <f>+[28]Main!$J$4*FX!C10</f>
         <v>501.81546996000003</v>
       </c>
       <c r="G259" s="17">
-        <f>+([24]Main!$J$6-[24]Main!$J$5)*FX!C10</f>
+        <f>+([28]Main!$J$6-[28]Main!$J$5)*FX!C10</f>
         <v>12.976179999999999</v>
       </c>
       <c r="H259" s="17">
@@ -20825,15 +20825,15 @@
         <v>924</v>
       </c>
       <c r="E348" s="4">
-        <f>+[25]Main!$I$2</f>
+        <f>+[29]Main!$I$2</f>
         <v>85</v>
       </c>
       <c r="F348" s="17">
-        <f>+[25]Main!$I$4*FX!C10</f>
+        <f>+[29]Main!$I$4*FX!C10</f>
         <v>302.45397000000003</v>
       </c>
       <c r="G348" s="17">
-        <f>+([25]Main!$I$6-[25]Main!$I$5)*FX!C10</f>
+        <f>+([29]Main!$I$6-[29]Main!$I$5)*FX!C10</f>
         <v>86.644348000000022</v>
       </c>
       <c r="H348" s="17">
@@ -21352,15 +21352,15 @@
         <v>27</v>
       </c>
       <c r="E4" s="4">
-        <f>+[26]Main!$I$2</f>
+        <f>+[1]Main!$I$2</f>
         <v>70.05</v>
       </c>
       <c r="F4" s="17">
-        <f>+[26]Main!$I$4</f>
+        <f>+[1]Main!$I$4</f>
         <v>301327.69959224999</v>
       </c>
       <c r="G4" s="17">
-        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
+        <f>+[1]Main!$I$6-[1]Main!$I$5</f>
         <v>33524</v>
       </c>
       <c r="H4" s="17">
@@ -21574,15 +21574,15 @@
         <v>27</v>
       </c>
       <c r="E6" s="4">
-        <f>+[40]Main!$I$2</f>
+        <f>+[2]Main!$I$2</f>
         <v>153.69</v>
       </c>
       <c r="F6" s="17">
-        <f>+[40]Main!$I$4</f>
+        <f>+[2]Main!$I$4</f>
         <v>210040.29295557001</v>
       </c>
       <c r="G6" s="17">
-        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
+        <f>+[2]Main!$I$6-[2]Main!$I$5</f>
         <v>39652</v>
       </c>
       <c r="H6" s="17">
@@ -21899,15 +21899,15 @@
         <v>27</v>
       </c>
       <c r="E9" s="4">
-        <f>+[27]Main!$J$2</f>
+        <f>+[3]Main!$J$2</f>
         <v>87.85</v>
       </c>
       <c r="F9" s="17">
-        <f>+[27]Main!$J$4</f>
+        <f>+[3]Main!$J$4</f>
         <v>99859.095000000001</v>
       </c>
       <c r="G9" s="17">
-        <f>+[27]Main!$J$6-[27]Main!$J$5</f>
+        <f>+[3]Main!$J$6-[3]Main!$J$5</f>
         <v>12813.199999999997</v>
       </c>
       <c r="H9" s="17">
@@ -22636,15 +22636,15 @@
         <v>27</v>
       </c>
       <c r="E16" s="4">
-        <f>+[28]Main!$I$2</f>
+        <f>+[4]Main!$I$2</f>
         <v>141.83000000000001</v>
       </c>
       <c r="F16" s="17">
-        <f>+[28]Main!$I$4</f>
+        <f>+[4]Main!$I$4</f>
         <v>28675.237054880003</v>
       </c>
       <c r="G16" s="17">
-        <f>+[28]Main!$I$6-[28]Main!$I$5</f>
+        <f>+[4]Main!$I$6-[4]Main!$I$5</f>
         <v>10472.9</v>
       </c>
       <c r="H16" s="17">
@@ -33863,15 +33863,15 @@
         <v>27</v>
       </c>
       <c r="E5" s="31">
-        <f>+[29]Main!$K$3</f>
+        <f>+[30]Main!$K$3</f>
         <v>182.31</v>
       </c>
       <c r="F5" s="17">
-        <f>+[29]Main!$K$5</f>
+        <f>+[30]Main!$K$5</f>
         <v>283798.25404749002</v>
       </c>
       <c r="G5" s="17">
-        <f>+[29]Main!$K$7-[29]Main!$K$6</f>
+        <f>+[30]Main!$K$7-[30]Main!$K$6</f>
         <v>43963</v>
       </c>
       <c r="H5" s="17">
@@ -33976,15 +33976,15 @@
         <v>27</v>
       </c>
       <c r="E6" s="31">
-        <f>+[30]Main!$M$3</f>
+        <f>+[31]Main!$M$3</f>
         <v>66.25</v>
       </c>
       <c r="F6" s="17">
-        <f>+[30]Main!$M$5</f>
+        <f>+[31]Main!$M$5</f>
         <v>111498.75</v>
       </c>
       <c r="G6" s="17">
-        <f>+[30]Main!$M$7-[30]Main!$M$6</f>
+        <f>+[31]Main!$M$7-[31]Main!$M$6</f>
         <v>21235</v>
       </c>
       <c r="H6" s="17">
@@ -34089,15 +34089,15 @@
         <v>31</v>
       </c>
       <c r="E7" s="31">
-        <f>+[31]Main!$H$2</f>
+        <f>+[32]Main!$H$2</f>
         <v>60.8</v>
       </c>
       <c r="F7" s="17">
-        <f>+[31]Main!$H$5*FX!C3</f>
+        <f>+[32]Main!$H$5*FX!C3</f>
         <v>122499.9936</v>
       </c>
       <c r="G7" s="17">
-        <f>+([30]Main!$M$7-[30]Main!$M$6)*FX!C3</f>
+        <f>+([31]Main!$M$7-[31]Main!$M$6)*FX!C3</f>
         <v>27180.799999999999</v>
       </c>
       <c r="H7" s="17">
@@ -34199,15 +34199,15 @@
         <v>40</v>
       </c>
       <c r="E8" s="31">
-        <f>+[32]Main!$H$2</f>
+        <f>+[33]Main!$H$2</f>
         <v>485.4</v>
       </c>
       <c r="F8" s="17">
-        <f>+[32]Main!$H$4*FX!C4</f>
+        <f>+[33]Main!$H$4*FX!C4</f>
         <v>72888.393927045603</v>
       </c>
       <c r="G8" s="17">
-        <f>+([32]Main!$H$6-[32]Main!$H$5)*FX!C4</f>
+        <f>+([33]Main!$H$6-[33]Main!$H$5)*FX!C4</f>
         <v>-228.87708000000006</v>
       </c>
       <c r="H8" s="17">
@@ -34300,15 +34300,15 @@
         <v>95</v>
       </c>
       <c r="E9" s="17">
-        <f>+[33]Main!$J$2</f>
+        <f>+[34]Main!$J$2</f>
         <v>5714</v>
       </c>
       <c r="F9" s="17">
-        <f>+[33]Main!$J$4*FX!C5</f>
+        <f>+[34]Main!$J$4*FX!C5</f>
         <v>68983.677500799997</v>
       </c>
       <c r="G9" s="17">
-        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C5</f>
+        <f>+([34]Main!$J$6-[34]Main!$J$5)*FX!C5</f>
         <v>2758.2091999999998</v>
       </c>
       <c r="H9" s="17">
@@ -34406,15 +34406,15 @@
         <v>31</v>
       </c>
       <c r="E10" s="31">
-        <f>+[34]Main!$I$2</f>
+        <f>+[35]Main!$I$2</f>
         <v>32.61</v>
       </c>
       <c r="F10" s="17">
-        <f>+([34]Main!$I$4)*FX!C3</f>
+        <f>+([35]Main!$I$4)*FX!C3</f>
         <v>34427.811840000002</v>
       </c>
       <c r="G10" s="17">
-        <f>+([34]Main!$I$6-[34]Main!$I$5)*FX!C3</f>
+        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C3</f>
         <v>10438.4</v>
       </c>
       <c r="H10" s="17">
@@ -34507,15 +34507,15 @@
         <v>617</v>
       </c>
       <c r="E11" s="17">
-        <f>+[35]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>107400</v>
       </c>
       <c r="F11" s="17">
-        <f>+[35]Main!$I$4*FX!C6</f>
+        <f>+[36]Main!$I$4*FX!C6</f>
         <v>9270.9964935000007</v>
       </c>
       <c r="G11" s="17">
-        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C6</f>
+        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C6</f>
         <v>-575.42399999999998</v>
       </c>
       <c r="H11" s="17">
@@ -34606,15 +34606,15 @@
         <v>240</v>
       </c>
       <c r="E12" s="17">
-        <f>+[36]Main!$I$2</f>
+        <f>+[37]Main!$I$2</f>
         <v>590</v>
       </c>
       <c r="F12" s="17">
-        <f>+[36]Main!$I$4*FX!C7</f>
+        <f>+[37]Main!$I$4*FX!C7</f>
         <v>4254.915253002001</v>
       </c>
       <c r="G12" s="17">
-        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C7</f>
+        <f>+([37]Main!$I$6-[37]Main!$I$5)*FX!C7</f>
         <v>-162.340056</v>
       </c>
       <c r="H12" s="17">
@@ -35033,15 +35033,15 @@
         <v>527</v>
       </c>
       <c r="E17" s="31">
-        <f>+[37]Main!$J$2</f>
+        <f>+[38]Main!$J$2</f>
         <v>66.2</v>
       </c>
       <c r="F17" s="17">
-        <f>+[37]Main!$J$4*FX!C11</f>
+        <f>+[38]Main!$J$4*FX!C11</f>
         <v>834.02467200000001</v>
       </c>
       <c r="G17" s="17">
-        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C11</f>
+        <f>+([38]Main!$J$6-[38]Main!$J$5)*FX!C11</f>
         <v>781.26400000000012</v>
       </c>
       <c r="H17" s="17">
@@ -35213,15 +35213,15 @@
         <v>27</v>
       </c>
       <c r="E19" s="31">
-        <f>+[38]Main!$I$3</f>
+        <f>+[39]Main!$I$3</f>
         <v>69.63</v>
       </c>
       <c r="F19" s="17">
-        <f>+[38]Main!$I$5</f>
+        <f>+[39]Main!$I$5</f>
         <v>1232.2425974099999</v>
       </c>
       <c r="G19" s="17">
-        <f>+[38]Main!$I$7-[38]Main!$I$6</f>
+        <f>+[39]Main!$I$7-[39]Main!$I$6</f>
         <v>214.72500000000002</v>
       </c>
       <c r="H19" s="17">
@@ -35312,15 +35312,15 @@
         <v>27</v>
       </c>
       <c r="E20" s="31">
-        <f>+[39]Main!$I$2</f>
+        <f>+[40]Main!$I$2</f>
         <v>4.3600000000000003</v>
       </c>
       <c r="F20" s="17">
-        <f>+[39]Main!$I$4</f>
+        <f>+[40]Main!$I$4</f>
         <v>248.91663792000003</v>
       </c>
       <c r="G20" s="17">
-        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
+        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
         <v>-34.395385999999995</v>
       </c>
       <c r="H20" s="17">

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E6ABB9-95EA-41F1-AF1C-BC475EE9C731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4797C565-7395-48A1-B40B-616FBA0F0929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="1176">
   <si>
     <t>Consumer Goods</t>
   </si>
@@ -3666,6 +3666,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -3951,10 +3954,10 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3963,10 +3966,10 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -3997,27 +4000,111 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="K3">
+            <v>192</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>299243.29843199998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>5450</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>49501</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>90.75</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1757.6037105</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>192.43899999999999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>293.88499999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>70.05</v>
+            <v>4.3600000000000003</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>301327.69959224999</v>
+            <v>248.91663792000003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>13874</v>
+            <v>34.395385999999995</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>47398</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -4027,7 +4114,205 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>77.62</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>203364.40000000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>6394</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>65867</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>316.05</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>225076.38231750001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2413</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>41283</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>47.255000000000003</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>118657.30500000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>6415</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>31654</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>68.88</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>89186.882892239984</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>1561</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>17624</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>56.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>76686.73404000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>698.54700000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4067,7 +4352,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4101,7 +4386,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4141,7 +4426,49 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="M3">
+            <v>66.25</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="M5">
+            <v>111498.75</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="M6">
+            <v>4474</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="M7">
+            <v>25709</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4181,7 +4508,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4221,7 +4548,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4261,7 +4588,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4301,7 +4628,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4341,7 +4668,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4381,7 +4708,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4421,47 +4748,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>153.69</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>210040.29295557001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>9530</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>49182</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4501,7 +4788,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4541,7 +4828,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4581,7 +4868,43 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Products"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>60.8</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>95703.12</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4621,7 +4944,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4661,7 +4984,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4701,7 +5024,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4741,7 +5064,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4791,7 +5114,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4831,7 +5154,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4871,7 +5194,87 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>70.05</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>301327.69959224999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>13874</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>47398</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>153.69</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>210040.29295557001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>9530</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>49182</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4911,129 +5314,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="K3">
-            <v>182.31</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>283798.25404749002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>4872</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="K7">
-            <v>48835</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="M3">
-            <v>66.25</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="M5">
-            <v>111498.75</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="M6">
-            <v>4474</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="M7">
-            <v>25709</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Products"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>60.8</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>95703.12</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5073,7 +5354,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>141.83000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>28675.237054880003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>10544.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5113,7 +5434,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5153,7 +5474,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5193,7 +5514,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5233,7 +5554,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5272,324 +5593,6 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>69.63</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1232.2425974099999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>33.557000000000002</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>248.28200000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>141.83000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>28675.237054880003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>72</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>10544.9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4.3600000000000003</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>248.91663792000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>34.395385999999995</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>77.62</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>203364.40000000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>6394</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>65867</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>316.05</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>225076.38231750001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2413</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>41283</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>47.255000000000003</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>118657.30500000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>6415</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>31654</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>68.88</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>89186.882892239984</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>1561</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>17624</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>56.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>76686.73404000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>698.54700000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -13929,15 +13932,15 @@
         <v>23</v>
       </c>
       <c r="E4" s="4">
-        <f>+[5]Main!$H$2</f>
+        <f>+[12]Main!$H$2</f>
         <v>77.62</v>
       </c>
       <c r="F4" s="17">
-        <f>+[5]Main!$H$4*FX!C9</f>
+        <f>+[12]Main!$H$4*FX!C9</f>
         <v>250138.21200000003</v>
       </c>
       <c r="G4" s="17">
-        <f>+([5]Main!$H$6-[5]Main!$H$5)*FX!C9</f>
+        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C9</f>
         <v>73151.789999999994</v>
       </c>
       <c r="H4" s="17">
@@ -13968,15 +13971,15 @@
         <v>27</v>
       </c>
       <c r="E5" s="19">
-        <f>+[6]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>316.05</v>
       </c>
       <c r="F5" s="17">
-        <f>+[6]Main!$H$4</f>
+        <f>+[13]Main!$H$4</f>
         <v>225076.38231750001</v>
       </c>
       <c r="G5" s="17">
-        <f>+[6]Main!$H$6-[6]Main!$H$5</f>
+        <f>+[13]Main!$H$6-[13]Main!$H$5</f>
         <v>38870</v>
       </c>
       <c r="H5" s="17">
@@ -14013,15 +14016,15 @@
         <v>31</v>
       </c>
       <c r="E6" s="19">
-        <f>+[7]Main!$I$2</f>
+        <f>+[14]Main!$I$2</f>
         <v>47.255000000000003</v>
       </c>
       <c r="F6" s="17">
-        <f>+[7]Main!$I$4*FX!C3</f>
+        <f>+[14]Main!$I$4*FX!C3</f>
         <v>151881.35040000002</v>
       </c>
       <c r="G6" s="17">
-        <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C3</f>
+        <f>+([14]Main!$I$6-[14]Main!$I$5)*FX!C3</f>
         <v>32305.920000000002</v>
       </c>
       <c r="H6" s="17">
@@ -14048,15 +14051,15 @@
         <v>27</v>
       </c>
       <c r="E7" s="19">
-        <f>+[8]Main!$H$2</f>
+        <f>+[15]Main!$H$2</f>
         <v>68.88</v>
       </c>
       <c r="F7" s="17">
-        <f>+[8]Main!$H$4</f>
+        <f>+[15]Main!$H$4</f>
         <v>89186.882892239984</v>
       </c>
       <c r="G7" s="17">
-        <f>+[8]Main!$H$6-[8]Main!$H$5</f>
+        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
         <v>16063</v>
       </c>
       <c r="H7" s="17">
@@ -14093,15 +14096,15 @@
         <v>27</v>
       </c>
       <c r="E8" s="19">
-        <f>+[9]Main!$H$2</f>
+        <f>+[16]Main!$H$2</f>
         <v>56.28</v>
       </c>
       <c r="F8" s="17">
-        <f>+[9]Main!$H$4</f>
+        <f>+[16]Main!$H$4</f>
         <v>76686.73404000001</v>
       </c>
       <c r="G8" s="17">
-        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
+        <f>+[16]Main!$H$6-[16]Main!$H$5</f>
         <v>-698.54700000000003</v>
       </c>
       <c r="H8" s="17">
@@ -14152,15 +14155,15 @@
         <v>27</v>
       </c>
       <c r="E10" s="19">
-        <f>+[10]Main!$G$3</f>
+        <f>+[17]Main!$G$3</f>
         <v>267.60000000000002</v>
       </c>
       <c r="F10" s="17">
-        <f>+[10]Main!$G$5</f>
+        <f>+[17]Main!$G$5</f>
         <v>114317.33704320001</v>
       </c>
       <c r="G10" s="17">
-        <f>+[10]Main!$G$7-[10]Main!$G$6</f>
+        <f>+[17]Main!$G$7-[17]Main!$G$6</f>
         <v>-2278</v>
       </c>
       <c r="H10" s="17">
@@ -14211,15 +14214,15 @@
         <v>47</v>
       </c>
       <c r="E12" s="19">
-        <f>+[11]Main!$H$2</f>
+        <f>+[18]Main!$H$2</f>
         <v>72.48</v>
       </c>
       <c r="F12" s="17">
-        <f>+[11]Main!$H$4*FX!C8</f>
+        <f>+[18]Main!$H$4*FX!C8</f>
         <v>52897.667876179192</v>
       </c>
       <c r="G12" s="17">
-        <f>+([11]Main!$H$6-[11]Main!$H$5)*FX!C8</f>
+        <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C8</f>
         <v>0</v>
       </c>
       <c r="H12" s="17">
@@ -14246,15 +14249,15 @@
         <v>27</v>
       </c>
       <c r="E13" s="19">
-        <f>+[12]Main!$H$2</f>
+        <f>+[19]Main!$H$2</f>
         <v>26.72</v>
       </c>
       <c r="F13" s="17">
-        <f>+[12]Main!$H$4</f>
+        <f>+[19]Main!$H$4</f>
         <v>31624.244938719999</v>
       </c>
       <c r="G13" s="17">
-        <f>+[12]Main!$H$6-[12]Main!$H$5</f>
+        <f>+[19]Main!$H$6-[19]Main!$H$5</f>
         <v>19490</v>
       </c>
       <c r="H13" s="17">
@@ -14285,15 +14288,15 @@
         <v>27</v>
       </c>
       <c r="E14" s="19">
-        <f>+[13]Main!$H$2</f>
+        <f>+[20]Main!$H$2</f>
         <v>75.650000000000006</v>
       </c>
       <c r="F14" s="17">
-        <f>+[13]Main!$H$4</f>
+        <f>+[20]Main!$H$4</f>
         <v>37161.254464999998</v>
       </c>
       <c r="G14" s="17">
-        <f>+[13]Main!$H$6-[13]Main!$H$5</f>
+        <f>+[20]Main!$H$6-[20]Main!$H$5</f>
         <v>11623</v>
       </c>
       <c r="H14" s="17">
@@ -14324,15 +14327,15 @@
         <v>27</v>
       </c>
       <c r="E15" s="19">
-        <f>+[14]Main!$J$2</f>
+        <f>+[21]Main!$J$2</f>
         <v>52.07</v>
       </c>
       <c r="F15" s="17">
-        <f>+[14]Main!$J$4</f>
+        <f>+[21]Main!$J$4</f>
         <v>28244.199404300001</v>
       </c>
       <c r="G15" s="17">
-        <f>+[14]Main!$J$6-[14]Main!$J$5</f>
+        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
         <v>13837.7</v>
       </c>
       <c r="H15" s="17">
@@ -14359,15 +14362,15 @@
         <v>27</v>
       </c>
       <c r="E16" s="19">
-        <f>+[15]Main!$J$2</f>
+        <f>+[22]Main!$J$2</f>
         <v>164.97</v>
       </c>
       <c r="F16" s="17">
-        <f>+[15]Main!$J$4</f>
+        <f>+[22]Main!$J$4</f>
         <v>33423.547236300001</v>
       </c>
       <c r="G16" s="17">
-        <f>+[15]Main!$J$6-[15]Main!$J$5</f>
+        <f>+[22]Main!$J$6-[22]Main!$J$5</f>
         <v>4410.2420000000002</v>
       </c>
       <c r="H16" s="17">
@@ -14494,15 +14497,15 @@
         <v>27</v>
       </c>
       <c r="E22" s="19">
-        <f>+[16]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>81.52</v>
       </c>
       <c r="F22" s="17">
-        <f>+[16]Main!$I$4</f>
+        <f>+[23]Main!$I$4</f>
         <v>28099.772318880001</v>
       </c>
       <c r="G22" s="17">
-        <f>+[16]Main!$I$6-[16]Main!$I$5</f>
+        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
         <v>5160</v>
       </c>
       <c r="H22" s="17">
@@ -14599,15 +14602,15 @@
         <v>27</v>
       </c>
       <c r="E26" s="19">
-        <f>+[17]Main!$I$2</f>
+        <f>+[24]Main!$I$2</f>
         <v>51.28</v>
       </c>
       <c r="F26" s="17">
-        <f>+[17]Main!$I$4</f>
+        <f>+[24]Main!$I$4</f>
         <v>24539.198905600002</v>
       </c>
       <c r="G26" s="17">
-        <f>+[17]Main!$I$6-[17]Main!$I$5</f>
+        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
         <v>1450</v>
       </c>
       <c r="H26" s="17">
@@ -14701,15 +14704,15 @@
         <v>27</v>
       </c>
       <c r="E30" s="19">
-        <f>+[18]Main!$J$2</f>
+        <f>+[25]Main!$J$2</f>
         <v>76.930000000000007</v>
       </c>
       <c r="F30" s="17">
-        <f>+[18]Main!$J$4</f>
+        <f>+[25]Main!$J$4</f>
         <v>20629.107760310002</v>
       </c>
       <c r="G30" s="17">
-        <f>+[18]Main!$J$6-[18]Main!$J$5</f>
+        <f>+[25]Main!$J$6-[25]Main!$J$5</f>
         <v>4155.7999999999993</v>
       </c>
       <c r="H30" s="17">
@@ -14740,15 +14743,15 @@
         <v>27</v>
       </c>
       <c r="E31" s="19">
-        <f>+[19]Main!$I$2</f>
+        <f>+[26]Main!$I$2</f>
         <v>192.3</v>
       </c>
       <c r="F31" s="17">
-        <f>+[19]Main!$I$4</f>
+        <f>+[26]Main!$I$4</f>
         <v>22527.326947800004</v>
       </c>
       <c r="G31" s="17">
-        <f>+[19]Main!$I$6-[19]Main!$I$5</f>
+        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
         <v>2179.5999999999995</v>
       </c>
       <c r="H31" s="17">
@@ -14919,15 +14922,15 @@
         <v>27</v>
       </c>
       <c r="E39" s="19">
-        <f>+[20]Main!$I$2</f>
+        <f>+[27]Main!$I$2</f>
         <v>90.6</v>
       </c>
       <c r="F39" s="17">
-        <f>+[20]Main!$I$4</f>
+        <f>+[27]Main!$I$4</f>
         <v>10478.7931914</v>
       </c>
       <c r="G39" s="17">
-        <f>+[20]Main!$I$6-[20]Main!$I$5</f>
+        <f>+[27]Main!$I$6-[27]Main!$I$5</f>
         <v>-289.35000000000002</v>
       </c>
       <c r="H39" s="17">
@@ -14954,15 +14957,15 @@
         <v>27</v>
       </c>
       <c r="E40" s="19">
-        <f>+[21]Main!$J$2</f>
+        <f>+[28]Main!$J$2</f>
         <v>480.97</v>
       </c>
       <c r="F40" s="17">
-        <f>+[21]Main!$J$4</f>
+        <f>+[28]Main!$J$4</f>
         <v>16328.412533369999</v>
       </c>
       <c r="G40" s="17">
-        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
+        <f>+[28]Main!$J$6-[28]Main!$J$5</f>
         <v>4491.2430000000004</v>
       </c>
       <c r="H40" s="17">
@@ -15049,15 +15052,15 @@
         <v>27</v>
       </c>
       <c r="E44" s="19">
-        <f>+[22]Main!$I$2</f>
+        <f>+[29]Main!$I$2</f>
         <v>164.28</v>
       </c>
       <c r="F44" s="17">
-        <f>+[22]Main!$I$4</f>
+        <f>+[29]Main!$I$4</f>
         <v>16076.2140936</v>
       </c>
       <c r="G44" s="17">
-        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
+        <f>+[29]Main!$I$6-[29]Main!$I$5</f>
         <v>-277.411</v>
       </c>
       <c r="H44" s="17">
@@ -15488,15 +15491,15 @@
         <v>172</v>
       </c>
       <c r="E66" s="4">
-        <f>+[23]Main!$J$2</f>
+        <f>+[30]Main!$J$2</f>
         <v>190.5</v>
       </c>
       <c r="F66" s="17">
-        <f>+[23]Main!$J$4*FX!C10</f>
+        <f>+[30]Main!$J$4*FX!C10</f>
         <v>9653.9469578789995</v>
       </c>
       <c r="G66" s="17">
-        <f>+([23]Main!$J$6-[23]Main!$J$5)*FX!C10</f>
+        <f>+([30]Main!$J$6-[30]Main!$J$5)*FX!C10</f>
         <v>185.67080000000001</v>
       </c>
       <c r="H66" s="17">
@@ -15618,15 +15621,15 @@
         <v>27</v>
       </c>
       <c r="E72" s="4">
-        <f>+[24]Main!$J$2</f>
+        <f>+[31]Main!$J$2</f>
         <v>137.83000000000001</v>
       </c>
       <c r="F72" s="17">
-        <f>+[24]Main!$J$4</f>
+        <f>+[31]Main!$J$4</f>
         <v>5880.7446451600008</v>
       </c>
       <c r="G72" s="17">
-        <f>+[24]Main!$J$6-[24]Main!$J$5</f>
+        <f>+[31]Main!$J$6-[31]Main!$J$5</f>
         <v>-65.975999999999999</v>
       </c>
       <c r="H72" s="17">
@@ -16698,15 +16701,15 @@
         <v>31</v>
       </c>
       <c r="E128" s="4">
-        <f>+[25]Main!$I$2</f>
+        <f>+[32]Main!$I$2</f>
         <v>15.7</v>
       </c>
       <c r="F128" s="17">
-        <f>+[25]Main!$I$4*FX!C3</f>
+        <f>+[32]Main!$I$4*FX!C3</f>
         <v>3243.4944</v>
       </c>
       <c r="G128" s="17">
-        <f>+([25]Main!$I$6-[25]Main!$I$5)*FX!C3</f>
+        <f>+([32]Main!$I$6-[32]Main!$I$5)*FX!C3</f>
         <v>2300.16</v>
       </c>
       <c r="H128" s="17">
@@ -18156,15 +18159,15 @@
         <v>172</v>
       </c>
       <c r="E203" s="4">
-        <f>+[26]Main!$J$2</f>
+        <f>+[33]Main!$J$2</f>
         <v>70.25</v>
       </c>
       <c r="F203" s="17">
-        <f>+[26]Main!$J$4*FX!C10</f>
+        <f>+[33]Main!$J$4*FX!C10</f>
         <v>772.74349442850007</v>
       </c>
       <c r="G203" s="17">
-        <f>+([26]Main!$J$6-[26]Main!$J$5)*FX!C10</f>
+        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C10</f>
         <v>466.023124</v>
       </c>
       <c r="H203" s="17">
@@ -18229,22 +18232,22 @@
         <v>146</v>
       </c>
       <c r="E206" s="4">
-        <f>+[27]Main!$H$2</f>
+        <f>+[34]Main!$H$2</f>
         <v>95.4</v>
       </c>
       <c r="F206" s="17">
-        <f>+[27]Main!$H$4*FX!C8</f>
+        <f>+[34]Main!$H$4*FX!C8</f>
         <v>740.91090808800004</v>
       </c>
       <c r="G206" s="17">
-        <f>+([27]Main!$H$6-[27]Main!$H$5)*FX!C8</f>
+        <f>+([34]Main!$H$6-[34]Main!$H$5)*FX!C8</f>
         <v>-119.44919999999999</v>
       </c>
       <c r="H206" s="17">
         <f>+F206+G206</f>
         <v>621.46170808800002</v>
       </c>
-      <c r="I206" s="40" t="s">
+      <c r="I206" s="39" t="s">
         <v>1174</v>
       </c>
       <c r="J206" s="22">
@@ -19225,15 +19228,15 @@
         <v>924</v>
       </c>
       <c r="E259" s="4">
-        <f>+[28]Main!$J$2</f>
+        <f>+[35]Main!$J$2</f>
         <v>58.4</v>
       </c>
       <c r="F259" s="17">
-        <f>+[28]Main!$J$4*FX!C10</f>
+        <f>+[35]Main!$J$4*FX!C10</f>
         <v>501.81546996000003</v>
       </c>
       <c r="G259" s="17">
-        <f>+([28]Main!$J$6-[28]Main!$J$5)*FX!C10</f>
+        <f>+([35]Main!$J$6-[35]Main!$J$5)*FX!C10</f>
         <v>12.976179999999999</v>
       </c>
       <c r="H259" s="17">
@@ -20825,15 +20828,15 @@
         <v>924</v>
       </c>
       <c r="E348" s="4">
-        <f>+[29]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>85</v>
       </c>
       <c r="F348" s="17">
-        <f>+[29]Main!$I$4*FX!C10</f>
+        <f>+[36]Main!$I$4*FX!C10</f>
         <v>302.45397000000003</v>
       </c>
       <c r="G348" s="17">
-        <f>+([29]Main!$I$6-[29]Main!$I$5)*FX!C10</f>
+        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C10</f>
         <v>86.644348000000022</v>
       </c>
       <c r="H348" s="17">
@@ -21352,15 +21355,15 @@
         <v>27</v>
       </c>
       <c r="E4" s="4">
-        <f>+[1]Main!$I$2</f>
+        <f>+[37]Main!$I$2</f>
         <v>70.05</v>
       </c>
       <c r="F4" s="17">
-        <f>+[1]Main!$I$4</f>
+        <f>+[37]Main!$I$4</f>
         <v>301327.69959224999</v>
       </c>
       <c r="G4" s="17">
-        <f>+[1]Main!$I$6-[1]Main!$I$5</f>
+        <f>+[37]Main!$I$6-[37]Main!$I$5</f>
         <v>33524</v>
       </c>
       <c r="H4" s="17">
@@ -21574,22 +21577,22 @@
         <v>27</v>
       </c>
       <c r="E6" s="4">
-        <f>+[2]Main!$I$2</f>
+        <f>+[38]Main!$I$2</f>
         <v>153.69</v>
       </c>
       <c r="F6" s="17">
-        <f>+[2]Main!$I$4</f>
+        <f>+[38]Main!$I$4</f>
         <v>210040.29295557001</v>
       </c>
       <c r="G6" s="17">
-        <f>+[2]Main!$I$6-[2]Main!$I$5</f>
+        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
         <v>39652</v>
       </c>
       <c r="H6" s="17">
         <f>+F6+G6</f>
         <v>249692.29295557001</v>
       </c>
-      <c r="I6" s="44" t="s">
+      <c r="I6" s="43" t="s">
         <v>1174</v>
       </c>
       <c r="J6" s="4"/>
@@ -21899,15 +21902,15 @@
         <v>27</v>
       </c>
       <c r="E9" s="4">
-        <f>+[3]Main!$J$2</f>
+        <f>+[39]Main!$J$2</f>
         <v>87.85</v>
       </c>
       <c r="F9" s="17">
-        <f>+[3]Main!$J$4</f>
+        <f>+[39]Main!$J$4</f>
         <v>99859.095000000001</v>
       </c>
       <c r="G9" s="17">
-        <f>+[3]Main!$J$6-[3]Main!$J$5</f>
+        <f>+[39]Main!$J$6-[39]Main!$J$5</f>
         <v>12813.199999999997</v>
       </c>
       <c r="H9" s="17">
@@ -22636,15 +22639,15 @@
         <v>27</v>
       </c>
       <c r="E16" s="4">
-        <f>+[4]Main!$I$2</f>
+        <f>+[40]Main!$I$2</f>
         <v>141.83000000000001</v>
       </c>
       <c r="F16" s="17">
-        <f>+[4]Main!$I$4</f>
+        <f>+[40]Main!$I$4</f>
         <v>28675.237054880003</v>
       </c>
       <c r="G16" s="17">
-        <f>+[4]Main!$I$6-[4]Main!$I$5</f>
+        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
         <v>10472.9</v>
       </c>
       <c r="H16" s="17">
@@ -33770,15 +33773,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>718429.85656916746</v>
+        <v>734400.26206676755</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>105570.36167799999</v>
+        <v>105545.08267799998</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>815508.33824716776</v>
+        <v>831453.46474476776</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33863,27 +33866,25 @@
         <v>27</v>
       </c>
       <c r="E5" s="31">
-        <f>+[30]Main!$K$3</f>
-        <v>182.31</v>
+        <f>+[1]Main!$K$3</f>
+        <v>192</v>
       </c>
       <c r="F5" s="17">
-        <f>+[30]Main!$K$5</f>
-        <v>283798.25404749002</v>
+        <f>+[1]Main!$K$5</f>
+        <v>299243.29843199998</v>
       </c>
       <c r="G5" s="17">
-        <f>+[30]Main!$K$7-[30]Main!$K$6</f>
-        <v>43963</v>
+        <f>+[1]Main!$K$7-[1]Main!$K$6</f>
+        <v>44051</v>
       </c>
       <c r="H5" s="17">
         <f>+F5+G5</f>
-        <v>327761.25404749002</v>
-      </c>
-      <c r="I5" s="38" t="s">
-        <v>1174</v>
-      </c>
-      <c r="J5" s="22">
-        <v>46134</v>
-      </c>
+        <v>343294.29843199998</v>
+      </c>
+      <c r="I5" s="44" t="s">
+        <v>1175</v>
+      </c>
+      <c r="J5" s="22"/>
       <c r="K5" s="31">
         <v>35174</v>
       </c>
@@ -33976,22 +33977,22 @@
         <v>27</v>
       </c>
       <c r="E6" s="31">
-        <f>+[31]Main!$M$3</f>
+        <f>+[2]Main!$M$3</f>
         <v>66.25</v>
       </c>
       <c r="F6" s="17">
-        <f>+[31]Main!$M$5</f>
+        <f>+[2]Main!$M$5</f>
         <v>111498.75</v>
       </c>
       <c r="G6" s="17">
-        <f>+[31]Main!$M$7-[31]Main!$M$6</f>
+        <f>+[2]Main!$M$7-[2]Main!$M$6</f>
         <v>21235</v>
       </c>
       <c r="H6" s="17">
         <f>+F6+G6</f>
         <v>132733.75</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="42" t="s">
         <v>1174</v>
       </c>
       <c r="J6" s="22">
@@ -34089,22 +34090,22 @@
         <v>31</v>
       </c>
       <c r="E7" s="31">
-        <f>+[32]Main!$H$2</f>
+        <f>+[3]Main!$H$2</f>
         <v>60.8</v>
       </c>
       <c r="F7" s="17">
-        <f>+[32]Main!$H$5*FX!C3</f>
+        <f>+[3]Main!$H$5*FX!C3</f>
         <v>122499.9936</v>
       </c>
       <c r="G7" s="17">
-        <f>+([31]Main!$M$7-[31]Main!$M$6)*FX!C3</f>
+        <f>+([2]Main!$M$7-[2]Main!$M$6)*FX!C3</f>
         <v>27180.799999999999</v>
       </c>
       <c r="H7" s="17">
         <f>F7+G7</f>
         <v>149680.7936</v>
       </c>
-      <c r="I7" s="39" t="s">
+      <c r="I7" s="38" t="s">
         <v>1174</v>
       </c>
       <c r="J7" s="22">
@@ -34199,15 +34200,15 @@
         <v>40</v>
       </c>
       <c r="E8" s="31">
-        <f>+[33]Main!$H$2</f>
+        <f>+[4]Main!$H$2</f>
         <v>485.4</v>
       </c>
       <c r="F8" s="17">
-        <f>+[33]Main!$H$4*FX!C4</f>
+        <f>+[4]Main!$H$4*FX!C4</f>
         <v>72888.393927045603</v>
       </c>
       <c r="G8" s="17">
-        <f>+([33]Main!$H$6-[33]Main!$H$5)*FX!C4</f>
+        <f>+([4]Main!$H$6-[4]Main!$H$5)*FX!C4</f>
         <v>-228.87708000000006</v>
       </c>
       <c r="H8" s="17">
@@ -34300,22 +34301,22 @@
         <v>95</v>
       </c>
       <c r="E9" s="17">
-        <f>+[34]Main!$J$2</f>
+        <f>+[5]Main!$J$2</f>
         <v>5714</v>
       </c>
       <c r="F9" s="17">
-        <f>+[34]Main!$J$4*FX!C5</f>
+        <f>+[5]Main!$J$4*FX!C5</f>
         <v>68983.677500799997</v>
       </c>
       <c r="G9" s="17">
-        <f>+([34]Main!$J$6-[34]Main!$J$5)*FX!C5</f>
+        <f>+([5]Main!$J$6-[5]Main!$J$5)*FX!C5</f>
         <v>2758.2091999999998</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
         <v>71741.886700799994</v>
       </c>
-      <c r="I9" s="43" t="s">
+      <c r="I9" s="42" t="s">
         <v>1174</v>
       </c>
       <c r="J9" s="22">
@@ -34406,22 +34407,22 @@
         <v>31</v>
       </c>
       <c r="E10" s="31">
-        <f>+[35]Main!$I$2</f>
+        <f>+[6]Main!$I$2</f>
         <v>32.61</v>
       </c>
       <c r="F10" s="17">
-        <f>+([35]Main!$I$4)*FX!C3</f>
+        <f>+([6]Main!$I$4)*FX!C3</f>
         <v>34427.811840000002</v>
       </c>
       <c r="G10" s="17">
-        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C3</f>
+        <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C3</f>
         <v>10438.4</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
         <v>44866.211840000004</v>
       </c>
-      <c r="I10" s="41" t="s">
+      <c r="I10" s="40" t="s">
         <v>1174</v>
       </c>
       <c r="J10" s="22">
@@ -34507,15 +34508,15 @@
         <v>617</v>
       </c>
       <c r="E11" s="17">
-        <f>+[36]Main!$I$2</f>
+        <f>+[7]Main!$I$2</f>
         <v>107400</v>
       </c>
       <c r="F11" s="17">
-        <f>+[36]Main!$I$4*FX!C6</f>
+        <f>+[7]Main!$I$4*FX!C6</f>
         <v>9270.9964935000007</v>
       </c>
       <c r="G11" s="17">
-        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C6</f>
+        <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C6</f>
         <v>-575.42399999999998</v>
       </c>
       <c r="H11" s="17">
@@ -34606,15 +34607,15 @@
         <v>240</v>
       </c>
       <c r="E12" s="17">
-        <f>+[37]Main!$I$2</f>
+        <f>+[8]Main!$I$2</f>
         <v>590</v>
       </c>
       <c r="F12" s="17">
-        <f>+[37]Main!$I$4*FX!C7</f>
+        <f>+[8]Main!$I$4*FX!C7</f>
         <v>4254.915253002001</v>
       </c>
       <c r="G12" s="17">
-        <f>+([37]Main!$I$6-[37]Main!$I$5)*FX!C7</f>
+        <f>+([8]Main!$I$6-[8]Main!$I$5)*FX!C7</f>
         <v>-162.340056</v>
       </c>
       <c r="H12" s="17">
@@ -35033,22 +35034,22 @@
         <v>527</v>
       </c>
       <c r="E17" s="31">
-        <f>+[38]Main!$J$2</f>
+        <f>+[9]Main!$J$2</f>
         <v>66.2</v>
       </c>
       <c r="F17" s="17">
-        <f>+[38]Main!$J$4*FX!C11</f>
+        <f>+[9]Main!$J$4*FX!C11</f>
         <v>834.02467200000001</v>
       </c>
       <c r="G17" s="17">
-        <f>+([38]Main!$J$6-[38]Main!$J$5)*FX!C11</f>
+        <f>+([9]Main!$J$6-[9]Main!$J$5)*FX!C11</f>
         <v>781.26400000000012</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ref="H17" si="3">F17+G17</f>
         <v>1615.2886720000001</v>
       </c>
-      <c r="I17" s="42" t="s">
+      <c r="I17" s="41" t="s">
         <v>1174</v>
       </c>
       <c r="J17" s="22">
@@ -35213,27 +35214,25 @@
         <v>27</v>
       </c>
       <c r="E19" s="31">
-        <f>+[39]Main!$I$3</f>
-        <v>69.63</v>
+        <f>+[10]Main!$I$3</f>
+        <v>90.75</v>
       </c>
       <c r="F19" s="17">
-        <f>+[39]Main!$I$5</f>
-        <v>1232.2425974099999</v>
+        <f>+[10]Main!$I$5</f>
+        <v>1757.6037105</v>
       </c>
       <c r="G19" s="17">
-        <f>+[39]Main!$I$7-[39]Main!$I$6</f>
-        <v>214.72500000000002</v>
+        <f>+[10]Main!$I$7-[10]Main!$I$6</f>
+        <v>101.446</v>
       </c>
       <c r="H19" s="17">
         <f t="shared" ref="H19:H20" si="4">F19+G19</f>
-        <v>1446.9675974100001</v>
-      </c>
-      <c r="I19" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="22">
-        <v>45714</v>
-      </c>
+        <v>1859.0497104999999</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>1175</v>
+      </c>
+      <c r="J19" s="22"/>
       <c r="K19" s="31"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -35312,15 +35311,15 @@
         <v>27</v>
       </c>
       <c r="E20" s="31">
-        <f>+[40]Main!$I$2</f>
+        <f>+[11]Main!$I$2</f>
         <v>4.3600000000000003</v>
       </c>
       <c r="F20" s="17">
-        <f>+[40]Main!$I$4</f>
+        <f>+[11]Main!$I$4</f>
         <v>248.91663792000003</v>
       </c>
       <c r="G20" s="17">
-        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
+        <f>+[11]Main!$I$6-[11]Main!$I$5</f>
         <v>-34.395385999999995</v>
       </c>
       <c r="H20" s="17">

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4797C565-7395-48A1-B40B-616FBA0F0929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B33EC8-F17B-4166-9B76-CBAF0E08D748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="5070" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3963,10 +3963,10 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4026,9 +4026,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4068,7 +4068,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5581,18 +5581,18 @@
         </row>
         <row r="5">
           <cell r="J5">
-            <v>197.7</v>
+            <v>13.5</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>5080.6000000000004</v>
+            <v>4770.6000000000004</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -21592,7 +21592,7 @@
         <f>+F6+G6</f>
         <v>249692.29295557001</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="I6" s="42" t="s">
         <v>1174</v>
       </c>
       <c r="J6" s="4"/>
@@ -33777,11 +33777,11 @@
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>105545.08267799998</v>
+        <v>105524.95467799998</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>831453.46474476776</v>
+        <v>831433.33674476773</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33881,7 +33881,7 @@
         <f>+F5+G5</f>
         <v>343294.29843199998</v>
       </c>
-      <c r="I5" s="44" t="s">
+      <c r="I5" s="43" t="s">
         <v>1175</v>
       </c>
       <c r="J5" s="22"/>
@@ -33992,7 +33992,7 @@
         <f>+F6+G6</f>
         <v>132733.75</v>
       </c>
-      <c r="I6" s="42" t="s">
+      <c r="I6" s="41" t="s">
         <v>1174</v>
       </c>
       <c r="J6" s="22">
@@ -34316,7 +34316,7 @@
         <f t="shared" si="1"/>
         <v>71741.886700799994</v>
       </c>
-      <c r="I9" s="42" t="s">
+      <c r="I9" s="41" t="s">
         <v>1174</v>
       </c>
       <c r="J9" s="22">
@@ -35043,17 +35043,17 @@
       </c>
       <c r="G17" s="17">
         <f>+([9]Main!$J$6-[9]Main!$J$5)*FX!C11</f>
-        <v>781.26400000000012</v>
+        <v>761.13600000000008</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ref="H17" si="3">F17+G17</f>
-        <v>1615.2886720000001</v>
-      </c>
-      <c r="I17" s="41" t="s">
-        <v>1174</v>
+        <v>1595.160672</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>1175</v>
       </c>
       <c r="J17" s="22">
-        <v>46162</v>
+        <v>46260</v>
       </c>
       <c r="K17" s="31"/>
       <c r="L17" s="4"/>
@@ -35229,7 +35229,7 @@
         <f t="shared" ref="H19:H20" si="4">F19+G19</f>
         <v>1859.0497104999999</v>
       </c>
-      <c r="I19" s="44" t="s">
+      <c r="I19" s="43" t="s">
         <v>1175</v>
       </c>
       <c r="J19" s="22"/>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B33EC8-F17B-4166-9B76-CBAF0E08D748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304C2A1D-C062-4C67-9699-72CC7B5AC61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="5070" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -5590,9 +5590,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304C2A1D-C062-4C67-9699-72CC7B5AC61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C31EA8C-031C-49BC-A236-86AF5C1B9914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="4680" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="1176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="1177">
   <si>
     <t>Consumer Goods</t>
   </si>
@@ -3669,6 +3669,9 @@
   </si>
   <si>
     <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
@@ -3954,22 +3957,22 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -3991,6 +3994,934 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>77.62</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>203364.40000000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>6394</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>65867</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>52.07</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>28244.199404300001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>363.9</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>14201.6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>164.97</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>33423.547236300001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1515.252</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>5925.4940000000006</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>81.52</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>28099.772318880001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>569</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5729</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>51.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>24539.198905600002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>7861</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>9311</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>76.930000000000007</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>20629.107760310002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>186.1</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>4341.8999999999996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>192.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>22527.326947800004</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>217.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2396.8999999999996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>90.6</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>10478.7931914</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>289.35000000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>480.97</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>16328.412533369999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>484.59299999999996</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>4975.8360000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>164.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>16076.2140936</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>285.66300000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>8.2520000000000007</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>190.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>98509.662835499999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>200.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2094.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>316.05</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>225076.38231750001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2413</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>41283</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>137.83000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5880.7446451600008</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>312.92099999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>246.94499999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>15.7</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2533.98</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>334.4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2131.4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>70.25</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>7885.1376982500005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1386.9570000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>6142.2950000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="WC"/>
+      <sheetName val="BC"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+      <sheetName val="CoC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>101.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>691.47869700000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>83.239000000000004</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>15.463999999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>58.4</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5120.5660200000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>15.09</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>147.5</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>85</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3086.2649999999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>194.86799999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1078.9940000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>70.05</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>301327.69959224999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>13874</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>47398</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>153.69</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>210040.29295557001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>9530</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>49182</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>87.85</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>99859.095000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>4505.9000000000005</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>17319.099999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>141.83000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>28675.237054880003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>10544.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>47.255000000000003</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>118657.30500000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>6415</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>31654</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4034,399 +4965,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>90.75</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1757.6037105</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>192.43899999999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>293.88499999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4.3600000000000003</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>248.91663792000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>34.395385999999995</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>77.62</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>203364.40000000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>6394</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>65867</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>316.05</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>225076.38231750001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2413</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>41283</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>47.255000000000003</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>118657.30500000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>6415</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>31654</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>68.88</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>89186.882892239984</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>1561</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>17624</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>56.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>76686.73404000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>698.54700000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="G3">
-            <v>267.60000000000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>114317.33704320001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>4999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="G7">
-            <v>2721</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>72.48</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>46401.463049279999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5"/>
-        </row>
-        <row r="6">
-          <cell r="H6"/>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>26.72</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>31624.244938719999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2113</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>21603</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4468,407 +5007,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>75.650000000000006</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>37161.254464999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>733</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>12356</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>52.07</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>28244.199404300001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>363.9</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>14201.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>164.97</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>33423.547236300001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1515.252</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>5925.4940000000006</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>81.52</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>28099.772318880001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>569</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5729</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>51.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>24539.198905600002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>7861</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>9311</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>76.930000000000007</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>20629.107760310002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>186.1</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>4341.8999999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>192.3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>22527.326947800004</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>217.3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2396.8999999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>90.6</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>10478.7931914</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>289.35000000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>480.97</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>16328.412533369999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>484.59299999999996</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>4975.8360000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>164.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>16076.2140936</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>285.66300000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>8.2520000000000007</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4904,417 +5043,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>190.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>98509.662835499999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>200.3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>2094.9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>137.83000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5880.7446451600008</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>312.92099999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>246.94499999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>15.7</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2533.98</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>334.4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2131.4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>70.25</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>7885.1376982500005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1386.9570000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>6142.2950000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="WC"/>
-      <sheetName val="BC"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-      <sheetName val="CoC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>95.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>649.92184920000011</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>116.907</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>12.127000000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>58.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5120.5660200000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>15.09</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>147.5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3086.2649999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>194.86799999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1078.9940000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>70.05</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>301327.69959224999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>13874</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>47398</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>153.69</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>210040.29295557001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>9530</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>49182</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>87.85</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>99859.095000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>4505.9000000000005</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>17319.099999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5354,47 +5083,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>141.83000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>28675.237054880003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>72</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>10544.9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5434,7 +5123,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5474,7 +5163,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5514,7 +5203,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5554,7 +5243,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5593,6 +5282,320 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>90.75</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1757.6037105</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>192.43899999999999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>293.88499999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>68.88</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>89186.882892239984</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>1561</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>17624</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4.3600000000000003</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>248.91663792000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>34.395385999999995</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>56.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>76686.73404000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>698.54700000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="G3">
+            <v>267.60000000000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>114317.33704320001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>4999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="G7">
+            <v>2721</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>72.48</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>46401.463049279999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5"/>
+        </row>
+        <row r="6">
+          <cell r="H6"/>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>26.72</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>31624.244938719999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2113</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>21603</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>75.650000000000006</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>37161.254464999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>733</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>12356</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -13932,15 +13935,15 @@
         <v>23</v>
       </c>
       <c r="E4" s="4">
-        <f>+[12]Main!$H$2</f>
+        <f>+[1]Main!$H$2</f>
         <v>77.62</v>
       </c>
       <c r="F4" s="17">
-        <f>+[12]Main!$H$4*FX!C9</f>
+        <f>+[1]Main!$H$4*FX!C9</f>
         <v>250138.21200000003</v>
       </c>
       <c r="G4" s="17">
-        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C9</f>
+        <f>+([1]Main!$H$6-[1]Main!$H$5)*FX!C9</f>
         <v>73151.789999999994</v>
       </c>
       <c r="H4" s="17">
@@ -13971,15 +13974,15 @@
         <v>27</v>
       </c>
       <c r="E5" s="19">
-        <f>+[13]Main!$H$2</f>
+        <f>+[2]Main!$H$2</f>
         <v>316.05</v>
       </c>
       <c r="F5" s="17">
-        <f>+[13]Main!$H$4</f>
+        <f>+[2]Main!$H$4</f>
         <v>225076.38231750001</v>
       </c>
       <c r="G5" s="17">
-        <f>+[13]Main!$H$6-[13]Main!$H$5</f>
+        <f>+[2]Main!$H$6-[2]Main!$H$5</f>
         <v>38870</v>
       </c>
       <c r="H5" s="17">
@@ -14016,15 +14019,15 @@
         <v>31</v>
       </c>
       <c r="E6" s="19">
-        <f>+[14]Main!$I$2</f>
+        <f>+[3]Main!$I$2</f>
         <v>47.255000000000003</v>
       </c>
       <c r="F6" s="17">
-        <f>+[14]Main!$I$4*FX!C3</f>
+        <f>+[3]Main!$I$4*FX!C3</f>
         <v>151881.35040000002</v>
       </c>
       <c r="G6" s="17">
-        <f>+([14]Main!$I$6-[14]Main!$I$5)*FX!C3</f>
+        <f>+([3]Main!$I$6-[3]Main!$I$5)*FX!C3</f>
         <v>32305.920000000002</v>
       </c>
       <c r="H6" s="17">
@@ -14051,15 +14054,15 @@
         <v>27</v>
       </c>
       <c r="E7" s="19">
-        <f>+[15]Main!$H$2</f>
+        <f>+[4]Main!$H$2</f>
         <v>68.88</v>
       </c>
       <c r="F7" s="17">
-        <f>+[15]Main!$H$4</f>
+        <f>+[4]Main!$H$4</f>
         <v>89186.882892239984</v>
       </c>
       <c r="G7" s="17">
-        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
+        <f>+[4]Main!$H$6-[4]Main!$H$5</f>
         <v>16063</v>
       </c>
       <c r="H7" s="17">
@@ -14096,15 +14099,15 @@
         <v>27</v>
       </c>
       <c r="E8" s="19">
-        <f>+[16]Main!$H$2</f>
+        <f>+[5]Main!$H$2</f>
         <v>56.28</v>
       </c>
       <c r="F8" s="17">
-        <f>+[16]Main!$H$4</f>
+        <f>+[5]Main!$H$4</f>
         <v>76686.73404000001</v>
       </c>
       <c r="G8" s="17">
-        <f>+[16]Main!$H$6-[16]Main!$H$5</f>
+        <f>+[5]Main!$H$6-[5]Main!$H$5</f>
         <v>-698.54700000000003</v>
       </c>
       <c r="H8" s="17">
@@ -14155,15 +14158,15 @@
         <v>27</v>
       </c>
       <c r="E10" s="19">
-        <f>+[17]Main!$G$3</f>
+        <f>+[6]Main!$G$3</f>
         <v>267.60000000000002</v>
       </c>
       <c r="F10" s="17">
-        <f>+[17]Main!$G$5</f>
+        <f>+[6]Main!$G$5</f>
         <v>114317.33704320001</v>
       </c>
       <c r="G10" s="17">
-        <f>+[17]Main!$G$7-[17]Main!$G$6</f>
+        <f>+[6]Main!$G$7-[6]Main!$G$6</f>
         <v>-2278</v>
       </c>
       <c r="H10" s="17">
@@ -14214,15 +14217,15 @@
         <v>47</v>
       </c>
       <c r="E12" s="19">
-        <f>+[18]Main!$H$2</f>
+        <f>+[7]Main!$H$2</f>
         <v>72.48</v>
       </c>
       <c r="F12" s="17">
-        <f>+[18]Main!$H$4*FX!C8</f>
+        <f>+[7]Main!$H$4*FX!C8</f>
         <v>52897.667876179192</v>
       </c>
       <c r="G12" s="17">
-        <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C8</f>
+        <f>+([7]Main!$H$6-[7]Main!$H$5)*FX!C8</f>
         <v>0</v>
       </c>
       <c r="H12" s="17">
@@ -14249,15 +14252,15 @@
         <v>27</v>
       </c>
       <c r="E13" s="19">
-        <f>+[19]Main!$H$2</f>
+        <f>+[8]Main!$H$2</f>
         <v>26.72</v>
       </c>
       <c r="F13" s="17">
-        <f>+[19]Main!$H$4</f>
+        <f>+[8]Main!$H$4</f>
         <v>31624.244938719999</v>
       </c>
       <c r="G13" s="17">
-        <f>+[19]Main!$H$6-[19]Main!$H$5</f>
+        <f>+[8]Main!$H$6-[8]Main!$H$5</f>
         <v>19490</v>
       </c>
       <c r="H13" s="17">
@@ -14288,15 +14291,15 @@
         <v>27</v>
       </c>
       <c r="E14" s="19">
-        <f>+[20]Main!$H$2</f>
+        <f>+[9]Main!$H$2</f>
         <v>75.650000000000006</v>
       </c>
       <c r="F14" s="17">
-        <f>+[20]Main!$H$4</f>
+        <f>+[9]Main!$H$4</f>
         <v>37161.254464999998</v>
       </c>
       <c r="G14" s="17">
-        <f>+[20]Main!$H$6-[20]Main!$H$5</f>
+        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
         <v>11623</v>
       </c>
       <c r="H14" s="17">
@@ -14327,15 +14330,15 @@
         <v>27</v>
       </c>
       <c r="E15" s="19">
-        <f>+[21]Main!$J$2</f>
+        <f>+[10]Main!$J$2</f>
         <v>52.07</v>
       </c>
       <c r="F15" s="17">
-        <f>+[21]Main!$J$4</f>
+        <f>+[10]Main!$J$4</f>
         <v>28244.199404300001</v>
       </c>
       <c r="G15" s="17">
-        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
+        <f>+[10]Main!$J$6-[10]Main!$J$5</f>
         <v>13837.7</v>
       </c>
       <c r="H15" s="17">
@@ -14362,15 +14365,15 @@
         <v>27</v>
       </c>
       <c r="E16" s="19">
-        <f>+[22]Main!$J$2</f>
+        <f>+[11]Main!$J$2</f>
         <v>164.97</v>
       </c>
       <c r="F16" s="17">
-        <f>+[22]Main!$J$4</f>
+        <f>+[11]Main!$J$4</f>
         <v>33423.547236300001</v>
       </c>
       <c r="G16" s="17">
-        <f>+[22]Main!$J$6-[22]Main!$J$5</f>
+        <f>+[11]Main!$J$6-[11]Main!$J$5</f>
         <v>4410.2420000000002</v>
       </c>
       <c r="H16" s="17">
@@ -14497,15 +14500,15 @@
         <v>27</v>
       </c>
       <c r="E22" s="19">
-        <f>+[23]Main!$I$2</f>
+        <f>+[12]Main!$I$2</f>
         <v>81.52</v>
       </c>
       <c r="F22" s="17">
-        <f>+[23]Main!$I$4</f>
+        <f>+[12]Main!$I$4</f>
         <v>28099.772318880001</v>
       </c>
       <c r="G22" s="17">
-        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
+        <f>+[12]Main!$I$6-[12]Main!$I$5</f>
         <v>5160</v>
       </c>
       <c r="H22" s="17">
@@ -14602,15 +14605,15 @@
         <v>27</v>
       </c>
       <c r="E26" s="19">
-        <f>+[24]Main!$I$2</f>
+        <f>+[13]Main!$I$2</f>
         <v>51.28</v>
       </c>
       <c r="F26" s="17">
-        <f>+[24]Main!$I$4</f>
+        <f>+[13]Main!$I$4</f>
         <v>24539.198905600002</v>
       </c>
       <c r="G26" s="17">
-        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
+        <f>+[13]Main!$I$6-[13]Main!$I$5</f>
         <v>1450</v>
       </c>
       <c r="H26" s="17">
@@ -14704,15 +14707,15 @@
         <v>27</v>
       </c>
       <c r="E30" s="19">
-        <f>+[25]Main!$J$2</f>
+        <f>+[14]Main!$J$2</f>
         <v>76.930000000000007</v>
       </c>
       <c r="F30" s="17">
-        <f>+[25]Main!$J$4</f>
+        <f>+[14]Main!$J$4</f>
         <v>20629.107760310002</v>
       </c>
       <c r="G30" s="17">
-        <f>+[25]Main!$J$6-[25]Main!$J$5</f>
+        <f>+[14]Main!$J$6-[14]Main!$J$5</f>
         <v>4155.7999999999993</v>
       </c>
       <c r="H30" s="17">
@@ -14743,15 +14746,15 @@
         <v>27</v>
       </c>
       <c r="E31" s="19">
-        <f>+[26]Main!$I$2</f>
+        <f>+[15]Main!$I$2</f>
         <v>192.3</v>
       </c>
       <c r="F31" s="17">
-        <f>+[26]Main!$I$4</f>
+        <f>+[15]Main!$I$4</f>
         <v>22527.326947800004</v>
       </c>
       <c r="G31" s="17">
-        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
+        <f>+[15]Main!$I$6-[15]Main!$I$5</f>
         <v>2179.5999999999995</v>
       </c>
       <c r="H31" s="17">
@@ -14922,15 +14925,15 @@
         <v>27</v>
       </c>
       <c r="E39" s="19">
-        <f>+[27]Main!$I$2</f>
+        <f>+[16]Main!$I$2</f>
         <v>90.6</v>
       </c>
       <c r="F39" s="17">
-        <f>+[27]Main!$I$4</f>
+        <f>+[16]Main!$I$4</f>
         <v>10478.7931914</v>
       </c>
       <c r="G39" s="17">
-        <f>+[27]Main!$I$6-[27]Main!$I$5</f>
+        <f>+[16]Main!$I$6-[16]Main!$I$5</f>
         <v>-289.35000000000002</v>
       </c>
       <c r="H39" s="17">
@@ -14957,15 +14960,15 @@
         <v>27</v>
       </c>
       <c r="E40" s="19">
-        <f>+[28]Main!$J$2</f>
+        <f>+[17]Main!$J$2</f>
         <v>480.97</v>
       </c>
       <c r="F40" s="17">
-        <f>+[28]Main!$J$4</f>
+        <f>+[17]Main!$J$4</f>
         <v>16328.412533369999</v>
       </c>
       <c r="G40" s="17">
-        <f>+[28]Main!$J$6-[28]Main!$J$5</f>
+        <f>+[17]Main!$J$6-[17]Main!$J$5</f>
         <v>4491.2430000000004</v>
       </c>
       <c r="H40" s="17">
@@ -15052,15 +15055,15 @@
         <v>27</v>
       </c>
       <c r="E44" s="19">
-        <f>+[29]Main!$I$2</f>
+        <f>+[18]Main!$I$2</f>
         <v>164.28</v>
       </c>
       <c r="F44" s="17">
-        <f>+[29]Main!$I$4</f>
+        <f>+[18]Main!$I$4</f>
         <v>16076.2140936</v>
       </c>
       <c r="G44" s="17">
-        <f>+[29]Main!$I$6-[29]Main!$I$5</f>
+        <f>+[18]Main!$I$6-[18]Main!$I$5</f>
         <v>-277.411</v>
       </c>
       <c r="H44" s="17">
@@ -15491,15 +15494,15 @@
         <v>172</v>
       </c>
       <c r="E66" s="4">
-        <f>+[30]Main!$J$2</f>
+        <f>+[19]Main!$J$2</f>
         <v>190.5</v>
       </c>
       <c r="F66" s="17">
-        <f>+[30]Main!$J$4*FX!C10</f>
+        <f>+[19]Main!$J$4*FX!C10</f>
         <v>9653.9469578789995</v>
       </c>
       <c r="G66" s="17">
-        <f>+([30]Main!$J$6-[30]Main!$J$5)*FX!C10</f>
+        <f>+([19]Main!$J$6-[19]Main!$J$5)*FX!C10</f>
         <v>185.67080000000001</v>
       </c>
       <c r="H66" s="17">
@@ -15621,15 +15624,15 @@
         <v>27</v>
       </c>
       <c r="E72" s="4">
-        <f>+[31]Main!$J$2</f>
+        <f>+[20]Main!$J$2</f>
         <v>137.83000000000001</v>
       </c>
       <c r="F72" s="17">
-        <f>+[31]Main!$J$4</f>
+        <f>+[20]Main!$J$4</f>
         <v>5880.7446451600008</v>
       </c>
       <c r="G72" s="17">
-        <f>+[31]Main!$J$6-[31]Main!$J$5</f>
+        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
         <v>-65.975999999999999</v>
       </c>
       <c r="H72" s="17">
@@ -16701,15 +16704,15 @@
         <v>31</v>
       </c>
       <c r="E128" s="4">
-        <f>+[32]Main!$I$2</f>
+        <f>+[21]Main!$I$2</f>
         <v>15.7</v>
       </c>
       <c r="F128" s="17">
-        <f>+[32]Main!$I$4*FX!C3</f>
+        <f>+[21]Main!$I$4*FX!C3</f>
         <v>3243.4944</v>
       </c>
       <c r="G128" s="17">
-        <f>+([32]Main!$I$6-[32]Main!$I$5)*FX!C3</f>
+        <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C3</f>
         <v>2300.16</v>
       </c>
       <c r="H128" s="17">
@@ -18159,15 +18162,15 @@
         <v>172</v>
       </c>
       <c r="E203" s="4">
-        <f>+[33]Main!$J$2</f>
+        <f>+[22]Main!$J$2</f>
         <v>70.25</v>
       </c>
       <c r="F203" s="17">
-        <f>+[33]Main!$J$4*FX!C10</f>
+        <f>+[22]Main!$J$4*FX!C10</f>
         <v>772.74349442850007</v>
       </c>
       <c r="G203" s="17">
-        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C10</f>
+        <f>+([22]Main!$J$6-[22]Main!$J$5)*FX!C10</f>
         <v>466.023124</v>
       </c>
       <c r="H203" s="17">
@@ -18232,23 +18235,23 @@
         <v>146</v>
       </c>
       <c r="E206" s="4">
-        <f>+[34]Main!$H$2</f>
-        <v>95.4</v>
+        <f>+[23]Main!$H$2</f>
+        <v>101.5</v>
       </c>
       <c r="F206" s="17">
-        <f>+[34]Main!$H$4*FX!C8</f>
-        <v>740.91090808800004</v>
+        <f>+[23]Main!$H$4*FX!C8</f>
+        <v>788.28571457999999</v>
       </c>
       <c r="G206" s="17">
-        <f>+([34]Main!$H$6-[34]Main!$H$5)*FX!C8</f>
-        <v>-119.44919999999999</v>
+        <f>+([23]Main!$H$6-[23]Main!$H$5)*FX!C8</f>
+        <v>-77.263499999999993</v>
       </c>
       <c r="H206" s="17">
         <f>+F206+G206</f>
-        <v>621.46170808800002</v>
-      </c>
-      <c r="I206" s="39" t="s">
-        <v>1174</v>
+        <v>711.02221457999997</v>
+      </c>
+      <c r="I206" s="44" t="s">
+        <v>1176</v>
       </c>
       <c r="J206" s="22">
         <v>46186</v>
@@ -19228,15 +19231,15 @@
         <v>924</v>
       </c>
       <c r="E259" s="4">
-        <f>+[35]Main!$J$2</f>
+        <f>+[24]Main!$J$2</f>
         <v>58.4</v>
       </c>
       <c r="F259" s="17">
-        <f>+[35]Main!$J$4*FX!C10</f>
+        <f>+[24]Main!$J$4*FX!C10</f>
         <v>501.81546996000003</v>
       </c>
       <c r="G259" s="17">
-        <f>+([35]Main!$J$6-[35]Main!$J$5)*FX!C10</f>
+        <f>+([24]Main!$J$6-[24]Main!$J$5)*FX!C10</f>
         <v>12.976179999999999</v>
       </c>
       <c r="H259" s="17">
@@ -20828,15 +20831,15 @@
         <v>924</v>
       </c>
       <c r="E348" s="4">
-        <f>+[36]Main!$I$2</f>
+        <f>+[25]Main!$I$2</f>
         <v>85</v>
       </c>
       <c r="F348" s="17">
-        <f>+[36]Main!$I$4*FX!C10</f>
+        <f>+[25]Main!$I$4*FX!C10</f>
         <v>302.45397000000003</v>
       </c>
       <c r="G348" s="17">
-        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C10</f>
+        <f>+([25]Main!$I$6-[25]Main!$I$5)*FX!C10</f>
         <v>86.644348000000022</v>
       </c>
       <c r="H348" s="17">
@@ -21355,15 +21358,15 @@
         <v>27</v>
       </c>
       <c r="E4" s="4">
-        <f>+[37]Main!$I$2</f>
+        <f>+[26]Main!$I$2</f>
         <v>70.05</v>
       </c>
       <c r="F4" s="17">
-        <f>+[37]Main!$I$4</f>
+        <f>+[26]Main!$I$4</f>
         <v>301327.69959224999</v>
       </c>
       <c r="G4" s="17">
-        <f>+[37]Main!$I$6-[37]Main!$I$5</f>
+        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
         <v>33524</v>
       </c>
       <c r="H4" s="17">
@@ -21577,22 +21580,22 @@
         <v>27</v>
       </c>
       <c r="E6" s="4">
-        <f>+[38]Main!$I$2</f>
+        <f>+[27]Main!$I$2</f>
         <v>153.69</v>
       </c>
       <c r="F6" s="17">
-        <f>+[38]Main!$I$4</f>
+        <f>+[27]Main!$I$4</f>
         <v>210040.29295557001</v>
       </c>
       <c r="G6" s="17">
-        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
+        <f>+[27]Main!$I$6-[27]Main!$I$5</f>
         <v>39652</v>
       </c>
       <c r="H6" s="17">
         <f>+F6+G6</f>
         <v>249692.29295557001</v>
       </c>
-      <c r="I6" s="42" t="s">
+      <c r="I6" s="41" t="s">
         <v>1174</v>
       </c>
       <c r="J6" s="4"/>
@@ -21902,15 +21905,15 @@
         <v>27</v>
       </c>
       <c r="E9" s="4">
-        <f>+[39]Main!$J$2</f>
+        <f>+[28]Main!$J$2</f>
         <v>87.85</v>
       </c>
       <c r="F9" s="17">
-        <f>+[39]Main!$J$4</f>
+        <f>+[28]Main!$J$4</f>
         <v>99859.095000000001</v>
       </c>
       <c r="G9" s="17">
-        <f>+[39]Main!$J$6-[39]Main!$J$5</f>
+        <f>+[28]Main!$J$6-[28]Main!$J$5</f>
         <v>12813.199999999997</v>
       </c>
       <c r="H9" s="17">
@@ -22639,15 +22642,15 @@
         <v>27</v>
       </c>
       <c r="E16" s="4">
-        <f>+[40]Main!$I$2</f>
+        <f>+[29]Main!$I$2</f>
         <v>141.83000000000001</v>
       </c>
       <c r="F16" s="17">
-        <f>+[40]Main!$I$4</f>
+        <f>+[29]Main!$I$4</f>
         <v>28675.237054880003</v>
       </c>
       <c r="G16" s="17">
-        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
+        <f>+[29]Main!$I$6-[29]Main!$I$5</f>
         <v>10472.9</v>
       </c>
       <c r="H16" s="17">
@@ -33866,22 +33869,22 @@
         <v>27</v>
       </c>
       <c r="E5" s="31">
-        <f>+[1]Main!$K$3</f>
+        <f>+[30]Main!$K$3</f>
         <v>192</v>
       </c>
       <c r="F5" s="17">
-        <f>+[1]Main!$K$5</f>
+        <f>+[30]Main!$K$5</f>
         <v>299243.29843199998</v>
       </c>
       <c r="G5" s="17">
-        <f>+[1]Main!$K$7-[1]Main!$K$6</f>
+        <f>+[30]Main!$K$7-[30]Main!$K$6</f>
         <v>44051</v>
       </c>
       <c r="H5" s="17">
         <f>+F5+G5</f>
         <v>343294.29843199998</v>
       </c>
-      <c r="I5" s="43" t="s">
+      <c r="I5" s="42" t="s">
         <v>1175</v>
       </c>
       <c r="J5" s="22"/>
@@ -33977,22 +33980,22 @@
         <v>27</v>
       </c>
       <c r="E6" s="31">
-        <f>+[2]Main!$M$3</f>
+        <f>+[31]Main!$M$3</f>
         <v>66.25</v>
       </c>
       <c r="F6" s="17">
-        <f>+[2]Main!$M$5</f>
+        <f>+[31]Main!$M$5</f>
         <v>111498.75</v>
       </c>
       <c r="G6" s="17">
-        <f>+[2]Main!$M$7-[2]Main!$M$6</f>
+        <f>+[31]Main!$M$7-[31]Main!$M$6</f>
         <v>21235</v>
       </c>
       <c r="H6" s="17">
         <f>+F6+G6</f>
         <v>132733.75</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="40" t="s">
         <v>1174</v>
       </c>
       <c r="J6" s="22">
@@ -34090,15 +34093,15 @@
         <v>31</v>
       </c>
       <c r="E7" s="31">
-        <f>+[3]Main!$H$2</f>
+        <f>+[32]Main!$H$2</f>
         <v>60.8</v>
       </c>
       <c r="F7" s="17">
-        <f>+[3]Main!$H$5*FX!C3</f>
+        <f>+[32]Main!$H$5*FX!C3</f>
         <v>122499.9936</v>
       </c>
       <c r="G7" s="17">
-        <f>+([2]Main!$M$7-[2]Main!$M$6)*FX!C3</f>
+        <f>+([31]Main!$M$7-[31]Main!$M$6)*FX!C3</f>
         <v>27180.799999999999</v>
       </c>
       <c r="H7" s="17">
@@ -34200,15 +34203,15 @@
         <v>40</v>
       </c>
       <c r="E8" s="31">
-        <f>+[4]Main!$H$2</f>
+        <f>+[33]Main!$H$2</f>
         <v>485.4</v>
       </c>
       <c r="F8" s="17">
-        <f>+[4]Main!$H$4*FX!C4</f>
+        <f>+[33]Main!$H$4*FX!C4</f>
         <v>72888.393927045603</v>
       </c>
       <c r="G8" s="17">
-        <f>+([4]Main!$H$6-[4]Main!$H$5)*FX!C4</f>
+        <f>+([33]Main!$H$6-[33]Main!$H$5)*FX!C4</f>
         <v>-228.87708000000006</v>
       </c>
       <c r="H8" s="17">
@@ -34301,22 +34304,22 @@
         <v>95</v>
       </c>
       <c r="E9" s="17">
-        <f>+[5]Main!$J$2</f>
+        <f>+[34]Main!$J$2</f>
         <v>5714</v>
       </c>
       <c r="F9" s="17">
-        <f>+[5]Main!$J$4*FX!C5</f>
+        <f>+[34]Main!$J$4*FX!C5</f>
         <v>68983.677500799997</v>
       </c>
       <c r="G9" s="17">
-        <f>+([5]Main!$J$6-[5]Main!$J$5)*FX!C5</f>
+        <f>+([34]Main!$J$6-[34]Main!$J$5)*FX!C5</f>
         <v>2758.2091999999998</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
         <v>71741.886700799994</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="40" t="s">
         <v>1174</v>
       </c>
       <c r="J9" s="22">
@@ -34407,22 +34410,22 @@
         <v>31</v>
       </c>
       <c r="E10" s="31">
-        <f>+[6]Main!$I$2</f>
+        <f>+[35]Main!$I$2</f>
         <v>32.61</v>
       </c>
       <c r="F10" s="17">
-        <f>+([6]Main!$I$4)*FX!C3</f>
+        <f>+([35]Main!$I$4)*FX!C3</f>
         <v>34427.811840000002</v>
       </c>
       <c r="G10" s="17">
-        <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C3</f>
+        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C3</f>
         <v>10438.4</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
         <v>44866.211840000004</v>
       </c>
-      <c r="I10" s="40" t="s">
+      <c r="I10" s="39" t="s">
         <v>1174</v>
       </c>
       <c r="J10" s="22">
@@ -34508,15 +34511,15 @@
         <v>617</v>
       </c>
       <c r="E11" s="17">
-        <f>+[7]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>107400</v>
       </c>
       <c r="F11" s="17">
-        <f>+[7]Main!$I$4*FX!C6</f>
+        <f>+[36]Main!$I$4*FX!C6</f>
         <v>9270.9964935000007</v>
       </c>
       <c r="G11" s="17">
-        <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C6</f>
+        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C6</f>
         <v>-575.42399999999998</v>
       </c>
       <c r="H11" s="17">
@@ -34607,15 +34610,15 @@
         <v>240</v>
       </c>
       <c r="E12" s="17">
-        <f>+[8]Main!$I$2</f>
+        <f>+[37]Main!$I$2</f>
         <v>590</v>
       </c>
       <c r="F12" s="17">
-        <f>+[8]Main!$I$4*FX!C7</f>
+        <f>+[37]Main!$I$4*FX!C7</f>
         <v>4254.915253002001</v>
       </c>
       <c r="G12" s="17">
-        <f>+([8]Main!$I$6-[8]Main!$I$5)*FX!C7</f>
+        <f>+([37]Main!$I$6-[37]Main!$I$5)*FX!C7</f>
         <v>-162.340056</v>
       </c>
       <c r="H12" s="17">
@@ -35034,22 +35037,22 @@
         <v>527</v>
       </c>
       <c r="E17" s="31">
-        <f>+[9]Main!$J$2</f>
+        <f>+[38]Main!$J$2</f>
         <v>66.2</v>
       </c>
       <c r="F17" s="17">
-        <f>+[9]Main!$J$4*FX!C11</f>
+        <f>+[38]Main!$J$4*FX!C11</f>
         <v>834.02467200000001</v>
       </c>
       <c r="G17" s="17">
-        <f>+([9]Main!$J$6-[9]Main!$J$5)*FX!C11</f>
+        <f>+([38]Main!$J$6-[38]Main!$J$5)*FX!C11</f>
         <v>761.13600000000008</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ref="H17" si="3">F17+G17</f>
         <v>1595.160672</v>
       </c>
-      <c r="I17" s="44" t="s">
+      <c r="I17" s="43" t="s">
         <v>1175</v>
       </c>
       <c r="J17" s="22">
@@ -35214,22 +35217,22 @@
         <v>27</v>
       </c>
       <c r="E19" s="31">
-        <f>+[10]Main!$I$3</f>
+        <f>+[39]Main!$I$3</f>
         <v>90.75</v>
       </c>
       <c r="F19" s="17">
-        <f>+[10]Main!$I$5</f>
+        <f>+[39]Main!$I$5</f>
         <v>1757.6037105</v>
       </c>
       <c r="G19" s="17">
-        <f>+[10]Main!$I$7-[10]Main!$I$6</f>
+        <f>+[39]Main!$I$7-[39]Main!$I$6</f>
         <v>101.446</v>
       </c>
       <c r="H19" s="17">
         <f t="shared" ref="H19:H20" si="4">F19+G19</f>
         <v>1859.0497104999999</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="42" t="s">
         <v>1175</v>
       </c>
       <c r="J19" s="22"/>
@@ -35311,15 +35314,15 @@
         <v>27</v>
       </c>
       <c r="E20" s="31">
-        <f>+[11]Main!$I$2</f>
+        <f>+[40]Main!$I$2</f>
         <v>4.3600000000000003</v>
       </c>
       <c r="F20" s="17">
-        <f>+[11]Main!$I$4</f>
+        <f>+[40]Main!$I$4</f>
         <v>248.91663792000003</v>
       </c>
       <c r="G20" s="17">
-        <f>+[11]Main!$I$6-[11]Main!$I$5</f>
+        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
         <v>-34.395385999999995</v>
       </c>
       <c r="H20" s="17">

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C31EA8C-031C-49BC-A236-86AF5C1B9914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F63282-C3E6-4CEC-9F2C-99106288807C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4680" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4003,6 +4003,130 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="K3">
+            <v>192</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>299243.29843199998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>5450</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>49501</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>90.75</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1757.6037105</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>192.43899999999999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>293.88499999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4.3600000000000003</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>248.91663792000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>34.395385999999995</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -4033,407 +4157,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>52.07</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>28244.199404300001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>363.9</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>14201.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>164.97</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>33423.547236300001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1515.252</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>5925.4940000000006</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>81.52</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>28099.772318880001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>569</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5729</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>51.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>24539.198905600002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>7861</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>9311</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>76.930000000000007</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>20629.107760310002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>186.1</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>4341.8999999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>192.3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>22527.326947800004</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>217.3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2396.8999999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>90.6</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>10478.7931914</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>289.35000000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>480.97</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>16328.412533369999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>484.59299999999996</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>4975.8360000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>164.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>16076.2140936</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>285.66300000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>8.2520000000000007</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>190.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>98509.662835499999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>200.3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>2094.9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4473,417 +4197,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>137.83000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5880.7446451600008</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>312.92099999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>246.94499999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>15.7</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2533.98</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>334.4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2131.4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>70.25</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>7885.1376982500005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1386.9570000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>6142.2950000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="WC"/>
-      <sheetName val="BC"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-      <sheetName val="CoC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>101.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>691.47869700000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>83.239000000000004</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>15.463999999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>58.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5120.5660200000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>15.09</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>147.5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>85</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3086.2649999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>194.86799999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1078.9940000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>70.05</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>301327.69959224999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>13874</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>47398</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>153.69</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>210040.29295557001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>9530</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>49182</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>87.85</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>99859.095000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>4505.9000000000005</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>17319.099999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>141.83000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>28675.237054880003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>72</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>10544.9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4921,7 +4235,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4931,41 +4245,191 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="3">
-          <cell r="K3">
-            <v>192</v>
+        <row r="2">
+          <cell r="H2">
+            <v>68.88</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>89186.882892239984</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>299243.29843199998</v>
+          <cell r="H5">
+            <v>1561</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
-            <v>5450</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="K7">
-            <v>49501</v>
+          <cell r="H6">
+            <v>17624</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>56.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>76686.73404000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>698.54700000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="G3">
+            <v>267.60000000000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>114317.33704320001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>4999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="G7">
+            <v>2721</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>72.48</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>46401.463049279999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5"/>
+        </row>
+        <row r="6">
+          <cell r="H6"/>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>26.72</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>31624.244938719999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2113</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>21603</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5007,7 +4471,407 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>75.650000000000006</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>37161.254464999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>733</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>12356</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>52.07</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>28244.199404300001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>363.9</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>14201.6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>164.97</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>33423.547236300001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1515.252</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>5925.4940000000006</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>81.52</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>28099.772318880001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>569</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5729</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>51.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>24539.198905600002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>7861</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>9311</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>76.930000000000007</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>20629.107760310002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>186.1</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>4341.8999999999996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>192.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>22527.326947800004</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>217.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2396.8999999999996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>90.6</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>10478.7931914</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>289.35000000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>480.97</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>16328.412533369999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>484.59299999999996</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>4975.8360000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>164.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>16076.2140936</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>285.66300000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>8.2520000000000007</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5030,7 +4894,221 @@
         </row>
         <row r="5">
           <cell r="H5">
-            <v>95703.12</v>
+            <v>100930.05</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
+        <row r="4">
+          <cell r="J4">
+            <v>42.245377497915634</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>190.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>98509.662835499999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>200.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2094.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>137.83000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5880.7446451600008</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>312.92099999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>246.94499999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>15.7</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2533.98</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>334.4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2131.4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>70.25</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>7885.1376982500005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1386.9570000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>6142.2950000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="WC"/>
+      <sheetName val="BC"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+      <sheetName val="CoC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>101.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>691.47869700000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>83.239000000000004</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>15.463999999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -5038,12 +5116,220 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
+      <sheetData sheetId="5">
+        <row r="3">
+          <cell r="J3">
+            <v>97.40723155701005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>58.4</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5120.5660200000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>15.09</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>147.5</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>85</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3086.2649999999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>194.86799999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1078.9940000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>70.05</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>301327.69959224999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>13874</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>47398</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>153.69</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>210040.29295557001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>9530</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>49182</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>87.85</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>99859.095000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>4505.9000000000005</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>17319.099999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5083,7 +5369,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>141.83000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>28675.237054880003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>72</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>10544.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5123,7 +5449,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5163,7 +5489,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5203,7 +5529,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5243,7 +5569,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5260,12 +5586,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>66.2</v>
+            <v>70</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>5212.6541999999999</v>
+            <v>5511.87</v>
           </cell>
         </row>
         <row r="5">
@@ -5281,321 +5607,13 @@
       </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>90.75</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1757.6037105</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>192.43899999999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>293.88499999999999</v>
+      <sheetData sheetId="3">
+        <row r="4">
+          <cell r="J4">
+            <v>110.50341825100335</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>68.88</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>89186.882892239984</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>1561</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>17624</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4.3600000000000003</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>248.91663792000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>34.395385999999995</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>56.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>76686.73404000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>698.54700000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="G3">
-            <v>267.60000000000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>114317.33704320001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>4999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="G7">
-            <v>2721</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>72.48</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>46401.463049279999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5"/>
-        </row>
-        <row r="6">
-          <cell r="H6"/>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>26.72</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>31624.244938719999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2113</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>21603</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>75.650000000000006</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>37161.254464999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>733</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>12356</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -13935,15 +13953,15 @@
         <v>23</v>
       </c>
       <c r="E4" s="4">
-        <f>+[1]Main!$H$2</f>
+        <f>+[12]Main!$H$2</f>
         <v>77.62</v>
       </c>
       <c r="F4" s="17">
-        <f>+[1]Main!$H$4*FX!C9</f>
+        <f>+[12]Main!$H$4*FX!C9</f>
         <v>250138.21200000003</v>
       </c>
       <c r="G4" s="17">
-        <f>+([1]Main!$H$6-[1]Main!$H$5)*FX!C9</f>
+        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C9</f>
         <v>73151.789999999994</v>
       </c>
       <c r="H4" s="17">
@@ -13974,15 +13992,15 @@
         <v>27</v>
       </c>
       <c r="E5" s="19">
-        <f>+[2]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>316.05</v>
       </c>
       <c r="F5" s="17">
-        <f>+[2]Main!$H$4</f>
+        <f>+[13]Main!$H$4</f>
         <v>225076.38231750001</v>
       </c>
       <c r="G5" s="17">
-        <f>+[2]Main!$H$6-[2]Main!$H$5</f>
+        <f>+[13]Main!$H$6-[13]Main!$H$5</f>
         <v>38870</v>
       </c>
       <c r="H5" s="17">
@@ -14019,15 +14037,15 @@
         <v>31</v>
       </c>
       <c r="E6" s="19">
-        <f>+[3]Main!$I$2</f>
+        <f>+[14]Main!$I$2</f>
         <v>47.255000000000003</v>
       </c>
       <c r="F6" s="17">
-        <f>+[3]Main!$I$4*FX!C3</f>
+        <f>+[14]Main!$I$4*FX!C3</f>
         <v>151881.35040000002</v>
       </c>
       <c r="G6" s="17">
-        <f>+([3]Main!$I$6-[3]Main!$I$5)*FX!C3</f>
+        <f>+([14]Main!$I$6-[14]Main!$I$5)*FX!C3</f>
         <v>32305.920000000002</v>
       </c>
       <c r="H6" s="17">
@@ -14054,15 +14072,15 @@
         <v>27</v>
       </c>
       <c r="E7" s="19">
-        <f>+[4]Main!$H$2</f>
+        <f>+[15]Main!$H$2</f>
         <v>68.88</v>
       </c>
       <c r="F7" s="17">
-        <f>+[4]Main!$H$4</f>
+        <f>+[15]Main!$H$4</f>
         <v>89186.882892239984</v>
       </c>
       <c r="G7" s="17">
-        <f>+[4]Main!$H$6-[4]Main!$H$5</f>
+        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
         <v>16063</v>
       </c>
       <c r="H7" s="17">
@@ -14099,15 +14117,15 @@
         <v>27</v>
       </c>
       <c r="E8" s="19">
-        <f>+[5]Main!$H$2</f>
+        <f>+[16]Main!$H$2</f>
         <v>56.28</v>
       </c>
       <c r="F8" s="17">
-        <f>+[5]Main!$H$4</f>
+        <f>+[16]Main!$H$4</f>
         <v>76686.73404000001</v>
       </c>
       <c r="G8" s="17">
-        <f>+[5]Main!$H$6-[5]Main!$H$5</f>
+        <f>+[16]Main!$H$6-[16]Main!$H$5</f>
         <v>-698.54700000000003</v>
       </c>
       <c r="H8" s="17">
@@ -14158,15 +14176,15 @@
         <v>27</v>
       </c>
       <c r="E10" s="19">
-        <f>+[6]Main!$G$3</f>
+        <f>+[17]Main!$G$3</f>
         <v>267.60000000000002</v>
       </c>
       <c r="F10" s="17">
-        <f>+[6]Main!$G$5</f>
+        <f>+[17]Main!$G$5</f>
         <v>114317.33704320001</v>
       </c>
       <c r="G10" s="17">
-        <f>+[6]Main!$G$7-[6]Main!$G$6</f>
+        <f>+[17]Main!$G$7-[17]Main!$G$6</f>
         <v>-2278</v>
       </c>
       <c r="H10" s="17">
@@ -14217,15 +14235,15 @@
         <v>47</v>
       </c>
       <c r="E12" s="19">
-        <f>+[7]Main!$H$2</f>
+        <f>+[18]Main!$H$2</f>
         <v>72.48</v>
       </c>
       <c r="F12" s="17">
-        <f>+[7]Main!$H$4*FX!C8</f>
+        <f>+[18]Main!$H$4*FX!C8</f>
         <v>52897.667876179192</v>
       </c>
       <c r="G12" s="17">
-        <f>+([7]Main!$H$6-[7]Main!$H$5)*FX!C8</f>
+        <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C8</f>
         <v>0</v>
       </c>
       <c r="H12" s="17">
@@ -14252,15 +14270,15 @@
         <v>27</v>
       </c>
       <c r="E13" s="19">
-        <f>+[8]Main!$H$2</f>
+        <f>+[19]Main!$H$2</f>
         <v>26.72</v>
       </c>
       <c r="F13" s="17">
-        <f>+[8]Main!$H$4</f>
+        <f>+[19]Main!$H$4</f>
         <v>31624.244938719999</v>
       </c>
       <c r="G13" s="17">
-        <f>+[8]Main!$H$6-[8]Main!$H$5</f>
+        <f>+[19]Main!$H$6-[19]Main!$H$5</f>
         <v>19490</v>
       </c>
       <c r="H13" s="17">
@@ -14291,15 +14309,15 @@
         <v>27</v>
       </c>
       <c r="E14" s="19">
-        <f>+[9]Main!$H$2</f>
+        <f>+[20]Main!$H$2</f>
         <v>75.650000000000006</v>
       </c>
       <c r="F14" s="17">
-        <f>+[9]Main!$H$4</f>
+        <f>+[20]Main!$H$4</f>
         <v>37161.254464999998</v>
       </c>
       <c r="G14" s="17">
-        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
+        <f>+[20]Main!$H$6-[20]Main!$H$5</f>
         <v>11623</v>
       </c>
       <c r="H14" s="17">
@@ -14330,15 +14348,15 @@
         <v>27</v>
       </c>
       <c r="E15" s="19">
-        <f>+[10]Main!$J$2</f>
+        <f>+[21]Main!$J$2</f>
         <v>52.07</v>
       </c>
       <c r="F15" s="17">
-        <f>+[10]Main!$J$4</f>
+        <f>+[21]Main!$J$4</f>
         <v>28244.199404300001</v>
       </c>
       <c r="G15" s="17">
-        <f>+[10]Main!$J$6-[10]Main!$J$5</f>
+        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
         <v>13837.7</v>
       </c>
       <c r="H15" s="17">
@@ -14365,15 +14383,15 @@
         <v>27</v>
       </c>
       <c r="E16" s="19">
-        <f>+[11]Main!$J$2</f>
+        <f>+[22]Main!$J$2</f>
         <v>164.97</v>
       </c>
       <c r="F16" s="17">
-        <f>+[11]Main!$J$4</f>
+        <f>+[22]Main!$J$4</f>
         <v>33423.547236300001</v>
       </c>
       <c r="G16" s="17">
-        <f>+[11]Main!$J$6-[11]Main!$J$5</f>
+        <f>+[22]Main!$J$6-[22]Main!$J$5</f>
         <v>4410.2420000000002</v>
       </c>
       <c r="H16" s="17">
@@ -14500,15 +14518,15 @@
         <v>27</v>
       </c>
       <c r="E22" s="19">
-        <f>+[12]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>81.52</v>
       </c>
       <c r="F22" s="17">
-        <f>+[12]Main!$I$4</f>
+        <f>+[23]Main!$I$4</f>
         <v>28099.772318880001</v>
       </c>
       <c r="G22" s="17">
-        <f>+[12]Main!$I$6-[12]Main!$I$5</f>
+        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
         <v>5160</v>
       </c>
       <c r="H22" s="17">
@@ -14605,15 +14623,15 @@
         <v>27</v>
       </c>
       <c r="E26" s="19">
-        <f>+[13]Main!$I$2</f>
+        <f>+[24]Main!$I$2</f>
         <v>51.28</v>
       </c>
       <c r="F26" s="17">
-        <f>+[13]Main!$I$4</f>
+        <f>+[24]Main!$I$4</f>
         <v>24539.198905600002</v>
       </c>
       <c r="G26" s="17">
-        <f>+[13]Main!$I$6-[13]Main!$I$5</f>
+        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
         <v>1450</v>
       </c>
       <c r="H26" s="17">
@@ -14707,15 +14725,15 @@
         <v>27</v>
       </c>
       <c r="E30" s="19">
-        <f>+[14]Main!$J$2</f>
+        <f>+[25]Main!$J$2</f>
         <v>76.930000000000007</v>
       </c>
       <c r="F30" s="17">
-        <f>+[14]Main!$J$4</f>
+        <f>+[25]Main!$J$4</f>
         <v>20629.107760310002</v>
       </c>
       <c r="G30" s="17">
-        <f>+[14]Main!$J$6-[14]Main!$J$5</f>
+        <f>+[25]Main!$J$6-[25]Main!$J$5</f>
         <v>4155.7999999999993</v>
       </c>
       <c r="H30" s="17">
@@ -14746,15 +14764,15 @@
         <v>27</v>
       </c>
       <c r="E31" s="19">
-        <f>+[15]Main!$I$2</f>
+        <f>+[26]Main!$I$2</f>
         <v>192.3</v>
       </c>
       <c r="F31" s="17">
-        <f>+[15]Main!$I$4</f>
+        <f>+[26]Main!$I$4</f>
         <v>22527.326947800004</v>
       </c>
       <c r="G31" s="17">
-        <f>+[15]Main!$I$6-[15]Main!$I$5</f>
+        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
         <v>2179.5999999999995</v>
       </c>
       <c r="H31" s="17">
@@ -14925,15 +14943,15 @@
         <v>27</v>
       </c>
       <c r="E39" s="19">
-        <f>+[16]Main!$I$2</f>
+        <f>+[27]Main!$I$2</f>
         <v>90.6</v>
       </c>
       <c r="F39" s="17">
-        <f>+[16]Main!$I$4</f>
+        <f>+[27]Main!$I$4</f>
         <v>10478.7931914</v>
       </c>
       <c r="G39" s="17">
-        <f>+[16]Main!$I$6-[16]Main!$I$5</f>
+        <f>+[27]Main!$I$6-[27]Main!$I$5</f>
         <v>-289.35000000000002</v>
       </c>
       <c r="H39" s="17">
@@ -14960,15 +14978,15 @@
         <v>27</v>
       </c>
       <c r="E40" s="19">
-        <f>+[17]Main!$J$2</f>
+        <f>+[28]Main!$J$2</f>
         <v>480.97</v>
       </c>
       <c r="F40" s="17">
-        <f>+[17]Main!$J$4</f>
+        <f>+[28]Main!$J$4</f>
         <v>16328.412533369999</v>
       </c>
       <c r="G40" s="17">
-        <f>+[17]Main!$J$6-[17]Main!$J$5</f>
+        <f>+[28]Main!$J$6-[28]Main!$J$5</f>
         <v>4491.2430000000004</v>
       </c>
       <c r="H40" s="17">
@@ -15055,15 +15073,15 @@
         <v>27</v>
       </c>
       <c r="E44" s="19">
-        <f>+[18]Main!$I$2</f>
+        <f>+[29]Main!$I$2</f>
         <v>164.28</v>
       </c>
       <c r="F44" s="17">
-        <f>+[18]Main!$I$4</f>
+        <f>+[29]Main!$I$4</f>
         <v>16076.2140936</v>
       </c>
       <c r="G44" s="17">
-        <f>+[18]Main!$I$6-[18]Main!$I$5</f>
+        <f>+[29]Main!$I$6-[29]Main!$I$5</f>
         <v>-277.411</v>
       </c>
       <c r="H44" s="17">
@@ -15494,15 +15512,15 @@
         <v>172</v>
       </c>
       <c r="E66" s="4">
-        <f>+[19]Main!$J$2</f>
+        <f>+[30]Main!$J$2</f>
         <v>190.5</v>
       </c>
       <c r="F66" s="17">
-        <f>+[19]Main!$J$4*FX!C10</f>
+        <f>+[30]Main!$J$4*FX!C10</f>
         <v>9653.9469578789995</v>
       </c>
       <c r="G66" s="17">
-        <f>+([19]Main!$J$6-[19]Main!$J$5)*FX!C10</f>
+        <f>+([30]Main!$J$6-[30]Main!$J$5)*FX!C10</f>
         <v>185.67080000000001</v>
       </c>
       <c r="H66" s="17">
@@ -15624,15 +15642,15 @@
         <v>27</v>
       </c>
       <c r="E72" s="4">
-        <f>+[20]Main!$J$2</f>
+        <f>+[31]Main!$J$2</f>
         <v>137.83000000000001</v>
       </c>
       <c r="F72" s="17">
-        <f>+[20]Main!$J$4</f>
+        <f>+[31]Main!$J$4</f>
         <v>5880.7446451600008</v>
       </c>
       <c r="G72" s="17">
-        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
+        <f>+[31]Main!$J$6-[31]Main!$J$5</f>
         <v>-65.975999999999999</v>
       </c>
       <c r="H72" s="17">
@@ -16704,15 +16722,15 @@
         <v>31</v>
       </c>
       <c r="E128" s="4">
-        <f>+[21]Main!$I$2</f>
+        <f>+[32]Main!$I$2</f>
         <v>15.7</v>
       </c>
       <c r="F128" s="17">
-        <f>+[21]Main!$I$4*FX!C3</f>
+        <f>+[32]Main!$I$4*FX!C3</f>
         <v>3243.4944</v>
       </c>
       <c r="G128" s="17">
-        <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C3</f>
+        <f>+([32]Main!$I$6-[32]Main!$I$5)*FX!C3</f>
         <v>2300.16</v>
       </c>
       <c r="H128" s="17">
@@ -18162,15 +18180,15 @@
         <v>172</v>
       </c>
       <c r="E203" s="4">
-        <f>+[22]Main!$J$2</f>
+        <f>+[33]Main!$J$2</f>
         <v>70.25</v>
       </c>
       <c r="F203" s="17">
-        <f>+[22]Main!$J$4*FX!C10</f>
+        <f>+[33]Main!$J$4*FX!C10</f>
         <v>772.74349442850007</v>
       </c>
       <c r="G203" s="17">
-        <f>+([22]Main!$J$6-[22]Main!$J$5)*FX!C10</f>
+        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C10</f>
         <v>466.023124</v>
       </c>
       <c r="H203" s="17">
@@ -18235,15 +18253,15 @@
         <v>146</v>
       </c>
       <c r="E206" s="4">
-        <f>+[23]Main!$H$2</f>
+        <f>+[34]Main!$H$2</f>
         <v>101.5</v>
       </c>
       <c r="F206" s="17">
-        <f>+[23]Main!$H$4*FX!C8</f>
+        <f>+[34]Main!$H$4*FX!C8</f>
         <v>788.28571457999999</v>
       </c>
       <c r="G206" s="17">
-        <f>+([23]Main!$H$6-[23]Main!$H$5)*FX!C8</f>
+        <f>+([34]Main!$H$6-[34]Main!$H$5)*FX!C8</f>
         <v>-77.263499999999993</v>
       </c>
       <c r="H206" s="17">
@@ -19231,15 +19249,15 @@
         <v>924</v>
       </c>
       <c r="E259" s="4">
-        <f>+[24]Main!$J$2</f>
+        <f>+[35]Main!$J$2</f>
         <v>58.4</v>
       </c>
       <c r="F259" s="17">
-        <f>+[24]Main!$J$4*FX!C10</f>
+        <f>+[35]Main!$J$4*FX!C10</f>
         <v>501.81546996000003</v>
       </c>
       <c r="G259" s="17">
-        <f>+([24]Main!$J$6-[24]Main!$J$5)*FX!C10</f>
+        <f>+([35]Main!$J$6-[35]Main!$J$5)*FX!C10</f>
         <v>12.976179999999999</v>
       </c>
       <c r="H259" s="17">
@@ -20831,15 +20849,15 @@
         <v>924</v>
       </c>
       <c r="E348" s="4">
-        <f>+[25]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>85</v>
       </c>
       <c r="F348" s="17">
-        <f>+[25]Main!$I$4*FX!C10</f>
+        <f>+[36]Main!$I$4*FX!C10</f>
         <v>302.45397000000003</v>
       </c>
       <c r="G348" s="17">
-        <f>+([25]Main!$I$6-[25]Main!$I$5)*FX!C10</f>
+        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C10</f>
         <v>86.644348000000022</v>
       </c>
       <c r="H348" s="17">
@@ -21358,15 +21376,15 @@
         <v>27</v>
       </c>
       <c r="E4" s="4">
-        <f>+[26]Main!$I$2</f>
+        <f>+[37]Main!$I$2</f>
         <v>70.05</v>
       </c>
       <c r="F4" s="17">
-        <f>+[26]Main!$I$4</f>
+        <f>+[37]Main!$I$4</f>
         <v>301327.69959224999</v>
       </c>
       <c r="G4" s="17">
-        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
+        <f>+[37]Main!$I$6-[37]Main!$I$5</f>
         <v>33524</v>
       </c>
       <c r="H4" s="17">
@@ -21580,15 +21598,15 @@
         <v>27</v>
       </c>
       <c r="E6" s="4">
-        <f>+[27]Main!$I$2</f>
+        <f>+[38]Main!$I$2</f>
         <v>153.69</v>
       </c>
       <c r="F6" s="17">
-        <f>+[27]Main!$I$4</f>
+        <f>+[38]Main!$I$4</f>
         <v>210040.29295557001</v>
       </c>
       <c r="G6" s="17">
-        <f>+[27]Main!$I$6-[27]Main!$I$5</f>
+        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
         <v>39652</v>
       </c>
       <c r="H6" s="17">
@@ -21905,15 +21923,15 @@
         <v>27</v>
       </c>
       <c r="E9" s="4">
-        <f>+[28]Main!$J$2</f>
+        <f>+[39]Main!$J$2</f>
         <v>87.85</v>
       </c>
       <c r="F9" s="17">
-        <f>+[28]Main!$J$4</f>
+        <f>+[39]Main!$J$4</f>
         <v>99859.095000000001</v>
       </c>
       <c r="G9" s="17">
-        <f>+[28]Main!$J$6-[28]Main!$J$5</f>
+        <f>+[39]Main!$J$6-[39]Main!$J$5</f>
         <v>12813.199999999997</v>
       </c>
       <c r="H9" s="17">
@@ -22642,15 +22660,15 @@
         <v>27</v>
       </c>
       <c r="E16" s="4">
-        <f>+[29]Main!$I$2</f>
+        <f>+[40]Main!$I$2</f>
         <v>141.83000000000001</v>
       </c>
       <c r="F16" s="17">
-        <f>+[29]Main!$I$4</f>
+        <f>+[40]Main!$I$4</f>
         <v>28675.237054880003</v>
       </c>
       <c r="G16" s="17">
-        <f>+[29]Main!$I$6-[29]Main!$I$5</f>
+        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
         <v>10472.9</v>
       </c>
       <c r="H16" s="17">
@@ -33776,7 +33794,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>734400.26206676755</v>
+        <v>741138.60699476756</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
@@ -33784,7 +33802,7 @@
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>831433.33674476773</v>
+        <v>838171.68167276774</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33869,15 +33887,15 @@
         <v>27</v>
       </c>
       <c r="E5" s="31">
-        <f>+[30]Main!$K$3</f>
+        <f>+[1]Main!$K$3</f>
         <v>192</v>
       </c>
       <c r="F5" s="17">
-        <f>+[30]Main!$K$5</f>
+        <f>+[1]Main!$K$5</f>
         <v>299243.29843199998</v>
       </c>
       <c r="G5" s="17">
-        <f>+[30]Main!$K$7-[30]Main!$K$6</f>
+        <f>+[1]Main!$K$7-[1]Main!$K$6</f>
         <v>44051</v>
       </c>
       <c r="H5" s="17">
@@ -33980,15 +33998,15 @@
         <v>27</v>
       </c>
       <c r="E6" s="31">
-        <f>+[31]Main!$M$3</f>
+        <f>+[2]Main!$M$3</f>
         <v>66.25</v>
       </c>
       <c r="F6" s="17">
-        <f>+[31]Main!$M$5</f>
+        <f>+[2]Main!$M$5</f>
         <v>111498.75</v>
       </c>
       <c r="G6" s="17">
-        <f>+[31]Main!$M$7-[31]Main!$M$6</f>
+        <f>+[2]Main!$M$7-[2]Main!$M$6</f>
         <v>21235</v>
       </c>
       <c r="H6" s="17">
@@ -34093,20 +34111,20 @@
         <v>31</v>
       </c>
       <c r="E7" s="31">
-        <f>+[32]Main!$H$2</f>
+        <f>+[3]Main!$H$2</f>
         <v>60.8</v>
       </c>
       <c r="F7" s="17">
-        <f>+[32]Main!$H$5*FX!C3</f>
-        <v>122499.9936</v>
+        <f>+[3]Main!$H$5*FX!C3</f>
+        <v>129190.46400000001</v>
       </c>
       <c r="G7" s="17">
-        <f>+([31]Main!$M$7-[31]Main!$M$6)*FX!C3</f>
+        <f>+([2]Main!$M$7-[2]Main!$M$6)*FX!C3</f>
         <v>27180.799999999999</v>
       </c>
       <c r="H7" s="17">
         <f>F7+G7</f>
-        <v>149680.7936</v>
+        <v>156371.264</v>
       </c>
       <c r="I7" s="38" t="s">
         <v>1174</v>
@@ -34203,15 +34221,15 @@
         <v>40</v>
       </c>
       <c r="E8" s="31">
-        <f>+[33]Main!$H$2</f>
+        <f>+[4]Main!$H$2</f>
         <v>485.4</v>
       </c>
       <c r="F8" s="17">
-        <f>+[33]Main!$H$4*FX!C4</f>
+        <f>+[4]Main!$H$4*FX!C4</f>
         <v>72888.393927045603</v>
       </c>
       <c r="G8" s="17">
-        <f>+([33]Main!$H$6-[33]Main!$H$5)*FX!C4</f>
+        <f>+([4]Main!$H$6-[4]Main!$H$5)*FX!C4</f>
         <v>-228.87708000000006</v>
       </c>
       <c r="H8" s="17">
@@ -34304,15 +34322,15 @@
         <v>95</v>
       </c>
       <c r="E9" s="17">
-        <f>+[34]Main!$J$2</f>
+        <f>+[5]Main!$J$2</f>
         <v>5714</v>
       </c>
       <c r="F9" s="17">
-        <f>+[34]Main!$J$4*FX!C5</f>
+        <f>+[5]Main!$J$4*FX!C5</f>
         <v>68983.677500799997</v>
       </c>
       <c r="G9" s="17">
-        <f>+([34]Main!$J$6-[34]Main!$J$5)*FX!C5</f>
+        <f>+([5]Main!$J$6-[5]Main!$J$5)*FX!C5</f>
         <v>2758.2091999999998</v>
       </c>
       <c r="H9" s="17">
@@ -34410,15 +34428,15 @@
         <v>31</v>
       </c>
       <c r="E10" s="31">
-        <f>+[35]Main!$I$2</f>
+        <f>+[6]Main!$I$2</f>
         <v>32.61</v>
       </c>
       <c r="F10" s="17">
-        <f>+([35]Main!$I$4)*FX!C3</f>
+        <f>+([6]Main!$I$4)*FX!C3</f>
         <v>34427.811840000002</v>
       </c>
       <c r="G10" s="17">
-        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C3</f>
+        <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C3</f>
         <v>10438.4</v>
       </c>
       <c r="H10" s="17">
@@ -34511,15 +34529,15 @@
         <v>617</v>
       </c>
       <c r="E11" s="17">
-        <f>+[36]Main!$I$2</f>
+        <f>+[7]Main!$I$2</f>
         <v>107400</v>
       </c>
       <c r="F11" s="17">
-        <f>+[36]Main!$I$4*FX!C6</f>
+        <f>+[7]Main!$I$4*FX!C6</f>
         <v>9270.9964935000007</v>
       </c>
       <c r="G11" s="17">
-        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C6</f>
+        <f>+([7]Main!$I$6-[7]Main!$I$5)*FX!C6</f>
         <v>-575.42399999999998</v>
       </c>
       <c r="H11" s="17">
@@ -34610,15 +34628,15 @@
         <v>240</v>
       </c>
       <c r="E12" s="17">
-        <f>+[37]Main!$I$2</f>
+        <f>+[8]Main!$I$2</f>
         <v>590</v>
       </c>
       <c r="F12" s="17">
-        <f>+[37]Main!$I$4*FX!C7</f>
+        <f>+[8]Main!$I$4*FX!C7</f>
         <v>4254.915253002001</v>
       </c>
       <c r="G12" s="17">
-        <f>+([37]Main!$I$6-[37]Main!$I$5)*FX!C7</f>
+        <f>+([8]Main!$I$6-[8]Main!$I$5)*FX!C7</f>
         <v>-162.340056</v>
       </c>
       <c r="H12" s="17">
@@ -35037,20 +35055,20 @@
         <v>527</v>
       </c>
       <c r="E17" s="31">
-        <f>+[38]Main!$J$2</f>
-        <v>66.2</v>
+        <f>+[9]Main!$J$2</f>
+        <v>70</v>
       </c>
       <c r="F17" s="17">
-        <f>+[38]Main!$J$4*FX!C11</f>
-        <v>834.02467200000001</v>
+        <f>+[9]Main!$J$4*FX!C11</f>
+        <v>881.89919999999995</v>
       </c>
       <c r="G17" s="17">
-        <f>+([38]Main!$J$6-[38]Main!$J$5)*FX!C11</f>
+        <f>+([9]Main!$J$6-[9]Main!$J$5)*FX!C11</f>
         <v>761.13600000000008</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ref="H17" si="3">F17+G17</f>
-        <v>1595.160672</v>
+        <v>1643.0352</v>
       </c>
       <c r="I17" s="43" t="s">
         <v>1175</v>
@@ -35217,15 +35235,15 @@
         <v>27</v>
       </c>
       <c r="E19" s="31">
-        <f>+[39]Main!$I$3</f>
+        <f>+[10]Main!$I$3</f>
         <v>90.75</v>
       </c>
       <c r="F19" s="17">
-        <f>+[39]Main!$I$5</f>
+        <f>+[10]Main!$I$5</f>
         <v>1757.6037105</v>
       </c>
       <c r="G19" s="17">
-        <f>+[39]Main!$I$7-[39]Main!$I$6</f>
+        <f>+[10]Main!$I$7-[10]Main!$I$6</f>
         <v>101.446</v>
       </c>
       <c r="H19" s="17">
@@ -35314,15 +35332,15 @@
         <v>27</v>
       </c>
       <c r="E20" s="31">
-        <f>+[40]Main!$I$2</f>
+        <f>+[11]Main!$I$2</f>
         <v>4.3600000000000003</v>
       </c>
       <c r="F20" s="17">
-        <f>+[40]Main!$I$4</f>
+        <f>+[11]Main!$I$4</f>
         <v>248.91663792000003</v>
       </c>
       <c r="G20" s="17">
-        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
+        <f>+[11]Main!$I$6-[11]Main!$I$5</f>
         <v>-34.395385999999995</v>
       </c>
       <c r="H20" s="17">

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F63282-C3E6-4CEC-9F2C-99106288807C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D853CA-0764-441F-A85F-5C4D3B155720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="4890" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3960,19 +3960,19 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -4889,25 +4889,19 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>60.8</v>
+            <v>63.6</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>100930.05</v>
+            <v>104105.3</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
-        <row r="4">
-          <cell r="J4">
-            <v>42.245377497915634</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5116,13 +5110,7 @@
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
-        <row r="3">
-          <cell r="J3">
-            <v>97.40723155701005</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
     </sheetDataSet>
   </externalBook>
@@ -5607,13 +5595,7 @@
       </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="4">
-          <cell r="J4">
-            <v>110.50341825100335</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -18268,7 +18250,7 @@
         <f>+F206+G206</f>
         <v>711.02221457999997</v>
       </c>
-      <c r="I206" s="44" t="s">
+      <c r="I206" s="43" t="s">
         <v>1176</v>
       </c>
       <c r="J206" s="22">
@@ -21613,7 +21595,7 @@
         <f>+F6+G6</f>
         <v>249692.29295557001</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="40" t="s">
         <v>1174</v>
       </c>
       <c r="J6" s="4"/>
@@ -33794,7 +33776,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>741138.60699476756</v>
+        <v>745202.92699476751</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
@@ -33802,7 +33784,7 @@
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>838171.68167276774</v>
+        <v>842236.0016727678</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -33902,7 +33884,7 @@
         <f>+F5+G5</f>
         <v>343294.29843199998</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="41" t="s">
         <v>1175</v>
       </c>
       <c r="J5" s="22"/>
@@ -34013,7 +33995,7 @@
         <f>+F6+G6</f>
         <v>132733.75</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="39" t="s">
         <v>1174</v>
       </c>
       <c r="J6" s="22">
@@ -34112,11 +34094,11 @@
       </c>
       <c r="E7" s="31">
         <f>+[3]Main!$H$2</f>
-        <v>60.8</v>
+        <v>63.6</v>
       </c>
       <c r="F7" s="17">
         <f>+[3]Main!$H$5*FX!C3</f>
-        <v>129190.46400000001</v>
+        <v>133254.78400000001</v>
       </c>
       <c r="G7" s="17">
         <f>+([2]Main!$M$7-[2]Main!$M$6)*FX!C3</f>
@@ -34124,13 +34106,13 @@
       </c>
       <c r="H7" s="17">
         <f>F7+G7</f>
-        <v>156371.264</v>
-      </c>
-      <c r="I7" s="38" t="s">
-        <v>1174</v>
+        <v>160435.584</v>
+      </c>
+      <c r="I7" s="44" t="s">
+        <v>1176</v>
       </c>
       <c r="J7" s="22">
-        <v>46203</v>
+        <v>46429</v>
       </c>
       <c r="K7" s="31">
         <f>25592.8810095771*C31</f>
@@ -34337,7 +34319,7 @@
         <f t="shared" si="1"/>
         <v>71741.886700799994</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="39" t="s">
         <v>1174</v>
       </c>
       <c r="J9" s="22">
@@ -34443,7 +34425,7 @@
         <f t="shared" si="1"/>
         <v>44866.211840000004</v>
       </c>
-      <c r="I10" s="39" t="s">
+      <c r="I10" s="38" t="s">
         <v>1174</v>
       </c>
       <c r="J10" s="22">
@@ -35070,7 +35052,7 @@
         <f t="shared" ref="H17" si="3">F17+G17</f>
         <v>1643.0352</v>
       </c>
-      <c r="I17" s="43" t="s">
+      <c r="I17" s="42" t="s">
         <v>1175</v>
       </c>
       <c r="J17" s="22">
@@ -35250,7 +35232,7 @@
         <f t="shared" ref="H19:H20" si="4">F19+G19</f>
         <v>1859.0497104999999</v>
       </c>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="41" t="s">
         <v>1175</v>
       </c>
       <c r="J19" s="22"/>

--- a/ConsumerGoods.xlsx
+++ b/ConsumerGoods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D853CA-0764-441F-A85F-5C4D3B155720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E647E415-0DA4-4CAE-A1E6-4BAF8EEF4190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4890" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
+    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{C5F9E374-3D8E-42B5-B067-E68CE63456D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3966,10 +3966,10 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4898,10 +4898,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5574,28 +5574,28 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>70</v>
+            <v>71.599999999999994</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>5511.87</v>
+            <v>5629.192</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>13.5</v>
+            <v>61.6</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>4770.6000000000004</v>
+            <v>4941.8999999999996</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -18250,7 +18250,7 @@
         <f>+F206+G206</f>
         <v>711.02221457999997</v>
       </c>
-      <c r="I206" s="43" t="s">
+      <c r="I206" s="42" t="s">
         <v>1176</v>
       </c>
       <c r="J206" s="22">
@@ -33776,15 +33776,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="29">
         <f>SUM(F5:F23)</f>
-        <v>745202.92699476751</v>
+        <v>745221.69851476757</v>
       </c>
       <c r="G4" s="29">
         <f>SUM(G5:G23)</f>
-        <v>105524.95467799998</v>
+        <v>105544.66667799998</v>
       </c>
       <c r="H4" s="29">
         <f>SUM(H5:H23)</f>
-        <v>842236.0016727678</v>
+        <v>842274.48519276781</v>
       </c>
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
@@ -34108,7 +34108,7 @@
         <f>F7+G7</f>
         <v>160435.584</v>
       </c>
-      <c r="I7" s="44" t="s">
+      <c r="I7" s="43" t="s">
         <v>1176</v>
       </c>
       <c r="J7" s="22">
@@ -35038,25 +35038,25 @@
       </c>
       <c r="E17" s="31">
         <f>+[9]Main!$J$2</f>
-        <v>70</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="F17" s="17">
         <f>+[9]Main!$J$4*FX!C11</f>
-        <v>881.89919999999995</v>
+        <v>900.67072000000007</v>
       </c>
       <c r="G17" s="17">
         <f>+([9]Main!$J$6-[9]Main!$J$5)*FX!C11</f>
-        <v>761.13600000000008</v>
+        <v>780.84799999999996</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ref="H17" si="3">F17+G17</f>
-        <v>1643.0352</v>
-      </c>
-      <c r="I17" s="42" t="s">
-        <v>1175</v>
+        <v>1681.51872</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>1176</v>
       </c>
       <c r="J17" s="22">
-        <v>46260</v>
+        <v>46338</v>
       </c>
       <c r="K17" s="31"/>
       <c r="L17" s="4"/>
